--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>&gt; ご利用上の注意</t>
+          <t>&gt; ⚠️ ご利用上の注意</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>&gt; 修正はその権限をお持ちの全員に反映されます</t>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>&gt; 権限を外した方はログインしても画面が表示されません</t>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">

--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>ラクミー経営管理クラウドを使うメンバーごとに、「どの画面を見られるか」「どの店舗のデータを扱えるか」を設定できます。経理担当・エリアマネージャー・アルバイトリーダーなど、貴社の体制に合わせた権限を自由に作成できます。</t>
+          <t>ラクミー経営管理クラウドを使うメンバーごとに、どの画面を見られるかを設定できます。経理担当・エリアマネージャー・アルバイトリーダーなど、貴社の体制に合わせた権限を自由に作成できます。</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -694,7 +694,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>エリアマネージャーに担当店舗だけ見せたい ｜ 店舗の権限を作り、担当2店舗を紐付ける</t>
+          <t>人事担当に従業員情報だけ見せたい ｜ 従業員関連を「閲覧」、売上系を「なし」</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>顧問税理士に数字を見せたいが、変更はさせたくない ｜ 全画面を「閲覧」に設定</t>
+          <t>アルバイトリーダーに売上画面だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -720,36 +720,40 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに売上だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
+          <t>新入社員にはまず最小限から始めたい ｜ ダッシュボード以外を「なし」</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 今回のリリースでできること</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ご利用の前提条件</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>・操作できるのは本部管理者のみです。</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -759,7 +763,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
+          <t>・操作できるのは本部管理者のみです。</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -772,7 +776,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
+          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -785,62 +789,62 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>・権限は会社／店舗の区分で分かれます。区分によって設定できる画面が変わります。</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>用語の説明</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>設定を始める前に、3つの言葉を押さえてください。</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>用語 ｜ 意味</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
+      <c r="C22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -850,7 +854,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
+          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -863,7 +867,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>担当店舗 ｜ どの店舗のデータを扱えるか。メンバーごとに設定します</t>
+          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -871,12 +875,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>権限と担当店舗は別々に設定します。 同じ「エリアマネージャー」でも、Aさんは2店舗、Bさんは3店舗というように担当が異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
+          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -889,46 +893,46 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>権限と担当店舗は別々に設定します。 同じ「エリアマネージャー」でも、Aさんは2店舗、Bさんは3店舗というように担当が異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>ご利用の流れ</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>権限を使い始めるまでの全体像です。</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>1. 初期設定で権限を用意する — おすすめの権限をまとめて登録します。</t>
+          <t>権限を使い始めるまでの全体像です。</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -941,7 +945,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2. 足りない権限を作る — 貴社に合わせた権限を追加します。</t>
+          <t>1. 初期設定で権限を用意する — おすすめの権限をまとめて登録します。</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -954,7 +958,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>3. メンバーに割り当てる — 誰にどの権限を付けるかを決めます。</t>
+          <t>2. 足りない権限を作る — 貴社に合わせた権限を追加します。</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -967,7 +971,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>4. 担当店舗を設定する — 店舗の権限を付けた方に、担当店舗を紐付けます。</t>
+          <t>3. メンバーに割り当てる — 誰にどの権限を付けるかを決めます。</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -980,75 +984,75 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>4. 担当店舗を設定する — 店舗の権限を付けた方に、担当店舗を紐付けます。</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>5. 確認する — 誰が何の権限を持っているかを一覧で確認します。</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>導入時の初期設定</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
+          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>1. 用意する権限を選びます（初期状態ではすべて選択されています）。</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>権限 ｜ 内容</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
+      <c r="C38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1058,7 +1062,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>会社ロール（権限の土台） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1071,7 +1075,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>店長（権限の土台） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
+          <t>会社ロール（権限の土台） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1084,7 +1088,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>店長（権限の土台） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1092,12 +1096,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2. それぞれの初期値を選びます（推奨／操作可／閲覧のみ／なし）。</t>
+          <t>従業員 ｜ 閲覧が中心です</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1110,42 +1114,38 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>2. それぞれの初期値を選びます（推奨／操作可／閲覧のみ／なし）。</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
           <t>3. 「適用」を選択すると、権限一覧に登録された状態になります。</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>【画像①】</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>権限テンプレートの画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 途中で中断できます</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>「一時保存」を選択すると、選んだ内容が保存されます。別の画面に移動しても、次に開いたときに続きから設定できます。</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>&gt; やり直したいとき</t>
+          <t>&gt; 途中で中断できます</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>「下書きを破棄」を選択すると、保存した内容が消えて初期状態に戻ります。</t>
+          <t>「一時保存」を選択すると、選んだ内容が保存されます。別の画面に移動しても、次に開いたときに続きから設定できます。</t>
         </is>
       </c>
     </row>
@@ -1174,53 +1174,57 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>&gt; やり直したいとき</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>「下書きを破棄」を選択すると、保存した内容が消えて初期状態に戻ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>導入時は「会社ロール」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>権限を作成する</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>STEP 1　権限設定画面を開く</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
+      <c r="C50" s="13" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -1230,7 +1234,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -1243,70 +1247,70 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>【画像②】</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>権限設定の一覧画面</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>&gt; スコープによって表示が変わります</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>STEP 2　雛形を選ぶ</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>1. 「＋ 権限を新規作成」を選択します。</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr"/>
+      <c r="C56" s="13" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -1316,36 +1320,36 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
+          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
           <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>雛形 ｜ 内容</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr"/>
+      <c r="C59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -1355,7 +1359,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -1368,7 +1372,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -1381,7 +1385,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>従業員 ｜ 閲覧が中心です</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -1394,42 +1398,38 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>【画像③】</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>雛形（ベース）の選択画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ゼロから設定する必要はありません</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
         </is>
       </c>
     </row>
@@ -1441,40 +1441,44 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
+          <t>&gt; ゼロから設定する必要はありません</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
           <t>&gt; エリアマネージャーのような役割は「店長」から作ります</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>雛形にはありませんが、店長を雛形に選んで権限名を「エリアマネージャー」に変え、担当店舗を複数紐付ければ作れます。組織によって権限の中身が変わるため、雛形としては用意していません。</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>STEP 3　権限名と区分を決める</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
+      <c r="C68" s="13" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -1484,36 +1488,36 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
           <t>2. 区分を選びます。</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>区分 ｜ 設定できる画面</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>会社 ｜ 共通の画面＋会社画面（会社情報・お支払い・店舗管理・ダウンロード）</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr"/>
+      <c r="C71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -1523,27 +1527,23 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
+          <t>会社 ｜ 共通の画面＋会社画面（会社情報・お支払い・店舗管理・ダウンロード）</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>店舗 ｜ 共通の画面＋店舗画面（発注先&amp;仕入商品・店舗情報・連携設定・費用設定・休業日設定・予算設定）</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
+      <c r="C73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -1553,66 +1553,70 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
           <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>STEP 4　画面ごとに設定する</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B76" s="4" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>画面ごとに「操作」「閲覧」「なし」を選びます。</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>設定 ｜ できること</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr"/>
+      <c r="C78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -1622,7 +1626,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>閲覧 ｜ 画面を開けますが、変更はできません</t>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -1635,7 +1639,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>なし ｜ 画面が表示されません</t>
+          <t>閲覧 ｜ 画面を開けます</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -1643,127 +1647,131 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>なし ｜ 画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 「閲覧」と「操作」の違いについて</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="12" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>【画像④】</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C84" s="12" t="inlineStr">
         <is>
           <t>画面ごとの設定（操作／閲覧／なし）</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>&gt; さらに細かく設定するには</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
         </is>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>3. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>作成した権限を修正する</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+          <t>3. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr"/>
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr"/>
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -1773,7 +1781,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -1786,59 +1794,51 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
           <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B92" s="12" t="inlineStr">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>【画像⑤】</t>
         </is>
       </c>
-      <c r="C92" s="12" t="inlineStr">
+      <c r="C94" s="12" t="inlineStr">
         <is>
           <t>マス目を選択して該当箇所へ移動したところ</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -1850,79 +1850,87 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
+          <t>&gt; マス目を選択すると該当箇所が開きます</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
           <t>&gt; 割当の画面からも権限を新規作成できます</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選択できます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
+      <c r="B98" s="9" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B98" s="14" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
-        </is>
-      </c>
-      <c r="C98" s="13" t="inlineStr"/>
+      <c r="C98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
+          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr"/>
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -1932,7 +1940,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -1945,100 +1953,100 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
+          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
           <t>4. 「保存」を選択します。</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B103" s="12" t="inlineStr">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>【画像⑥】</t>
         </is>
       </c>
-      <c r="C103" s="12" t="inlineStr">
+      <c r="C105" s="12" t="inlineStr">
         <is>
           <t>まとめて割り当てる画面</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>&gt; すでに別の権限をお持ちの方</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>&gt; 対象の絞り込み</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="13" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B106" s="14" t="inlineStr">
+      <c r="B108" s="14" t="inlineStr">
         <is>
           <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
         </is>
       </c>
-      <c r="C106" s="13" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr"/>
+      <c r="C108" s="13" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -2048,7 +2056,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>3. 権限を1つ選びます。</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
@@ -2061,66 +2069,66 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
+          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>3. 権限を1つ選びます。</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
           <t>4. 「保存」を選択します。</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="12" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B111" s="12" t="inlineStr">
+      <c r="B113" s="12" t="inlineStr">
         <is>
           <t>【画像⑦】</t>
         </is>
       </c>
-      <c r="C111" s="12" t="inlineStr">
+      <c r="C113" s="12" t="inlineStr">
         <is>
           <t>メンバーごとの割当編集画面</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="13" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B112" s="14" t="inlineStr">
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
         </is>
       </c>
-      <c r="C112" s="13" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>2. 対象の権限の「割当へ →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr"/>
+      <c r="C114" s="13" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -2130,59 +2138,59 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr"/>
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>2. 対象の権限の「割当へ →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>店舗の権限を割り当てると、担当店舗の選択欄が表示されます。</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr"/>
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+          <t>店舗の権限を割り当てると、担当店舗の選択欄が表示されます。</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
@@ -2195,7 +2203,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
@@ -2208,152 +2216,152 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
+          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
           <t>4. 「保存」を選択します。</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="12" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B122" s="12" t="inlineStr">
+      <c r="B124" s="12" t="inlineStr">
         <is>
           <t>【画像⑧】</t>
         </is>
       </c>
-      <c r="C122" s="12" t="inlineStr">
+      <c r="C124" s="12" t="inlineStr">
         <is>
           <t>担当店舗の選択画面</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗の反映について</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B128" s="9" t="inlineStr">
         <is>
           <t>権限を変更・解除する</t>
         </is>
       </c>
-      <c r="C125" s="8" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="C128" s="8" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>&gt; 別の権限に変更する</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>&gt; 権限を外す</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr"/>
+      <c r="C131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -2363,182 +2371,190 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに変えられます。</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr"/>
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr"/>
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 設定の反映について</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
           <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="12" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B136" s="12" t="inlineStr">
+      <c r="B140" s="12" t="inlineStr">
         <is>
           <t>【画像⑨】</t>
         </is>
       </c>
-      <c r="C136" s="12" t="inlineStr">
+      <c r="C140" s="12" t="inlineStr">
         <is>
           <t>指標一覧の画面</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>&gt; 初期値は自動で設定されます</t>
         </is>
       </c>
-      <c r="C137" s="5" t="inlineStr">
+      <c r="C141" s="5" t="inlineStr">
         <is>
           <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="B142" s="6" t="inlineStr">
         <is>
           <t>&gt; 項目が多い場合は「指標条件設定」が便利です</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>&gt; 作った組み合わせは保存して使い回せます</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr">
         <is>
           <t>「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B140" s="9" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>オーナーだけができること</t>
         </is>
       </c>
-      <c r="C140" s="8" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="10" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B142" s="11" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C142" s="10" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
-        </is>
-      </c>
-      <c r="C143" s="4" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr"/>
+      <c r="C144" s="8" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -2548,33 +2564,33 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>設定内容を確認する</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr"/>
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr"/>
@@ -2582,12 +2598,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr"/>
@@ -2600,108 +2616,92 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
           <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="12" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B150" s="12" t="inlineStr">
+      <c r="B154" s="12" t="inlineStr">
         <is>
           <t>【画像⑩】</t>
         </is>
       </c>
-      <c r="C150" s="12" t="inlineStr">
+      <c r="C154" s="12" t="inlineStr">
         <is>
           <t>役割サマリの画面</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="8" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B151" s="9" t="inlineStr">
+      <c r="B155" s="9" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
-      <c r="C151" s="8" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B152" s="15" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C152" s="15" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B153" s="15" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C153" s="15" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B154" s="15" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C154" s="15" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B155" s="15" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C155" s="15" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
+      <c r="C155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="15" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -2728,12 +2728,12 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Q. 同じ権限で、人によって見える店舗を変えられますか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C157" s="15" t="inlineStr">
         <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ「エリアマネージャー」でも、Aさんは2店舗、Bさんは3店舗という設定が可能です。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C159" s="15" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
         </is>
       </c>
       <c r="C161" s="15" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
@@ -2813,82 +2813,167 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B163" s="15" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C163" s="15" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B164" s="15" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C164" s="15" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B165" s="15" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C165" s="15" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B166" s="15" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C166" s="15" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B167" s="15" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C162" s="15" t="inlineStr">
+      <c r="C167" s="15" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="8" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B163" s="9" t="inlineStr">
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C163" s="8" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="4" t="inlineStr">
+      <c r="C168" s="8" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
+      <c r="C171" s="4" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C167" s="4" t="inlineStr"/>
+      <c r="C172" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C167"/>
+  <autoFilter ref="A2:C172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -932,33 +932,33 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>権限を使い始めるまでの全体像です。</t>
+          <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>1. 初期設定で権限を用意する — おすすめの権限をまとめて登録します。</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>画面 ｜ ここで何をするか</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2. 足りない権限を作る — 貴社に合わせた権限を追加します。</t>
+          <t>権限設定 ｜ 権限を作る・直す</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -966,12 +966,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>3. メンバーに割り当てる — 誰にどの権限を付けるかを決めます。</t>
+          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -979,51 +979,55 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>4. 担当店舗を設定する — 店舗の権限を付けた方に、担当店舗を紐付けます。</t>
+          <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>5. 確認する — 誰が何の権限を持っているかを一覧で確認します。</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>導入時の初期設定</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr"/>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
+          <t>1. 初期設定で権限を用意する — おすすめの権限をまとめて登録します。</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1036,33 +1040,33 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>1. 用意する権限を選びます（初期状態ではすべて選択されています）。</t>
+          <t>2. 足りない権限を作る — 貴社に合わせた権限を追加します。</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>権限 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr"/>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>3. メンバーに割り当てる — 誰にどの権限を付けるかを決めます。</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
+          <t>4. 担当店舗を設定する — 店舗の権限を付けた方に、担当店舗を紐付けます。</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1070,38 +1074,38 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>会社ロール（権限の土台） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+          <t>5. 権限一覧で確認する — 誰が何の権限を持っているかを確認します。</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>店長（権限の土台） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr"/>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>導入時の初期設定</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1114,190 +1118,182 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>1. 用意する権限を選びます（初期状態ではすべて選択されています）。</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>権限 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>会社ロール（権限の土台） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>店長（権限の土台） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>従業員 ｜ 閲覧が中心です</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>2. それぞれの初期値を選びます（推奨／操作可／閲覧のみ／なし）。</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>3. 「適用」を選択すると、権限一覧に登録された状態になります。</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>【画像①】</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>権限テンプレートの画面</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>&gt; 途中で中断できます</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>「一時保存」を選択すると、選んだ内容が保存されます。別の画面に移動しても、次に開いたときに続きから設定できます。</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>&gt; やり直したいとき</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>「下書きを破棄」を選択すると、保存した内容が消えて初期状態に戻ります。</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>導入時は「会社ロール」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>権限を作成する</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>STEP 1　権限設定画面を開く</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>【画像②】</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>権限設定の一覧画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>&gt; スコープによって表示が変わります</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
-        </is>
-      </c>
+      <c r="C55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
@@ -1307,7 +1303,7 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>STEP 2　雛形を選ぶ</t>
+          <t>STEP 1　権限設定画面を開く</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr"/>
@@ -1320,7 +1316,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -1333,72 +1329,80 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>雛形 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr"/>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr"/>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>【画像②】</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>権限設定の一覧画面</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>&gt; スコープによって表示が変わります</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>STEP 2　雛形を選ぶ</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>1. 「＋ 権限を新規作成」を選択します。</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -1406,89 +1410,77 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>雛形 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
           <t>表 行</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>【画像③】</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>雛形（ベース）の選択画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ゼロから設定する必要はありません</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
-        </is>
-      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>&gt; エリアマネージャーのような役割は「店長」から作ります</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>雛形にはありませんが、店長を雛形に選んで権限名を「エリアマネージャー」に変え、担当店舗を複数紐付ければ作れます。組織によって権限の中身が変わるため、雛形としては用意していません。</t>
-        </is>
-      </c>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>STEP 3　権限名と区分を決める</t>
-        </is>
-      </c>
-      <c r="C68" s="13" t="inlineStr"/>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>従業員 ｜ 閲覧が中心です</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -1496,127 +1488,131 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
+          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>【画像③】</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>雛形（ベース）の選択画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ゼロから設定する必要はありません</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>&gt; エリアマネージャーのような役割は「店長」から作ります</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>雛形にはありませんが、店長を雛形に選んで権限名を「エリアマネージャー」に変え、担当店舗を複数紐付ければ作れます。組織によって権限の中身が変わるため、雛形としては用意していません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>2. 区分を選びます。</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>区分 ｜ 設定できる画面</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>表 行</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>会社 ｜ 共通の画面＋会社画面（会社情報・お支払い・店舗管理・ダウンロード）</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>店舗 ｜ 共通の画面＋店舗画面（発注先&amp;仕入商品・店舗情報・連携設定・費用設定・休業日設定・予算設定）</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>STEP 4　画面ごとに設定する</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>画面ごとに「操作」「閲覧」「なし」を選びます。</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>設定 ｜ できること</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr"/>
+      <c r="C78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -1626,53 +1622,57 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
+          <t>店舗 ｜ 共通の画面＋店舗画面（発注先&amp;仕入商品・店舗情報・連携設定・費用設定・休業日設定・予算設定）</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>閲覧 ｜ 画面を開けます</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr"/>
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>なし ｜ 画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 「閲覧」と「操作」の違いについて</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
-        </is>
-      </c>
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>STEP 4　画面ごとに設定する</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -1682,371 +1682,363 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
+          <t>画面ごとに「操作」「閲覧」「なし」を選びます。</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>【画像④】</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t>画面ごとの設定（操作／閲覧／なし）</t>
-        </is>
-      </c>
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>設定 ｜ できること</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>&gt; さらに細かく設定するには</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
-        </is>
-      </c>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>3. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
+          <t>閲覧 ｜ 画面を開けます</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>作成した権限を修正する</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr"/>
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>なし ｜ 画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 「閲覧」と「操作」の違いについて</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr"/>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr"/>
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>【画像④】</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>画面ごとの設定（操作／閲覧／なし）</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr"/>
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>&gt; さらに細かく設定するには</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>3. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
           <t>表 行</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑤】</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 割当の画面からも権限を新規作成できます</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選択できます。作成後は元の割当編集の画面に戻ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>権限をメンバーに割り当てる</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr"/>
+      <c r="C98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑤】</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>マス目を選択して該当箇所へ移動したところ</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>&gt; マス目を選択すると該当箇所が開きます</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 割当の画面からも権限を新規作成できます</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選択できます。作成後は元の割当編集の画面に戻ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="13" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B100" s="14" t="inlineStr">
+      <c r="B106" s="14" t="inlineStr">
         <is>
           <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
         </is>
       </c>
-      <c r="C100" s="13" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="C106" s="13" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑥】</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>まとめて割り当てる画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>&gt; すでに別の権限をお持ちの方</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 対象の絞り込み</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B108" s="14" t="inlineStr">
-        <is>
-          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
-        </is>
-      </c>
-      <c r="C108" s="13" t="inlineStr"/>
+      <c r="C108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -2056,7 +2048,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
@@ -2069,51 +2061,59 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
+          <t>4. 「保存」を選択します。</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>3. 権限を1つ選びます。</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr"/>
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑥】</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>まとめて割り当てる画面</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr"/>
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>&gt; すでに別の権限をお持ちの方</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>メンバーごとの割当編集画面</t>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 対象の絞り込み</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr"/>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の権限の「割当へ →」を選択します。</t>
+          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr"/>
@@ -2164,49 +2164,53 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
+          <t>3. 権限を1つ選びます。</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr"/>
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択します。</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>店舗の権限を割り当てると、担当店舗の選択欄が表示されます。</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr"/>
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>メンバーごとの割当編集画面</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr"/>
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+        </is>
+      </c>
+      <c r="C120" s="13" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
@@ -2229,7 +2233,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
+          <t>2. 対象の権限の「割当へ →」を選択します。</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr"/>
@@ -2242,113 +2246,105 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択します。</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B124" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑧】</t>
-        </is>
-      </c>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面</t>
-        </is>
-      </c>
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>店舗の権限を割り当てると、担当店舗の選択欄が表示されます。</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗の反映について</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr"/>
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr"/>
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択します。</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr"/>
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -2358,10 +2354,14 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>&gt; 権限を外す</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr"/>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
+          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+          <t>&gt; 担当店舗の反映について</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
@@ -2401,113 +2401,105 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>表示する数字を選ぶ</t>
+          <t>権限を変更・解除する</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 設定の反映について</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr"/>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限を外す</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr"/>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B140" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C140" s="12" t="inlineStr">
-        <is>
-          <t>指標一覧の画面</t>
-        </is>
-      </c>
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 初期値は自動で設定されます</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
-        </is>
-      </c>
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -2517,109 +2509,121 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>&gt; 項目が多い場合は「指標条件設定」が便利です</t>
+          <t>&gt; 設定の反映について</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
+          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 作った組み合わせは保存して使い回せます</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
-        </is>
-      </c>
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr"/>
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B146" s="11" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C146" s="10" t="inlineStr"/>
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B146" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑨】</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>指標一覧の画面</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr"/>
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 初期値は自動で設定されます</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr"/>
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 項目が多い場合は「指標条件設定」が便利です</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr"/>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 作った組み合わせは保存して使い回せます</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="8" t="inlineStr">
@@ -2629,7 +2633,7 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>設定内容を確認する</t>
+          <t>オーナーだけができること</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr"/>
@@ -2642,168 +2646,144 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr"/>
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="12" t="inlineStr">
+      <c r="C159" s="4" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B154" s="12" t="inlineStr">
+      <c r="B160" s="12" t="inlineStr">
         <is>
           <t>【画像⑩】</t>
         </is>
       </c>
-      <c r="C154" s="12" t="inlineStr">
+      <c r="C160" s="12" t="inlineStr">
         <is>
           <t>役割サマリの画面</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="8" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B155" s="9" t="inlineStr">
+      <c r="B161" s="9" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
-      <c r="C155" s="8" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B156" s="15" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C156" s="15" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B157" s="15" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C157" s="15" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B158" s="15" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C158" s="15" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B159" s="15" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C159" s="15" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B160" s="15" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C160" s="15" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B161" s="15" t="inlineStr">
-        <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
-        </is>
-      </c>
-      <c r="C161" s="15" t="inlineStr">
-        <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="C161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="15" t="inlineStr">
@@ -2813,12 +2793,12 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -2830,12 +2810,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C163" s="15" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -2847,12 +2827,12 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2844,12 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C165" s="15" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2861,12 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
@@ -2898,82 +2878,184 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+        </is>
+      </c>
+      <c r="C167" s="15" t="inlineStr">
+        <is>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B168" s="15" t="inlineStr">
+        <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C168" s="15" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B169" s="15" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C169" s="15" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B170" s="15" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C170" s="15" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B171" s="15" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C171" s="15" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B172" s="15" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C172" s="15" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B173" s="15" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C167" s="15" t="inlineStr">
+      <c r="C173" s="15" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="8" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B168" s="9" t="inlineStr">
+      <c r="B174" s="9" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C168" s="8" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
+      <c r="C174" s="8" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B170" s="4" t="inlineStr">
+      <c r="B176" s="4" t="inlineStr">
         <is>
           <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
         </is>
       </c>
-      <c r="C170" s="4" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
+      <c r="C176" s="4" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
+      <c r="C177" s="4" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr"/>
+      <c r="C178" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C172"/>
+  <autoFilter ref="A2:C178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>会社ロール（権限の土台） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>店長（権限の土台） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
+          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>導入時は「会社ロール」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
+          <t>導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
         </is>
       </c>
     </row>

--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -648,30 +648,30 @@
       <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>&gt; やりたいことから、下の見出しへお進みください。</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t># ｜ 見出し ｜ こんなときにお読みください</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>1 ｜ 権限設定でできること ｜ 何ができる機能か知りたい</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>やりたいこと ｜ お読みいただく見出し</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2 ｜ ご利用の前提条件 ｜ 自分に操作できるか確かめたい</t>
+          <t>はじめて権限を設定する ｜ 導入時の初期設定</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -694,7 +694,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3 ｜ 用語の説明 ｜ 画面に出る言葉の意味を知りたい</t>
+          <t>経理担当に、売上とお支払だけ見せたい ｜ 権限を作成する</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -707,7 +707,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>4 ｜ ご利用の流れ ｜ 全体の手順を先に把握したい</t>
+          <t>人事担当に、従業員情報だけ見せたい ｜ 権限を作成する</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -720,7 +720,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>5 ｜ 導入時の初期設定 ｜ はじめて使う。まず何をすればいいか知りたい</t>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい ｜ 権限を作成する</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>6 ｜ 権限を作成する ｜ 経理担当など、新しい権限を作りたい</t>
+          <t>特定の店舗の数字だけ見せたい ｜ 担当店舗を設定する</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -746,7 +746,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>7 ｜ 作成した権限を修正する ｜ 作った権限の内容や名前を直したい</t>
+          <t>複数の店舗をまとめて見せたい ｜ 担当店舗を設定する</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>8 ｜ 権限をメンバーに割り当てる ｜ 作った権限を実際に人へ適用したい</t>
+          <t>新しく入った方に権限を与えたい ｜ 権限をメンバーに割り当てる</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>9 ｜ 担当店舗を設定する ｜ 特定の店舗の数字だけを見せたい</t>
+          <t>大勢にまとめて権限を与えたい ｜ 権限をメンバーに割り当てる</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -785,7 +785,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>10 ｜ 権限を変更・解除する ｜ 異動・退職で権限を付け替えたい／外したい</t>
+          <t>異動した方の権限を付け替えたい ｜ 権限を変更・解除する</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -798,7 +798,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>11 ｜ 表示する数字を選ぶ ｜ 売上や原価など、見せる数字を絞りたい</t>
+          <t>退職した方の権限を外したい ｜ 権限を変更・解除する</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -811,7 +811,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>12 ｜ オーナーだけができること ｜ 全権の委譲、すべての数字の確認をしたい</t>
+          <t>作った権限の内容や名前を直したい ｜ 作成した権限を修正する</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>13 ｜ 設定内容を確認する ｜ 設定した内容を一覧で見直したい</t>
+          <t>見せる数字（売上・原価など）を絞りたい ｜ 表示する数字を選ぶ</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -837,49 +837,49 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>14 ｜ よくあるご質問 ｜ 困りごとの答えを探したい</t>
+          <t>誰がどの権限を持っているか確認したい ｜ 設定内容を確認する</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>権限設定でできること</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>全権を別の方に譲りたい ｜ オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>貴社の体制に合わせて、メンバーごとに見える範囲を変えられます。</t>
+          <t>会社と店舗の両方の画面を使わせたい ｜ よくあるご質問</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>こんなときに ｜ 設定例</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>設定を誤って画面が開けなくなった ｜ よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -889,105 +889,101 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>経理担当に売上や支払は見せたいが、従業員情報は見せたくない ｜ 分析画面と支払を「閲覧」、従業員管理を「なし」</t>
+          <t>兼務する方の権限をどうするか決めたい ｜ よくあるご質問</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>人事担当に従業員情報だけ見せたい ｜ 従業員関連を「閲覧」、売上系を「なし」</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ページの構成</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに売上画面だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
+          <t>権限設定でできること ／ ご利用の前提条件 ／ 用語の説明 ／ ご利用の流れ ／ 導入時の初期設定 ／ 権限を作成する ／ 作成した権限を修正する ／ 権限をメンバーに割り当てる ／ 担当店舗を設定する ／ 権限を変更・解除する ／ 表示する数字を選ぶ ／ オーナーだけができること ／ 設定内容を確認する ／ よくあるご質問 ／ 参照リンク</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>新入社員にはまず最小限から始めたい ｜ ダッシュボード以外を「なし」</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr"/>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>権限設定でできること</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 今回のリリースでできること</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
-        </is>
-      </c>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>貴社の体制に合わせて、メンバーごとに見える範囲を変えられます。</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>ご利用の前提条件</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr"/>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>こんなときに ｜ 設定例</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>&gt; この画面で何ができるかは、ご自身の権限によって変わります。</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>経理担当に売上や支払は見せたいが、従業員情報は見せたくない ｜ 分析画面と支払を「閲覧」、従業員管理を「なし」</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ｜ オーナー ｜ 本部管理者</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>人事担当に従業員情報だけ見せたい ｜ 従業員関連を「閲覧」、売上系を「なし」</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -997,7 +993,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>権限を作る・直す ｜ できる ｜ できる</t>
+          <t>アルバイトリーダーに売上画面だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1010,62 +1006,66 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>メンバーに割り当てる ｜ できる ｜ できる</t>
+          <t>新入社員にはまず最小限から始めたい ｜ ダッシュボード以外を「なし」</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する ｜ できる ｜ できる</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr"/>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 今回のリリースでできること</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ ｜ できる ｜ できる</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>ご利用の前提条件</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>すべての数字を確認する ｜ できる ｜ できない</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr"/>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>&gt; この画面で何ができるかは、ご自身の権限によって変わります。</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>全権を他の方に委ねる ｜ できる ｜ できない</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr"/>
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ｜ オーナー ｜ 本部管理者</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>オーナーの権限を変更する ｜ できない（全権で固定） ｜ できない</t>
+          <t>権限を作る・直す ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1083,12 +1083,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>・操作できるのはオーナーと本部管理者のみです。</t>
+          <t>メンバーに割り当てる ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -1096,12 +1096,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
+          <t>担当店舗を設定する ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -1109,12 +1109,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
+          <t>表示する数字を選ぶ ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -1122,64 +1122,64 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>・権限は会社／店舗の区分で分かれます。区分によって設定できる画面が変わります。</t>
+          <t>すべての数字を確認する ｜ できる ｜ できない</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="inlineStr">
-        <is>
-          <t>用語の説明</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>全権を他の方に委ねる ｜ できる ｜ できない</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>画面に出てくる言葉です。読み進めていて分からない言葉が出たら、ここに戻ってきてください。</t>
+          <t>オーナーの権限を変更する ｜ できない（全権で固定） ｜ できない</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>用語 ｜ 意味</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>・操作できるのはオーナーと本部管理者のみです。</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
+          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
+          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -1200,64 +1200,64 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
+          <t>・権限は会社／店舗の区分で分かれます。区分によって設定できる画面が変わります。</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>用語の説明</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
+          <t>画面に出てくる言葉です。読み進めていて分からない言葉が出たら、ここに戻ってきてください。</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr"/>
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>用語 ｜ 意味</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>権限と担当店舗は別々に設定します。 同じ「エリアマネージャー」でも、Aさんは2店舗、Bさんは3店舗というように担当が異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
+          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -1265,54 +1265,54 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t>ご利用の流れ</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr"/>
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
+          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>画面 ｜ ここで何をするか</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr"/>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>権限設定 ｜ 権限を作る・直す</t>
+          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -1330,12 +1330,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
+          <t>権限と担当店舗は別々に設定します。 同じ「エリアマネージャー」でも、Aさんは2店舗、Bさんは3店舗というように担当が異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -1343,32 +1343,28 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
+          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
-        </is>
-      </c>
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>ご利用の流れ</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -1378,33 +1374,33 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
+          <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>1. 初期設定で権限を用意する — おすすめの権限をまとめて登録します。</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>画面 ｜ ここで何をするか</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>2. 足りない権限を作る — 貴社に合わせた権限を追加します。</t>
+          <t>権限設定 ｜ 権限を作る・直す</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -1412,12 +1408,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>3. メンバーに割り当てる — 誰にどの権限を付けるかを決めます。</t>
+          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -1425,51 +1421,55 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>4. 担当店舗を設定する — 店舗の権限を付けた方に、担当店舗を紐付けます。</t>
+          <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>5. 権限一覧で確認する — 誰が何の権限を持っているかを確認します。</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>導入時の初期設定</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr"/>
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
+          <t>1. 初期設定で権限を用意する — おすすめの権限をまとめて登録します。</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -1482,33 +1482,33 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>1. 用意する権限を選びます（初期状態ではすべて選択されています）。</t>
+          <t>2. 足りない権限を作る — 貴社に合わせた権限を追加します。</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>権限 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr"/>
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>3. メンバーに割り当てる — 誰にどの権限を付けるかを決めます。</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
+          <t>4. 担当店舗を設定する — 店舗の権限を付けた方に、担当店舗を紐付けます。</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -1516,38 +1516,38 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+          <t>5. 権限一覧で確認する — 誰が何の権限を持っているかを確認します。</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr"/>
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>導入時の初期設定</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -1560,203 +1560,195 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
+          <t>1. 用意する権限を選びます（初期状態ではすべて選択されています）。</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>権限 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>従業員 ｜ 閲覧が中心です</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
           <t>2. それぞれの初期値を選びます（推奨／操作可／閲覧のみ／なし）。</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>3. 「適用」を選択すると、権限一覧に登録された状態になります。</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="12" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>【画像①】</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C85" s="12" t="inlineStr">
         <is>
           <t>権限テンプレートの画面</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>&gt; 途中で中断できます</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>「一時保存」を選択すると、選んだ内容が保存されます。別の画面に移動しても、次に開いたときに続きから設定できます。</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>&gt; やり直したいとき</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>「下書きを破棄」を選択すると、保存した内容が消えて初期状態に戻ります。</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>&gt; 次に読む — 登録した権限をそのまま使う場合は「権限をメンバーに割り当てる」へ。内容を変えたい場合は下の「権限を作成する」へお進みください。</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>権限を作成する</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>STEP 1　権限設定画面を開く</t>
-        </is>
-      </c>
-      <c r="C85" s="13" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>【画像②】</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t>権限設定の一覧画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>&gt; スコープによって表示が変わります</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
-        </is>
-      </c>
+      <c r="C90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
@@ -1766,7 +1758,7 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>STEP 2　雛形を選ぶ</t>
+          <t>STEP 1　権限設定画面を開く</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr"/>
@@ -1779,7 +1771,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -1792,72 +1784,80 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>雛形 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr"/>
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr"/>
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>【画像②】</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>権限設定の一覧画面</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr"/>
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>&gt; スコープによって表示が変わります</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr"/>
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>STEP 2　雛形を選ぶ</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>1. 「＋ 権限を新規作成」を選択します。</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -1865,89 +1865,77 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
+          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>【画像③】</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>雛形（ベース）の選択画面</t>
-        </is>
-      </c>
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>雛形 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ゼロから設定する必要はありません</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
-        </is>
-      </c>
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>&gt; エリアマネージャーのような役割は「店長」から作ります</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>雛形にはありませんが、店長を雛形に選んで権限名を「エリアマネージャー」に変え、担当店舗を複数紐付ければ作れます。組織によって権限の中身が変わるため、雛形としては用意していません。</t>
-        </is>
-      </c>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>STEP 3　権限名と区分を決める</t>
-        </is>
-      </c>
-      <c r="C103" s="13" t="inlineStr"/>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>従業員 ｜ 閲覧が中心です</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -1955,127 +1943,131 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>【画像③】</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>雛形（ベース）の選択画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ゼロから設定する必要はありません</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>&gt; エリアマネージャーのような役割は「店長」から作ります</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>雛形にはありませんが、店長を雛形に選んで権限名を「エリアマネージャー」に変え、担当店舗を複数紐付ければ作れます。組織によって権限の中身が変わるため、雛形としては用意していません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>2. 区分を選びます。</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B112" s="9" t="inlineStr">
         <is>
           <t>区分 ｜ 設定できる画面</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>会社 ｜ 共通の画面＋会社画面（会社情報・お支払い・店舗管理・ダウンロード）</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>店舗 ｜ 共通の画面＋店舗画面（発注先&amp;仕入商品・店舗情報・連携設定・費用設定・休業日設定・予算設定）</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B111" s="14" t="inlineStr">
-        <is>
-          <t>STEP 4　画面ごとに設定する</t>
-        </is>
-      </c>
-      <c r="C111" s="13" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>画面ごとに「操作」「閲覧」「なし」を選びます。</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>設定 ｜ できること</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr"/>
+      <c r="C113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -2085,53 +2077,57 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
+          <t>店舗 ｜ 共通の画面＋店舗画面（発注先&amp;仕入商品・店舗情報・連携設定・費用設定・休業日設定・予算設定）</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>閲覧 ｜ 画面を開けます</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr"/>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>なし ｜ 画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr"/>
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 「閲覧」と「操作」の違いについて</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
-        </is>
-      </c>
+      <c r="A117" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>STEP 4　画面ごとに設定する</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -2141,83 +2137,79 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
+          <t>画面ごとに「操作」「閲覧」「なし」を選びます。</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B119" s="12" t="inlineStr">
-        <is>
-          <t>【画像④】</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>画面ごとの設定（操作／閲覧／なし）</t>
-        </is>
-      </c>
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>設定 ｜ できること</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>&gt; さらに細かく設定するには</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
-        </is>
-      </c>
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>3. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
+          <t>閲覧 ｜ 画面を開けます</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>なし ｜ 画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 次に読む — 作成した権限は、メンバーに割り当てて初めて有効になります。このまま読み進めず、「8. 権限をメンバーに割り当てる」まで下にお進みください。 次の「作成した権限を修正する」は、あとから内容を直したくなったときにお読みください。</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="inlineStr">
-        <is>
-          <t>作成した権限を修正する</t>
-        </is>
-      </c>
-      <c r="C123" s="10" t="inlineStr"/>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 「閲覧」と「操作」の違いについて</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -2227,166 +2219,158 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr"/>
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>【画像④】</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>画面ごとの設定（操作／閲覧／なし）</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr"/>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>&gt; さらに細かく設定するには</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
+          <t>3. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 次に読む — 作成した権限は、メンバーに割り当てて初めて有効になります。このまま読み進めず、「権限をメンバーに割り当てる」まで下にお進みください。 次の「作成した権限を修正する」は、あとから内容を直したくなったときにお読みください。</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
           <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑤】</t>
-        </is>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 割当の画面からも権限を新規作成できます</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選択できます。作成後は元の割当編集の画面に戻ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>権限をメンバーに割り当てる</t>
-        </is>
-      </c>
-      <c r="C134" s="10" t="inlineStr"/>
+      <c r="C134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 経営管理画面 右上のアカウントメニュー →「権限設定」</t>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr"/>
@@ -2399,139 +2383,143 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
+          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑤】</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>マス目を選択して該当箇所へ移動したところ</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>&gt; マス目を選択すると該当箇所が開きます</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 割当の画面からも権限を新規作成できます</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選択できます。作成後は元の割当編集の画面に戻ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B141" s="11" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>開く場所 — 経営管理画面 右上のアカウントメニュー →「権限設定」</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
           <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="13" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B137" s="14" t="inlineStr">
+      <c r="B144" s="14" t="inlineStr">
         <is>
           <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
         </is>
       </c>
-      <c r="C137" s="13" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="C144" s="13" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
-        </is>
-      </c>
-      <c r="C139" s="4" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B142" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑥】</t>
-        </is>
-      </c>
-      <c r="C142" s="12" t="inlineStr">
-        <is>
-          <t>まとめて割り当てる画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>&gt; すでに別の権限をお持ちの方</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 対象の絞り込み</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="13" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B145" s="14" t="inlineStr">
-        <is>
-          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
-        </is>
-      </c>
-      <c r="C145" s="13" t="inlineStr"/>
+      <c r="C145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -2541,7 +2529,7 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
+          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr"/>
@@ -2554,7 +2542,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr"/>
@@ -2567,66 +2555,74 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>3. 権限を1つ選びます。</t>
+          <t>4. 「保存」を選択します。</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr"/>
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B149" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑥】</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>まとめて割り当てる画面</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B150" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>メンバーごとの割当編集画面</t>
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>&gt; すでに別の権限をお持ちの方</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="13" t="inlineStr">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 対象の絞り込み</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B151" s="14" t="inlineStr">
-        <is>
-          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
-        </is>
-      </c>
-      <c r="C151" s="13" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr"/>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
+        </is>
+      </c>
+      <c r="C152" s="13" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -2636,7 +2632,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の権限の「割当へ →」を選択します。</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr"/>
@@ -2649,72 +2645,76 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
+          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 次に読む — 店舗の権限を割り当てた方には、担当店舗の設定が必要です。「担当店舗を設定する」へお進みください。</t>
-        </is>
-      </c>
-      <c r="C155" s="5" t="inlineStr"/>
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>3. 権限を1つ選びます。</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B156" s="11" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C156" s="10" t="inlineStr"/>
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択します。</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>開く場所 — 権限設定 →「👥 ユーザー割当」タブ → 対象の方の行の「編集」</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr"/>
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>メンバーごとの割当編集画面</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr"/>
+      <c r="A158" s="13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+        </is>
+      </c>
+      <c r="C158" s="13" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
+          <t>2. 対象の権限の「割当へ →」を選択します。</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr"/>
@@ -2740,70 +2740,62 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr"/>
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 次に読む — 店舗の権限を割り当てた方には、担当店舗の設定が必要です。「担当店舗を設定する」へお進みください。</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr"/>
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B164" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑧】</t>
-        </is>
-      </c>
-      <c r="C164" s="12" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面</t>
-        </is>
-      </c>
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>開く場所 — 権限設定 →「👥 ユーザー割当」タブ → 対象の方の行の「編集」</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
-        </is>
-      </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -2813,79 +2805,79 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗の反映について</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 次に読む — ここまでで設定は完了です。あとから付け替えるときは、このまま下の「権限を変更・解除する」をご覧ください。</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="inlineStr"/>
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C169" s="10" t="inlineStr"/>
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定 →「👥 ユーザー割当」タブ → 対象の方の行の「編集」</t>
+          <t>4. 「保存」を選択します。</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr"/>
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B171" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -2895,10 +2887,14 @@
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>&gt; 別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="inlineStr"/>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -2908,7 +2904,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
+          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
@@ -2921,53 +2917,53 @@
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>&gt; 権限を外す</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr"/>
+          <t>&gt; 担当店舗の反映について</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 次に読む — ここまでで設定は完了です。あとから付け替えるときは、このまま下の「権限を変更・解除する」をご覧ください。</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B177" s="11" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ</t>
-        </is>
-      </c>
-      <c r="C177" s="10" t="inlineStr"/>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>開く場所 — 権限設定 →「👥 ユーザー割当」タブ → 対象の方の行の「編集」</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -2977,7 +2973,7 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr"/>
@@ -2990,104 +2986,92 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>&gt; 設定の反映について</t>
-        </is>
-      </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
-        </is>
-      </c>
+          <t>&gt; 別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr"/>
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限を外す</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B183" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C183" s="12" t="inlineStr">
-        <is>
-          <t>指標一覧の画面</t>
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 初期値は自動で設定されます</t>
-        </is>
-      </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
-        </is>
-      </c>
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 項目が多い場合は「指標条件設定」が便利です</t>
-        </is>
-      </c>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
-        </is>
-      </c>
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -3097,118 +3081,134 @@
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>&gt; 作った組み合わせは保存して使い回せます</t>
+          <t>&gt; 設定の反映について</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr"/>
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B189" s="9" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C189" s="8" t="inlineStr"/>
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr"/>
+      <c r="A190" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B190" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑨】</t>
+        </is>
+      </c>
+      <c r="C190" s="12" t="inlineStr">
+        <is>
+          <t>指標一覧の画面</t>
+        </is>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr"/>
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 初期値は自動で設定されます</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr"/>
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 項目が多い場合は「指標条件設定」が便利です</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
+        </is>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="10" t="inlineStr">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 作った組み合わせは保存して使い回せます</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B193" s="11" t="inlineStr">
-        <is>
-          <t>設定内容を確認する</t>
-        </is>
-      </c>
-      <c r="C193" s="10" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr"/>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t>オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -3218,53 +3218,49 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr"/>
+      <c r="A196" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="12" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B197" s="12" t="inlineStr">
-        <is>
-          <t>【画像⑩】</t>
-        </is>
-      </c>
-      <c r="C197" s="12" t="inlineStr">
-        <is>
-          <t>役割サマリの画面</t>
-        </is>
-      </c>
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B198" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C198" s="10" t="inlineStr"/>
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -3274,129 +3270,105 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B204" s="12" t="inlineStr">
+        <is>
+          <t>【画像⑩】</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
+          <t>役割サマリの画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B205" s="11" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C205" s="10" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
           <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B200" s="15" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C200" s="15" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B201" s="15" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C201" s="15" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B202" s="15" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C202" s="15" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B203" s="15" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C203" s="15" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B204" s="15" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C204" s="15" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B205" s="15" t="inlineStr">
-        <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
-        </is>
-      </c>
-      <c r="C205" s="15" t="inlineStr">
-        <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="15" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B206" s="15" t="inlineStr">
-        <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
-        </is>
-      </c>
-      <c r="C206" s="15" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="C206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="15" t="inlineStr">
@@ -3406,12 +3378,12 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C207" s="15" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -3423,12 +3395,12 @@
       </c>
       <c r="B208" s="15" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -3440,12 +3412,12 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C209" s="15" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3429,12 @@
       </c>
       <c r="B210" s="15" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C210" s="15" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -3474,82 +3446,201 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
+        </is>
+      </c>
+      <c r="C211" s="15" t="inlineStr">
+        <is>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B212" s="15" t="inlineStr">
+        <is>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+        </is>
+      </c>
+      <c r="C212" s="15" t="inlineStr">
+        <is>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B213" s="15" t="inlineStr">
+        <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C213" s="15" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B214" s="15" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C214" s="15" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B215" s="15" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C215" s="15" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B216" s="15" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C216" s="15" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B217" s="15" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C217" s="15" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B218" s="15" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C211" s="15" t="inlineStr">
+      <c r="C218" s="15" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="10" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B212" s="11" t="inlineStr">
+      <c r="B219" s="11" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C212" s="10" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
+      <c r="C219" s="10" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B214" s="4" t="inlineStr">
+      <c r="B221" s="4" t="inlineStr">
         <is>
           <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
         </is>
       </c>
-      <c r="C214" s="4" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B215" s="4" t="inlineStr">
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
         </is>
       </c>
-      <c r="C215" s="4" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B216" s="4" t="inlineStr">
+      <c r="B223" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C216" s="4" t="inlineStr"/>
+      <c r="C223" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C216"/>
+  <autoFilter ref="A2:C223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,10 +59,15 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E5F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E5F"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -81,12 +86,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F5F7F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDF3F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E7EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,16 +167,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +186,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -614,30 +638,30 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 目次｜やりたいことからお探しください</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>目次</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>目次｜やりたいことからお探しください</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>やりたいこと ｜ お読みいただく見出し</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -861,17 +885,17 @@
       <c r="C24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>権限設定でできること</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr"/>
+      <c r="C25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -887,17 +911,17 @@
       <c r="C26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>こんなときに ｜ 設定例</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -969,43 +993,43 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>ご利用の前提条件</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr"/>
+      <c r="C33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>&gt; この画面で何ができるかは、ご自身の権限によって変わります。</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>この画面で何ができるかは、ご自身の権限によって変わります。</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve"> ｜ オーナー ｜ 本部管理者</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -1151,17 +1175,17 @@
       <c r="C46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>用語の説明</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr"/>
+      <c r="C47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -1177,17 +1201,17 @@
       <c r="C48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>用語 ｜ 意味</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr"/>
+      <c r="C49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1333,17 +1357,17 @@
       <c r="C60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="9" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>ご利用の流れ</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr"/>
+      <c r="C61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -1359,17 +1383,17 @@
       <c r="C62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>画面 ｜ ここで何をするか</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr"/>
+      <c r="C63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -1506,17 +1530,17 @@
       <c r="C73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>導入時の初期設定</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr"/>
+      <c r="C74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -1558,17 +1582,17 @@
       <c r="C77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>権限 ｜ 内容</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr"/>
+      <c r="C78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -1636,17 +1660,17 @@
       <c r="C83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="inlineStr">
+      <c r="A84" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>【画像①】</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>権限テンプレートの画面</t>
         </is>
@@ -1687,30 +1711,30 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>権限を作成する</t>
         </is>
       </c>
-      <c r="C87" s="9" t="inlineStr"/>
+      <c r="C87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="12" t="inlineStr">
+      <c r="A88" s="15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>STEP 1　権限設定画面を開く</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr"/>
+      <c r="C88" s="15" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -1752,17 +1776,17 @@
       <c r="C91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="inlineStr">
+      <c r="A92" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>【画像②】</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>権限設定の一覧画面</t>
         </is>
@@ -1786,17 +1810,17 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="A94" s="15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B94" s="13" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>STEP 2　雛形を選ぶ</t>
         </is>
       </c>
-      <c r="C94" s="12" t="inlineStr"/>
+      <c r="C94" s="15" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -1825,17 +1849,17 @@
       <c r="C96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
         <is>
           <t>雛形 ｜ 内容</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
+      <c r="C97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -1903,17 +1927,17 @@
       <c r="C102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="inlineStr">
+      <c r="A103" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
+      <c r="B103" s="14" t="inlineStr">
         <is>
           <t>【画像③】</t>
         </is>
       </c>
-      <c r="C103" s="11" t="inlineStr">
+      <c r="C103" s="14" t="inlineStr">
         <is>
           <t>雛形（ベース）の選択画面</t>
         </is>
@@ -1937,17 +1961,17 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="12" t="inlineStr">
+      <c r="A105" s="15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B105" s="13" t="inlineStr">
+      <c r="B105" s="16" t="inlineStr">
         <is>
           <t>STEP 3　権限名と区分を決める</t>
         </is>
       </c>
-      <c r="C105" s="12" t="inlineStr"/>
+      <c r="C105" s="15" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -1976,17 +2000,17 @@
       <c r="C107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B108" s="9" t="inlineStr">
         <is>
           <t>区分 ｜ 設定できる画面</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr"/>
+      <c r="C108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -2049,17 +2073,17 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="12" t="inlineStr">
+      <c r="A113" s="15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B113" s="13" t="inlineStr">
+      <c r="B113" s="16" t="inlineStr">
         <is>
           <t>STEP 4　画面ごとに設定して保存する</t>
         </is>
       </c>
-      <c r="C113" s="12" t="inlineStr"/>
+      <c r="C113" s="15" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -2075,17 +2099,17 @@
       <c r="C114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>設定 ｜ できること</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr"/>
+      <c r="C115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -2157,17 +2181,17 @@
       <c r="C120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="inlineStr">
+      <c r="A121" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B121" s="11" t="inlineStr">
+      <c r="B121" s="14" t="inlineStr">
         <is>
           <t>【画像④】</t>
         </is>
       </c>
-      <c r="C121" s="11" t="inlineStr">
+      <c r="C121" s="14" t="inlineStr">
         <is>
           <t>画面ごとの設定（操作／閲覧／なし）</t>
         </is>
@@ -2204,17 +2228,17 @@
       <c r="C123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる</t>
         </is>
       </c>
-      <c r="C124" s="9" t="inlineStr"/>
+      <c r="C124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -2230,17 +2254,17 @@
       <c r="C125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="12" t="inlineStr">
+      <c r="A126" s="15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B126" s="13" t="inlineStr">
+      <c r="B126" s="16" t="inlineStr">
         <is>
           <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
         </is>
       </c>
-      <c r="C126" s="12" t="inlineStr"/>
+      <c r="C126" s="15" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -2295,17 +2319,17 @@
       <c r="C130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="11" t="inlineStr">
+      <c r="A131" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B131" s="14" t="inlineStr">
         <is>
           <t>【画像⑥】</t>
         </is>
       </c>
-      <c r="C131" s="11" t="inlineStr">
+      <c r="C131" s="14" t="inlineStr">
         <is>
           <t>まとめて割り当てる画面</t>
         </is>
@@ -2346,17 +2370,17 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="12" t="inlineStr">
+      <c r="A134" s="15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B134" s="13" t="inlineStr">
+      <c r="B134" s="16" t="inlineStr">
         <is>
           <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
         </is>
       </c>
-      <c r="C134" s="12" t="inlineStr"/>
+      <c r="C134" s="15" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -2411,34 +2435,34 @@
       <c r="C138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="11" t="inlineStr">
+      <c r="A139" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B139" s="11" t="inlineStr">
+      <c r="B139" s="14" t="inlineStr">
         <is>
           <t>【画像⑦】</t>
         </is>
       </c>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="C139" s="14" t="inlineStr">
         <is>
           <t>メンバーごとの割当編集画面</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="12" t="inlineStr">
+      <c r="A140" s="15" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B140" s="13" t="inlineStr">
+      <c r="B140" s="16" t="inlineStr">
         <is>
           <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
         </is>
       </c>
-      <c r="C140" s="12" t="inlineStr"/>
+      <c r="C140" s="15" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -2480,17 +2504,17 @@
       <c r="C143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="9" t="inlineStr">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B144" s="10" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>担当店舗を設定する</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr"/>
+      <c r="C144" s="10" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -2584,17 +2608,17 @@
       <c r="C151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="11" t="inlineStr">
+      <c r="A152" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B152" s="11" t="inlineStr">
+      <c r="B152" s="14" t="inlineStr">
         <is>
           <t>【画像⑧】</t>
         </is>
       </c>
-      <c r="C152" s="11" t="inlineStr">
+      <c r="C152" s="14" t="inlineStr">
         <is>
           <t>担当店舗の選択画面</t>
         </is>
@@ -2661,17 +2685,17 @@
       <c r="C156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="9" t="inlineStr">
+      <c r="A157" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B157" s="10" t="inlineStr">
+      <c r="B157" s="11" t="inlineStr">
         <is>
           <t>表示する数字を選ぶ</t>
         </is>
       </c>
-      <c r="C157" s="9" t="inlineStr"/>
+      <c r="C157" s="10" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -2743,17 +2767,17 @@
       <c r="C162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="11" t="inlineStr">
+      <c r="A163" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B163" s="11" t="inlineStr">
+      <c r="B163" s="14" t="inlineStr">
         <is>
           <t>【画像⑨】</t>
         </is>
       </c>
-      <c r="C163" s="11" t="inlineStr">
+      <c r="C163" s="14" t="inlineStr">
         <is>
           <t>指標一覧の画面</t>
         </is>
@@ -2803,17 +2827,17 @@
       <c r="C166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
+      <c r="A167" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B167" s="10" t="inlineStr">
+      <c r="B167" s="11" t="inlineStr">
         <is>
           <t>作成した権限を修正する</t>
         </is>
       </c>
-      <c r="C167" s="9" t="inlineStr"/>
+      <c r="C167" s="10" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -2829,17 +2853,17 @@
       <c r="C168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="inlineStr">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B169" s="9" t="inlineStr">
         <is>
           <t>入口 ｜ 操作 ｜ こんなときに</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr"/>
+      <c r="C169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -2907,17 +2931,17 @@
       <c r="C174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="11" t="inlineStr">
+      <c r="A175" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B175" s="11" t="inlineStr">
+      <c r="B175" s="14" t="inlineStr">
         <is>
           <t>【画像⑤】</t>
         </is>
       </c>
-      <c r="C175" s="11" t="inlineStr">
+      <c r="C175" s="14" t="inlineStr">
         <is>
           <t>マス目を選択して該当箇所へ移動したところ</t>
         </is>
@@ -2971,17 +2995,17 @@
       <c r="C178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="9" t="inlineStr">
+      <c r="A179" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B179" s="10" t="inlineStr">
+      <c r="B179" s="11" t="inlineStr">
         <is>
           <t>権限を変更・解除する</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr"/>
+      <c r="C179" s="10" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -3010,17 +3034,17 @@
       <c r="C181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C182" s="5" t="inlineStr"/>
+      <c r="A182" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -3036,17 +3060,17 @@
       <c r="C183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限を外す</t>
-        </is>
-      </c>
-      <c r="C184" s="5" t="inlineStr"/>
+      <c r="A184" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B184" s="13" t="inlineStr">
+        <is>
+          <t>権限を外す</t>
+        </is>
+      </c>
+      <c r="C184" s="12" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -3079,17 +3103,17 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="9" t="inlineStr">
+      <c r="A187" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B187" s="10" t="inlineStr">
+      <c r="B187" s="11" t="inlineStr">
         <is>
           <t>オーナーだけができること</t>
         </is>
       </c>
-      <c r="C187" s="9" t="inlineStr"/>
+      <c r="C187" s="10" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -3105,17 +3129,17 @@
       <c r="C188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="7" t="inlineStr">
+      <c r="A189" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B189" s="8" t="inlineStr">
+      <c r="B189" s="9" t="inlineStr">
         <is>
           <t>操作 ｜ 内容</t>
         </is>
       </c>
-      <c r="C189" s="7" t="inlineStr"/>
+      <c r="C189" s="8" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -3157,17 +3181,17 @@
       <c r="C192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="9" t="inlineStr">
+      <c r="A193" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B193" s="10" t="inlineStr">
+      <c r="B193" s="11" t="inlineStr">
         <is>
           <t>設定内容を確認する</t>
         </is>
       </c>
-      <c r="C193" s="9" t="inlineStr"/>
+      <c r="C193" s="10" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -3209,34 +3233,34 @@
       <c r="C196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="11" t="inlineStr">
+      <c r="A197" s="14" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B197" s="11" t="inlineStr">
+      <c r="B197" s="14" t="inlineStr">
         <is>
           <t>【画像⑩】</t>
         </is>
       </c>
-      <c r="C197" s="11" t="inlineStr">
+      <c r="C197" s="14" t="inlineStr">
         <is>
           <t>役割サマリの画面</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="9" t="inlineStr">
+      <c r="A198" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B198" s="10" t="inlineStr">
+      <c r="B198" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
-      <c r="C198" s="9" t="inlineStr"/>
+      <c r="C198" s="10" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -3252,221 +3276,221 @@
       <c r="C199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="14" t="inlineStr">
+      <c r="A200" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B200" s="14" t="inlineStr">
+      <c r="B200" s="17" t="inlineStr">
         <is>
           <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
-      <c r="C200" s="14" t="inlineStr">
+      <c r="C200" s="17" t="inlineStr">
         <is>
           <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="14" t="inlineStr">
+      <c r="A201" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B201" s="14" t="inlineStr">
+      <c r="B201" s="17" t="inlineStr">
         <is>
           <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
-      <c r="C201" s="14" t="inlineStr">
+      <c r="C201" s="17" t="inlineStr">
         <is>
           <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="14" t="inlineStr">
+      <c r="A202" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B202" s="14" t="inlineStr">
+      <c r="B202" s="17" t="inlineStr">
         <is>
           <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
-      <c r="C202" s="14" t="inlineStr">
+      <c r="C202" s="17" t="inlineStr">
         <is>
           <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="14" t="inlineStr">
+      <c r="A203" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B203" s="14" t="inlineStr">
+      <c r="B203" s="17" t="inlineStr">
         <is>
           <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
-      <c r="C203" s="14" t="inlineStr">
+      <c r="C203" s="17" t="inlineStr">
         <is>
           <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="14" t="inlineStr">
+      <c r="A204" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B204" s="14" t="inlineStr">
+      <c r="B204" s="17" t="inlineStr">
         <is>
           <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
-      <c r="C204" s="14" t="inlineStr">
+      <c r="C204" s="17" t="inlineStr">
         <is>
           <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="14" t="inlineStr">
+      <c r="A205" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B205" s="14" t="inlineStr">
+      <c r="B205" s="17" t="inlineStr">
         <is>
           <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
         </is>
       </c>
-      <c r="C205" s="14" t="inlineStr">
+      <c r="C205" s="17" t="inlineStr">
         <is>
           <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="14" t="inlineStr">
+      <c r="A206" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B206" s="14" t="inlineStr">
+      <c r="B206" s="17" t="inlineStr">
         <is>
           <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
         </is>
       </c>
-      <c r="C206" s="14" t="inlineStr">
+      <c r="C206" s="17" t="inlineStr">
         <is>
           <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="14" t="inlineStr">
+      <c r="A207" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B207" s="14" t="inlineStr">
+      <c r="B207" s="17" t="inlineStr">
         <is>
           <t>Q. 役職を変更すると権限も変わりますか？</t>
         </is>
       </c>
-      <c r="C207" s="14" t="inlineStr">
+      <c r="C207" s="17" t="inlineStr">
         <is>
           <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="14" t="inlineStr">
+      <c r="A208" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B208" s="14" t="inlineStr">
+      <c r="B208" s="17" t="inlineStr">
         <is>
           <t>Q. 自分の権限を変更できますか？</t>
         </is>
       </c>
-      <c r="C208" s="14" t="inlineStr">
+      <c r="C208" s="17" t="inlineStr">
         <is>
           <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="14" t="inlineStr">
+      <c r="A209" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B209" s="14" t="inlineStr">
+      <c r="B209" s="17" t="inlineStr">
         <is>
           <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
         </is>
       </c>
-      <c r="C209" s="14" t="inlineStr">
+      <c r="C209" s="17" t="inlineStr">
         <is>
           <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="14" t="inlineStr">
+      <c r="A210" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B210" s="14" t="inlineStr">
+      <c r="B210" s="17" t="inlineStr">
         <is>
           <t>Q. 権限が未設定の方はどうなりますか？</t>
         </is>
       </c>
-      <c r="C210" s="14" t="inlineStr">
+      <c r="C210" s="17" t="inlineStr">
         <is>
           <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="14" t="inlineStr">
+      <c r="A211" s="17" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B211" s="14" t="inlineStr">
+      <c r="B211" s="17" t="inlineStr">
         <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C211" s="14" t="inlineStr">
+      <c r="C211" s="17" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="9" t="inlineStr">
+      <c r="A212" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B212" s="10" t="inlineStr">
+      <c r="B212" s="11" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C212" s="9" t="inlineStr"/>
+      <c r="C212" s="10" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">

--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -67,7 +67,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -102,6 +102,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6F2F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -146,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,10 +196,13 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -562,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C216"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1338,75 +1346,79 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>権限と担当店舗は別々に設定します。 同じ「エリアマネージャー」でも、Aさんは2店舗、Bさんは3店舗というように担当が異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
+          <t>権限と担当店舗は別々に設定します。 同じ権限でも、担当する店舗は人によって異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>【図2】</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>権限と担当店舗の関係（help/figures/ のSVGを掲載）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>ご利用の流れ</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>画面 ｜ ここで何をするか</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>権限設定 ｜ 権限を作る・直す</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
+      <c r="C64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -1416,7 +1428,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
+          <t>権限設定 ｜ 権限を作る・直す</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -1429,89 +1441,93 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
+          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>1. 初期設定で権限を用意する — おすすめの権限をまとめて登録します。</t>
+          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>2. 足りない権限を作る — 貴社に合わせた権限を追加します。</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr"/>
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>【図1】</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>ご利用の流れ（help/figures/ のSVGを掲載）</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>3. メンバーに割り当てる — 誰にどの権限を付けるかを決めます。</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr"/>
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>導入時の初期設定</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>4. 担当店舗を設定する — 店舗の権限を付けた方に、担当店舗を紐付けます。</t>
+          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -1519,51 +1535,51 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>5. 権限一覧で確認する — 誰が何の権限を持っているかを確認します。</t>
+          <t>手順 — ①用意する権限を選ぶ → ②それぞれの初期値を選ぶ（推奨／操作可／閲覧のみ／なし）→ ③「適用」を選択する</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t>導入時の初期設定</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr"/>
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>登録できる権限は次の4つです。初期状態ではすべて選択されています。</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr"/>
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>権限 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>手順 — ①用意する権限を選ぶ → ②それぞれの初期値を選ぶ（推奨／操作可／閲覧のみ／なし）→ ③「適用」を選択する</t>
+          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -1571,28 +1587,28 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>登録できる権限は次の4つです。初期状態ではすべて選択されています。</t>
+          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>権限 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr"/>
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -1602,7 +1618,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
+          <t>従業員 ｜ 閲覧が中心です</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -1610,227 +1626,227 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+          <t>「適用」を選択すると、権限一覧に登録された状態になります。</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr"/>
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>【画像①】</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>権限テンプレートの画面</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr"/>
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 途中で中断できます／やり直せます</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>「適用」を選択すると、権限一覧に登録された状態になります。</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr"/>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="14" t="inlineStr">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>権限を作成する</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>STEP 1　権限設定画面を開く</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>【画像①】</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr">
-        <is>
-          <t>権限テンプレートの画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>【画像②】</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>権限設定の一覧画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 途中で中断できます／やり直せます</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>権限を作成する</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="15" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>&gt; スコープによって表示が変わります</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B88" s="16" t="inlineStr">
-        <is>
-          <t>STEP 1　権限設定画面を開く</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>STEP 2　雛形を選ぶ</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B92" s="14" t="inlineStr">
-        <is>
-          <t>【画像②】</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="inlineStr">
-        <is>
-          <t>権限設定の一覧画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>&gt; スコープによって表示が変わります</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
-        </is>
-      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>STEP 2　雛形を選ぶ</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr"/>
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>雛形 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -1838,28 +1854,28 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>雛形 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr"/>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>従業員 ｜ 閲覧が中心です</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -1869,7 +1885,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -1882,290 +1898,302 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr"/>
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>【画像③】</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>雛形（ベース）の選択画面</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ゼロから設定する必要はありません</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。 たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr"/>
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>【画像③】</t>
-        </is>
-      </c>
-      <c r="C103" s="14" t="inlineStr">
-        <is>
-          <t>雛形（ベース）の選択画面</t>
-        </is>
-      </c>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>2. 区分を選びます。</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>【図3】</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>会社と店舗の区分（help/figures/ のSVGを掲載）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ゼロから設定する必要はありません</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。 たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="15" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B105" s="16" t="inlineStr">
-        <is>
-          <t>STEP 3　権限名と区分を決める</t>
-        </is>
-      </c>
-      <c r="C105" s="15" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>2. 区分を選びます。</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>区分 ｜ 設定できる画面</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr"/>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>STEP 4　画面ごとに設定して保存する</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>会社 ｜ 共通の画面＋会社画面（会社情報・お支払い・店舗管理・ダウンロード）</t>
+          <t>1. 画面ごとに「操作」「閲覧」「なし」を選びます。</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>店舗 ｜ 共通の画面＋店舗画面（発注先&amp;仕入商品・店舗情報・連携設定・費用設定・休業日設定・予算設定）</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr"/>
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>設定 ｜ できること</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>閲覧 ｜ 画面を開けます</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>なし ｜ 画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 「閲覧」と「操作」の違いについて</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>【画像④】</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>画面ごとの設定（操作／閲覧／なし）</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="15" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B113" s="16" t="inlineStr">
-        <is>
-          <t>STEP 4　画面ごとに設定して保存する</t>
-        </is>
-      </c>
-      <c r="C113" s="15" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面ごとに「操作」「閲覧」「なし」を選びます。</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>設定 ｜ できること</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>閲覧 ｜ 画面を開けます</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr"/>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>&gt; さらに細かく設定するには</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>なし ｜ 画面が表示されません</t>
+          <t>2. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 「閲覧」と「操作」の違いについて</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
-        </is>
-      </c>
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -2175,44 +2203,36 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
+          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B121" s="14" t="inlineStr">
-        <is>
-          <t>【画像④】</t>
-        </is>
-      </c>
-      <c r="C121" s="14" t="inlineStr">
-        <is>
-          <t>画面ごとの設定（操作／閲覧／なし）</t>
-        </is>
-      </c>
+      <c r="A121" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>&gt; さらに細かく設定するには</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
-        </is>
-      </c>
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -2222,33 +2242,33 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
+          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B124" s="11" t="inlineStr">
-        <is>
-          <t>権限をメンバーに割り当てる</t>
-        </is>
-      </c>
-      <c r="C124" s="10" t="inlineStr"/>
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
+          <t>4. 「保存」を選択します。</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr"/>
@@ -2256,54 +2276,66 @@
     <row r="126">
       <c r="A126" s="15" t="inlineStr">
         <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑥】</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr">
+        <is>
+          <t>まとめて割り当てる画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>&gt; すでに別の権限をお持ちの方</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 対象の絞り込み</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr"/>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
+        </is>
+      </c>
+      <c r="C129" s="16" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -2313,87 +2345,79 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>3. 権限を1つ選びます。</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
           <t>4. 「保存」を選択します。</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B131" s="14" t="inlineStr">
-        <is>
-          <t>【画像⑥】</t>
-        </is>
-      </c>
-      <c r="C131" s="14" t="inlineStr">
-        <is>
-          <t>まとめて割り当てる画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>&gt; すでに別の権限をお持ちの方</t>
-        </is>
-      </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 対象の絞り込み</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
-        </is>
-      </c>
+      <c r="C133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="15" t="inlineStr">
         <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>メンバーごとの割当編集画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="16" t="inlineStr">
+        <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B134" s="16" t="inlineStr">
-        <is>
-          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
-        </is>
-      </c>
-      <c r="C134" s="15" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr"/>
+      <c r="B135" s="17" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+        </is>
+      </c>
+      <c r="C135" s="16" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -2403,7 +2427,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr"/>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>3. 権限を1つ選びます。</t>
+          <t>2. 対象の権限の「割当へ →」を選択します。</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr"/>
@@ -2429,50 +2453,46 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択します。</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B139" s="14" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C139" s="14" t="inlineStr">
-        <is>
-          <t>メンバーごとの割当編集画面</t>
-        </is>
-      </c>
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="15" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B140" s="16" t="inlineStr">
-        <is>
-          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="inlineStr"/>
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
+          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr"/>
@@ -2480,12 +2500,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の権限の「割当へ →」を選択します。</t>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr"/>
@@ -2498,33 +2518,33 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B144" s="11" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C144" s="10" t="inlineStr"/>
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr"/>
@@ -2532,183 +2552,191 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
+          <t>4. 「保存」を選択します。</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr"/>
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr"/>
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr"/>
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗の反映について</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 設定の反映について</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B152" s="14" t="inlineStr">
-        <is>
-          <t>【画像⑧】</t>
-        </is>
-      </c>
-      <c r="C152" s="14" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
-        </is>
-      </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗の反映について</t>
-        </is>
-      </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B157" s="11" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr"/>
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr"/>
+      <c r="A158" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B158" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑨】</t>
+        </is>
+      </c>
+      <c r="C158" s="15" t="inlineStr">
+        <is>
+          <t>指標一覧の画面</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -2718,24 +2746,24 @@
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>&gt; 設定の反映について</t>
+          <t>&gt; 初期値は自動で設定されます</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr"/>
@@ -2743,72 +2771,64 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
+          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr"/>
+      <c r="A162" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B163" s="14" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C163" s="14" t="inlineStr">
-        <is>
-          <t>指標一覧の画面</t>
-        </is>
-      </c>
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 初期値は自動で設定されます</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="inlineStr">
-        <is>
-          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
-        </is>
-      </c>
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr"/>
@@ -2816,170 +2836,170 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>作成した権限を修正する</t>
-        </is>
-      </c>
-      <c r="C167" s="10" t="inlineStr"/>
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B169" s="9" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C169" s="8" t="inlineStr"/>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr"/>
+      <c r="A170" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B170" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑤】</t>
+        </is>
+      </c>
+      <c r="C170" s="15" t="inlineStr">
+        <is>
+          <t>マス目を選択して該当箇所へ移動したところ</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr"/>
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>&gt; マス目を選択すると該当箇所が開きます</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr"/>
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="inlineStr">
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B175" s="14" t="inlineStr">
-        <is>
-          <t>【画像⑤】</t>
-        </is>
-      </c>
-      <c r="C175" s="14" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ</t>
-        </is>
-      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
+      <c r="A177" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B177" s="13" t="inlineStr">
+        <is>
+          <t>別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -2989,23 +3009,23 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B179" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C179" s="10" t="inlineStr"/>
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B179" s="13" t="inlineStr">
+        <is>
+          <t>権限を外す</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -3015,36 +3035,40 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr"/>
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="12" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B182" s="13" t="inlineStr">
-        <is>
-          <t>別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C182" s="12" t="inlineStr"/>
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -3054,102 +3078,98 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="12" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B184" s="13" t="inlineStr">
-        <is>
-          <t>権限を外す</t>
-        </is>
-      </c>
-      <c r="C184" s="12" t="inlineStr"/>
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B186" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="10" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="inlineStr">
+      <c r="B188" s="11" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C188" s="10" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B189" s="9" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C189" s="8" t="inlineStr"/>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr"/>
@@ -3157,28 +3177,32 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr"/>
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑩】</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>役割サマリの画面</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
@@ -3188,7 +3212,7 @@
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>設定内容を確認する</t>
+          <t>よくあるご質問</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr"/>
@@ -3201,351 +3225,282 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
+          <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="inlineStr">
+      <c r="A195" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B195" s="18" t="inlineStr">
+        <is>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B196" s="18" t="inlineStr">
+        <is>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
+        <is>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B197" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B198" s="18" t="inlineStr">
+        <is>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="inlineStr">
+        <is>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B199" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
+        <is>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B200" s="18" t="inlineStr">
+        <is>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B201" s="18" t="inlineStr">
+        <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C201" s="18" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B202" s="18" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C202" s="18" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B203" s="18" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B204" s="18" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C204" s="18" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B205" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C205" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B206" s="18" t="inlineStr">
+        <is>
+          <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C206" s="18" t="inlineStr">
+        <is>
+          <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t>参照リンク</t>
+        </is>
+      </c>
+      <c r="C207" s="10" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
         <is>
           <t>本文</t>
         </is>
       </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="14" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B197" s="14" t="inlineStr">
-        <is>
-          <t>【画像⑩】</t>
-        </is>
-      </c>
-      <c r="C197" s="14" t="inlineStr">
-        <is>
-          <t>役割サマリの画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B198" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C198" s="10" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B200" s="17" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C200" s="17" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B201" s="17" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C201" s="17" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B202" s="17" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C202" s="17" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B203" s="17" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C203" s="17" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B204" s="17" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C204" s="17" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B205" s="17" t="inlineStr">
-        <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
-        </is>
-      </c>
-      <c r="C205" s="17" t="inlineStr">
-        <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B206" s="17" t="inlineStr">
-        <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
-        </is>
-      </c>
-      <c r="C206" s="17" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B207" s="17" t="inlineStr">
-        <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
-        </is>
-      </c>
-      <c r="C207" s="17" t="inlineStr">
-        <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B208" s="17" t="inlineStr">
-        <is>
-          <t>Q. 自分の権限を変更できますか？</t>
-        </is>
-      </c>
-      <c r="C208" s="17" t="inlineStr">
-        <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B209" s="17" t="inlineStr">
-        <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
-        </is>
-      </c>
-      <c r="C209" s="17" t="inlineStr">
-        <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B210" s="17" t="inlineStr">
-        <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
-        </is>
-      </c>
-      <c r="C210" s="17" t="inlineStr">
-        <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="17" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B211" s="17" t="inlineStr">
-        <is>
-          <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
-        </is>
-      </c>
-      <c r="C211" s="17" t="inlineStr">
-        <is>
-          <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B212" s="11" t="inlineStr">
-        <is>
-          <t>参照リンク</t>
-        </is>
-      </c>
-      <c r="C212" s="10" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B216" s="4" t="inlineStr">
+      <c r="B211" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C216" s="4" t="inlineStr"/>
+      <c r="C211" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C216"/>
+  <autoFilter ref="A2:C211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$232</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C211"/>
+  <dimension ref="A1:C232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -653,36 +653,36 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>目次｜やりたいことからお探しください</t>
+          <t>目次</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>共通項目　はじめにお読みください</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>やりたいこと ｜ お読みいただく見出し</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>はじめて権限を設定する ｜ 導入時の初期設定</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>見出し ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>経理担当に、売上とお支払だけ見せたい ｜ 権限を作成する</t>
+          <t>権限設定でできること ｜ この機能で何ができるか</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -705,7 +705,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>人事担当に、従業員情報だけ見せたい ｜ 権限を作成する</t>
+          <t>ご利用の前提条件 ｜ ご自身に操作できるか／守っていただく決まり</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -718,7 +718,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに、一部の画面だけ見せたい ｜ 権限を作成する</t>
+          <t>用語の説明 ｜ 画面に出てくる言葉の意味</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>特定の店舗の数字だけ見せたい ｜ 担当店舗を設定する</t>
+          <t>ご利用の流れ ｜ 設定全体の手順</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -739,28 +739,28 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>複数の店舗をまとめて見せたい ｜ 担当店舗を設定する</t>
+          <t>操作手順　ひとつずつの操作のやり方</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>新しく入った方に権限を与えたい ｜ 権限をメンバーに割り当てる</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>見出し ｜ こんなとき</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>大勢にまとめて権限を与えたい ｜ 権限をメンバーに割り当てる</t>
+          <t>導入時の初期設定 ｜ はじめて使う。まず何をすればいいか知りたい</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -783,7 +783,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>異動した方の権限を付け替えたい ｜ 権限を変更・解除する</t>
+          <t>権限を作成する ｜ 新しい権限を作りたい</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>退職した方の権限を外したい ｜ 権限を変更・解除する</t>
+          <t>権限をメンバーに割り当てる ｜ 作った権限を人に付けたい</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>作った権限の内容や名前を直したい ｜ 作成した権限を修正する</t>
+          <t>担当店舗を設定する ｜ どの店舗の数字を見せるか決めたい</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>見せる数字（売上・原価など）を絞りたい ｜ 表示する数字を選ぶ</t>
+          <t>表示する数字を選ぶ ｜ 見せる数字を絞りたい</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>誰がどの権限を持っているか確認したい ｜ 設定内容を確認する</t>
+          <t>作成した権限を修正する ｜ 作った権限の内容や名前を直したい</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>全権を別の方に譲りたい ｜ オーナーだけができること</t>
+          <t>権限を変更・解除する ｜ 異動・退職で付け替えたい／外したい</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>会社と店舗の両方の画面を使わせたい ｜ よくあるご質問</t>
+          <t>オーナーだけができること ｜ 全権を譲りたい／すべての数字を見たい</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>設定を誤って画面が開けなくなった ｜ よくあるご質問</t>
+          <t>設定内容を確認する ｜ 設定を一覧で見直したい</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -882,54 +882,54 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>兼務する方の権限をどうするか決めたい ｜ よくあるご質問</t>
+          <t>ケース別のやり方　やりたいことからお探しください</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>権限設定でできること</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr"/>
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>やりたいこと ｜ お読みいただく見出し</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>貴社の体制に合わせて、メンバーごとに見える範囲を変えられます。</t>
+          <t>経理担当に、売上とお支払だけ見せたい ｜ ケース別のやり方</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>こんなときに ｜ 設定例</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい ｜ ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>経理担当に売上や支払は見せたいが、従業員情報は見せたくない ｜ 分析画面と支払を「閲覧」、従業員管理を「なし」</t>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい ｜ ケース別のやり方</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>人事担当に従業員情報だけ見せたい ｜ 従業員関連を「閲覧」、売上系を「なし」</t>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー） ｜ ケース別のやり方</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -965,7 +965,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに売上画面だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
+          <t>新しく入った方には、まず最小限から始めたい ｜ ケース別のやり方</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -978,92 +978,88 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>新入社員にはまず最小限から始めたい ｜ ダッシュボード以外を「なし」</t>
+          <t>会社と店舗の両方の画面を使わせたい ｜ ケース別のやり方</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 今回のリリースでできること</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
-        </is>
-      </c>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>退職した方の権限を外したい ｜ 権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>設定を誤って画面が開けなくなった ｜ よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>兼務する方の権限をどうするか決めたい ｜ よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>ご利用の前提条件</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>この画面で何ができるかは、ご自身の権限によって変わります。</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ｜ オーナー ｜ 本部管理者</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr"/>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>権限設定でできること</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>権限を作る・直す ｜ できる ｜ できる</t>
+          <t>貴社の体制に合わせて、メンバーごとに見える範囲を変えられます。</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>メンバーに割り当てる ｜ できる ｜ できる</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr"/>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>こんなときに ｜ 設定例</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1073,7 +1069,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>担当店舗を設定する ｜ できる ｜ できる</t>
+          <t>経理担当に売上や支払は見せたいが、従業員情報は見せたくない ｜ 分析画面と支払を「閲覧」、従業員管理を「なし」</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -1086,7 +1082,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>表示する数字を選ぶ ｜ できる ｜ できる</t>
+          <t>人事担当に従業員情報だけ見せたい ｜ 従業員関連を「閲覧」、売上系を「なし」</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1099,7 +1095,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>すべての数字を確認する ｜ できる ｜ できない</t>
+          <t>アルバイトリーダーに売上画面だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1112,114 +1108,118 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>全権を他の方に委ねる ｜ できる ｜ できない</t>
+          <t>新入社員にはまず最小限から始めたい ｜ ダッシュボード以外を「なし」</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限を変更する ｜ できない（全権で固定） ｜ できない</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr"/>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 今回のリリースでできること</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>・操作できるのはオーナーと本部管理者のみです。</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>ご利用の前提条件</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>この画面で何ができるかは、ご自身の権限によって変わります。</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ｜ オーナー ｜ 本部管理者</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>・権限は会社／店舗の区分で分かれます。区分によって設定できる画面が変わります。</t>
+          <t>権限を作る・直す ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="inlineStr">
-        <is>
-          <t>用語の説明</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>メンバーに割り当てる ｜ できる ｜ できる</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>画面に出てくる言葉です。読み進めていて分からない言葉が出たら、ここに戻ってきてください。</t>
+          <t>担当店舗を設定する ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>用語 ｜ 意味</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr"/>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ ｜ できる ｜ できる</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
+          <t>すべての数字を確認する ｜ できる ｜ できない</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
+          <t>全権を他の方に委ねる ｜ できる ｜ できない</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
+          <t>オーナーの権限を変更する ｜ できない（全権で固定） ｜ できない</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -1263,12 +1263,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
+          <t>・操作できるのはオーナーと本部管理者のみです。</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -1276,12 +1276,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
+          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -1289,12 +1289,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -1302,123 +1302,119 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
+          <t>・権限は会社／店舗の区分で分かれます。区分によって設定できる画面が変わります。</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr"/>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>用語の説明</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+          <t>画面に出てくる言葉です。読み進めていて分からない言葉が出たら、ここに戻ってきてください。</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>権限と担当店舗は別々に設定します。 同じ権限でも、担当する店舗は人によって異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr"/>
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>用語 ｜ 意味</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>図</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>【図2】</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>権限と担当店舗の関係（help/figures/ のSVGを掲載）</t>
-        </is>
-      </c>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>ご利用の流れ</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr"/>
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
+          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>画面 ｜ ここで何をするか</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr"/>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -1428,7 +1424,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>権限設定 ｜ 権限を作る・直す</t>
+          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
+          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -1454,27 +1450,23 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
+          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
-        </is>
-      </c>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -1484,7 +1476,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
+          <t>権限と担当店舗は別々に設定します。 同じ権限でも、担当する店舗は人によって異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -1497,40 +1489,40 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>【図1】</t>
+          <t>【図2】</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>ご利用の流れ（help/figures/ のSVGを掲載）</t>
+          <t>権限と担当店舗の関係（help/figures/ のSVGを掲載）</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>導入時の初期設定</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr"/>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>ご利用の流れ</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -1540,36 +1532,36 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>手順 — ①用意する権限を選ぶ → ②それぞれの初期値を選ぶ（推奨／操作可／閲覧のみ／なし）→ ③「適用」を選択する</t>
+          <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>登録できる権限は次の4つです。初期状態ではすべて選択されています。</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr"/>
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>画面 ｜ ここで何をするか</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>権限 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr"/>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>権限設定 ｜ 権限を作る・直す</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -1579,7 +1571,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
+          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -1592,136 +1584,132 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
+          <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr"/>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>「適用」を選択すると、権限一覧に登録された状態になります。</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr"/>
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>【図1】</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>ご利用の流れ（help/figures/ のSVGを掲載）</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>【画像①】</t>
-        </is>
-      </c>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>権限テンプレートの画面</t>
-        </is>
-      </c>
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>導入時の初期設定</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 途中で中断できます／やり直せます</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
-        </is>
-      </c>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="inlineStr">
-        <is>
-          <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
-        </is>
-      </c>
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>手順 — ①用意する権限を選ぶ → ②それぞれの初期値を選ぶ（推奨／操作可／閲覧のみ／なし）→ ③「適用」を選択する</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t>権限を作成する</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr"/>
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>登録できる権限は次の4つです。初期状態ではすべて選択されています。</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>STEP 1　権限設定画面を開く</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr"/>
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>権限 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
+          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -1729,12 +1717,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
+          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -1742,124 +1730,128 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
+          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="15" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>従業員 ｜ 閲覧が中心です</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>「適用」を選択すると、権限一覧に登録された状態になります。</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>【画像②】</t>
-        </is>
-      </c>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>権限設定の一覧画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>【画像①】</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>権限テンプレートの画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>&gt; スコープによって表示が変わります</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 途中で中断できます／やり直せます</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>権限を作成する</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>STEP 2　雛形を選ぶ</t>
-        </is>
-      </c>
-      <c r="C91" s="16" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>1. 「＋ 権限を新規作成」を選択します。</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>雛形 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr"/>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>STEP 1　権限設定画面を開く</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -1867,12 +1859,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -1880,75 +1872,75 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr"/>
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>【画像②】</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>権限設定の一覧画面</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B100" s="15" t="inlineStr">
-        <is>
-          <t>【画像③】</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="inlineStr">
-        <is>
-          <t>雛形（ベース）の選択画面</t>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>&gt; スコープによって表示が変わります</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ゼロから設定する必要はありません</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。 たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
-        </is>
-      </c>
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>STEP 2　雛形を選ぶ</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>STEP 3　権限名と区分を決める</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="inlineStr"/>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -1958,197 +1950,193 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>2. 区分を選びます。</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>雛形 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="14" t="inlineStr">
-        <is>
-          <t>図</t>
-        </is>
-      </c>
-      <c r="B105" s="14" t="inlineStr">
-        <is>
-          <t>【図3】</t>
-        </is>
-      </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t>会社と店舗の区分（help/figures/ のSVGを掲載）</t>
-        </is>
-      </c>
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>従業員 ｜ 閲覧が中心です</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B108" s="17" t="inlineStr">
-        <is>
-          <t>STEP 4　画面ごとに設定して保存する</t>
-        </is>
-      </c>
-      <c r="C108" s="16" t="inlineStr"/>
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>1. 画面ごとに「操作」「閲覧」「なし」を選びます。</t>
+          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>設定 ｜ できること</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr"/>
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>【画像③】</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>雛形（ベース）の選択画面</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
-        </is>
-      </c>
-      <c r="C111" s="4" t="inlineStr"/>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ゼロから設定する必要はありません</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。 たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B112" s="4" t="inlineStr">
-        <is>
-          <t>閲覧 ｜ 画面を開けます</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr"/>
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>なし ｜ 画面が表示されません</t>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>2. 区分を選びます。</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>【図3】</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>会社と店舗の区分（help/figures/ のSVGを掲載）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 「閲覧」と「操作」の違いについて</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B116" s="15" t="inlineStr">
-        <is>
-          <t>【画像④】</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="inlineStr">
-        <is>
-          <t>画面ごとの設定（操作／閲覧／なし）</t>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
         </is>
       </c>
     </row>
@@ -2160,76 +2148,76 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>&gt; さらに細かく設定するには</t>
+          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
+          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>STEP 4　画面ごとに設定して保存する</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>2. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B119" s="11" t="inlineStr">
-        <is>
-          <t>権限をメンバーに割り当てる</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr"/>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>1. 画面ごとに「操作」「閲覧」「なし」を選びます。</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr"/>
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>設定 ｜ できること</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B121" s="17" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr"/>
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
+          <t>閲覧 ｜ 画面を開けます</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr"/>
@@ -2237,38 +2225,42 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
+          <t>なし ｜ 画面が表示されません</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr"/>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 「閲覧」と「操作」の違いについて</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択します。</t>
+          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr"/>
@@ -2281,12 +2273,12 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>【画像⑥】</t>
+          <t>【画像④】</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>まとめて割り当てる画面</t>
+          <t>画面ごとの設定（操作／閲覧／なし）</t>
         </is>
       </c>
     </row>
@@ -2298,70 +2290,66 @@
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>&gt; すでに別の権限をお持ちの方</t>
+          <t>&gt; さらに細かく設定するには</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 対象の絞り込み</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
-        </is>
-      </c>
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>2. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B129" s="17" t="inlineStr">
-        <is>
-          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
-        </is>
-      </c>
-      <c r="C129" s="16" t="inlineStr"/>
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
+          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr"/>
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -2371,7 +2359,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>3. 権限を1つ選びます。</t>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
@@ -2384,102 +2372,110 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
+          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
           <t>4. 「保存」を選択します。</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B134" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C134" s="15" t="inlineStr">
-        <is>
-          <t>メンバーごとの割当編集画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="16" t="inlineStr">
+      <c r="B136" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑥】</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="inlineStr">
+        <is>
+          <t>まとめて割り当てる画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>&gt; すでに別の権限をお持ちの方</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 対象の絞り込み</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B135" s="17" t="inlineStr">
-        <is>
-          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
-        </is>
-      </c>
-      <c r="C135" s="16" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>2. 対象の権限の「割当へ →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B139" s="11" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C139" s="10" t="inlineStr"/>
+      <c r="B139" s="17" t="inlineStr">
+        <is>
+          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
+        </is>
+      </c>
+      <c r="C139" s="16" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr"/>
@@ -2487,12 +2483,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
+          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr"/>
@@ -2500,12 +2496,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+          <t>3. 権限を1つ選びます。</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr"/>
@@ -2518,36 +2514,40 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
+          <t>4. 「保存」を選択します。</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr"/>
+      <c r="A144" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B144" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="inlineStr">
+        <is>
+          <t>メンバーごとの割当編集画面</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="inlineStr"/>
+      <c r="A145" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B145" s="17" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+        </is>
+      </c>
+      <c r="C145" s="16" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -2557,74 +2557,62 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択します。</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B147" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑧】</t>
-        </is>
-      </c>
-      <c r="C147" s="15" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面</t>
-        </is>
-      </c>
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>2. 対象の権限の「割当へ →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
-        </is>
-      </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr"/>
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗の反映について</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -2634,53 +2622,49 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
+          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B152" s="11" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ</t>
-        </is>
-      </c>
-      <c r="C152" s="10" t="inlineStr"/>
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 設定の反映について</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
-        </is>
-      </c>
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -2690,7 +2674,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr"/>
@@ -2703,70 +2687,74 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
+          <t>4. 「保存」を選択します。</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr"/>
+      <c r="A157" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B157" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C157" s="15" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B158" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C158" s="15" t="inlineStr">
-        <is>
-          <t>指標一覧の画面</t>
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 初期値は自動で設定されます</t>
-        </is>
-      </c>
-      <c r="C159" s="5" t="inlineStr">
-        <is>
-          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr"/>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗の反映について</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -2776,7 +2764,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr"/>
@@ -2789,7 +2777,7 @@
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>作成した権限を修正する</t>
+          <t>表示する数字を選ぶ</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr"/>
@@ -2802,33 +2790,37 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B164" s="9" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C164" s="8" t="inlineStr"/>
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 設定の反映について</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr"/>
@@ -2836,12 +2828,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr"/>
@@ -2849,92 +2841,88 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr"/>
+      <c r="A168" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B168" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑨】</t>
+        </is>
+      </c>
+      <c r="C168" s="15" t="inlineStr">
+        <is>
+          <t>指標一覧の画面</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr"/>
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 初期値は自動で設定されます</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B170" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑤】</t>
-        </is>
-      </c>
-      <c r="C170" s="15" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ</t>
-        </is>
-      </c>
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C171" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
+      <c r="A172" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B172" s="11" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -2944,33 +2932,33 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B174" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C174" s="10" t="inlineStr"/>
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr"/>
@@ -2978,67 +2966,71 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="12" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B177" s="13" t="inlineStr">
-        <is>
-          <t>別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C177" s="12" t="inlineStr"/>
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="12" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B179" s="13" t="inlineStr">
-        <is>
-          <t>権限を外す</t>
-        </is>
-      </c>
-      <c r="C179" s="12" t="inlineStr"/>
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr"/>
+      <c r="A180" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B180" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑤】</t>
+        </is>
+      </c>
+      <c r="C180" s="15" t="inlineStr">
+        <is>
+          <t>マス目を選択して該当箇所へ移動したところ</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -3048,27 +3040,31 @@
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+          <t>&gt; マス目を選択すると該当箇所が開きます</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B182" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C182" s="10" t="inlineStr"/>
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -3078,33 +3074,33 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B184" s="9" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr"/>
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
@@ -3112,54 +3108,54 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr"/>
+      <c r="A187" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B187" s="13" t="inlineStr">
+        <is>
+          <t>別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B188" s="11" t="inlineStr">
-        <is>
-          <t>設定内容を確認する</t>
-        </is>
-      </c>
-      <c r="C188" s="10" t="inlineStr"/>
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr"/>
+      <c r="A189" s="12" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B189" s="13" t="inlineStr">
+        <is>
+          <t>権限を外す</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -3169,293 +3165,249 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B192" s="11" t="inlineStr">
+        <is>
+          <t>オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C192" s="10" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C198" s="10" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
           <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
         </is>
       </c>
-      <c r="C190" s="4" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
+      <c r="C200" s="4" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
         <is>
           <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
         </is>
       </c>
-      <c r="C191" s="4" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="15" t="inlineStr">
+      <c r="C201" s="4" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B192" s="15" t="inlineStr">
+      <c r="B202" s="15" t="inlineStr">
         <is>
           <t>【画像⑩】</t>
         </is>
       </c>
-      <c r="C192" s="15" t="inlineStr">
+      <c r="C202" s="15" t="inlineStr">
         <is>
           <t>役割サマリの画面</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="10" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B193" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C193" s="10" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B195" s="18" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C195" s="18" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B196" s="18" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B197" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B198" s="18" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C198" s="18" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B199" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C199" s="18" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B200" s="18" t="inlineStr">
-        <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B201" s="18" t="inlineStr">
-        <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
-        </is>
-      </c>
-      <c r="C201" s="18" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B202" s="18" t="inlineStr">
-        <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
-        </is>
-      </c>
-      <c r="C202" s="18" t="inlineStr">
-        <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B203" s="18" t="inlineStr">
-        <is>
-          <t>Q. 自分の権限を変更できますか？</t>
-        </is>
-      </c>
-      <c r="C203" s="18" t="inlineStr">
-        <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
-        </is>
-      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="C203" s="10" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B204" s="18" t="inlineStr">
-        <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
-        </is>
-      </c>
-      <c r="C204" s="18" t="inlineStr">
-        <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
-        </is>
-      </c>
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>ここまでの操作手順を、よくあるケースに当てはめた設定例です。どのケースも、まず「権限を作成する」で権限を作り、次に「権限をメンバーに割り当てる」で人に付けます。 区分が「店舗」の場合は、あわせて「担当店舗を設定する」を行ってください。</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B205" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
-        </is>
-      </c>
-      <c r="C205" s="18" t="inlineStr">
-        <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
-        </is>
-      </c>
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B205" s="9" t="inlineStr">
+        <is>
+          <t>ケース ｜ 区分 ｜ 選ぶ雛形 ｜ 「なし」にする画面 ｜ 担当店舗</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B206" s="18" t="inlineStr">
-        <is>
-          <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
-        </is>
-      </c>
-      <c r="C206" s="18" t="inlineStr">
-        <is>
-          <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
-        </is>
-      </c>
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>経理担当に、売上とお支払だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 従業員（閲覧）・従業員管理・ユーザー ｜ 不要</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B207" s="11" t="inlineStr">
-        <is>
-          <t>参照リンク</t>
-        </is>
-      </c>
-      <c r="C207" s="10" t="inlineStr"/>
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 売上分析・仕入分析・詳細分析・集計・お支払い ｜ 不要</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい ｜ 店舗 ｜ 店長 ｜ 仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定 ｜ 所属店舗</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr"/>
@@ -3463,12 +3415,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー） ｜ 店舗 ｜ 店長 ｜ なし（画面はそのまま） ｜ 担当する店舗を複数選ぶ</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr"/>
@@ -3476,31 +3428,364 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>新しく入った方には、まず最小限から始めたい ｜ 店舗 ｜ まっさら（なし） ｜ ダッシュボード以外すべて ｜ 所属店舗</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 経理担当は、会社と店舗で権限を2つ作ります</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>お支払いは会社の画面、費用設定・予算設定は店舗の画面です。1つの権限で両方は扱えないため、「経理（会社）」と「経理（店舗）」の2つを作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>&gt; エリアマネージャーは雛形にありません</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>「店長」を雛形に選び、権限名を「エリアマネージャー」に変えて、担当店舗を複数紐付けてください。担当する店舗数は組織によって変わるため、権限は共通のものを使い、店舗はメンバーごとに設定します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 画面の名前は区分によって変わります</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>上の表の画面名は、区分「会社」と区分「店舗」で一部が異なります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C214" s="10" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B216" s="18" t="inlineStr">
+        <is>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
+        </is>
+      </c>
+      <c r="C216" s="18" t="inlineStr">
+        <is>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B217" s="18" t="inlineStr">
+        <is>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
+        </is>
+      </c>
+      <c r="C217" s="18" t="inlineStr">
+        <is>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B218" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
+        </is>
+      </c>
+      <c r="C218" s="18" t="inlineStr">
+        <is>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B219" s="18" t="inlineStr">
+        <is>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
+        </is>
+      </c>
+      <c r="C219" s="18" t="inlineStr">
+        <is>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B220" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
+        </is>
+      </c>
+      <c r="C220" s="18" t="inlineStr">
+        <is>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B221" s="18" t="inlineStr">
+        <is>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="inlineStr">
+        <is>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B222" s="18" t="inlineStr">
+        <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C222" s="18" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B223" s="18" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C223" s="18" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B224" s="18" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C224" s="18" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B225" s="18" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C225" s="18" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B226" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C226" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B227" s="18" t="inlineStr">
+        <is>
+          <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C227" s="18" t="inlineStr">
+        <is>
+          <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B228" s="11" t="inlineStr">
+        <is>
+          <t>参照リンク</t>
+        </is>
+      </c>
+      <c r="C228" s="10" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B210" s="4" t="inlineStr">
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
         <is>
           <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
         </is>
       </c>
-      <c r="C210" s="4" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
+      <c r="C231" s="4" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C211" s="4" t="inlineStr"/>
+      <c r="C232" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C211"/>
+  <autoFilter ref="A2:C232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C217"/>
+  <dimension ref="A1:C224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>手順 — ①用意する権限を選ぶ → ②それぞれの初期値を選ぶ（推奨／操作可／閲覧のみ／なし）→ ③「適用」を選択する</t>
+          <t>流れ — 権限テンプレート → 用意する権限を選ぶ → 初期値を選ぶ →「適用」→ 権限一覧に登録される</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>「適用」を選択すると、権限一覧に登録された状態になります。</t>
+          <t>「適用」を選択すると権限一覧が開き、登録された権限が並びます。</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -1636,30 +1636,30 @@
       <c r="C79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>流れ — 権限設定 →「＋ 権限を新規作成」→ 雛形を選ぶ → 権限名と区分 → 画面ごとに設定 →「保存」→ 権限一覧に戻る</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B80" s="17" t="inlineStr">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>STEP 1　権限設定画面を開く</t>
         </is>
       </c>
-      <c r="C80" s="16" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr"/>
+      <c r="C81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -1682,70 +1682,70 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
           <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="15" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B85" s="15" t="inlineStr">
         <is>
           <t>【画像②】</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>権限設定の一覧画面</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>&gt; スコープによって表示が変わります</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B86" s="17" t="inlineStr">
+      <c r="B87" s="17" t="inlineStr">
         <is>
           <t>STEP 2　雛形を選ぶ</t>
         </is>
       </c>
-      <c r="C86" s="16" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>1. 「＋ 権限を新規作成」を選択します。</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr"/>
+      <c r="C87" s="16" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -1755,36 +1755,36 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
+          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
           <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="12" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B89" s="13" t="inlineStr">
+      <c r="B90" s="13" t="inlineStr">
         <is>
           <t>雛形 ｜ 内容</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr"/>
+      <c r="C90" s="12" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>従業員 ｜ 閲覧が中心です</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -1833,70 +1833,70 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
           <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="B96" s="15" t="inlineStr">
         <is>
           <t>【画像③】</t>
         </is>
       </c>
-      <c r="C95" s="15" t="inlineStr">
+      <c r="C96" s="15" t="inlineStr">
         <is>
           <t>雛形（ベース）の選択画面</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>&gt; ゼロから設定する必要はありません</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。 たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="16" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr">
+      <c r="B98" s="17" t="inlineStr">
         <is>
           <t>STEP 3　権限名と区分を決める</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr"/>
+      <c r="C98" s="16" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -1906,42 +1906,38 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
           <t>2. 区分を選びます。</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="14" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
         <is>
           <t>図</t>
         </is>
       </c>
-      <c r="B100" s="14" t="inlineStr">
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>【図3】</t>
         </is>
       </c>
-      <c r="C100" s="14" t="inlineStr">
+      <c r="C101" s="14" t="inlineStr">
         <is>
           <t>会社と店舗の区分（help/figures/ のSVGを掲載）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
         </is>
       </c>
     </row>
@@ -1953,66 +1949,70 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
           <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="16" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B103" s="17" t="inlineStr">
+      <c r="B104" s="17" t="inlineStr">
         <is>
           <t>STEP 4　画面ごとに設定して保存する</t>
         </is>
       </c>
-      <c r="C103" s="16" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>1. 画面ごとに「操作」「閲覧」「なし」を選びます。</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
+      <c r="C104" s="16" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="12" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>画面ごとに「操作」「閲覧」「なし」を選び、「保存」を選択します。保存すると権限一覧に戻ります。</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B105" s="13" t="inlineStr">
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>設定 ｜ できること</t>
         </is>
       </c>
-      <c r="C105" s="12" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
-        </is>
-      </c>
-      <c r="C106" s="4" t="inlineStr"/>
+      <c r="C106" s="12" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>閲覧 ｜ 画面を開けます</t>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -2035,149 +2035,149 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
+          <t>閲覧 ｜ 画面を開けます</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
           <t>なし ｜ 画面が表示されません</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>&gt; 「閲覧」と「操作」の違いについて</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="15" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B111" s="15" t="inlineStr">
+      <c r="B112" s="15" t="inlineStr">
         <is>
           <t>【画像④】</t>
         </is>
       </c>
-      <c r="C111" s="15" t="inlineStr">
+      <c r="C112" s="15" t="inlineStr">
         <is>
           <t>画面ごとの設定（操作／閲覧／なし）</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>&gt; さらに細かく設定するには</t>
         </is>
       </c>
-      <c r="C112" s="5" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>2. 設定が終わったら「保存」を選択します。続けてメンバーに割り当てる場合は「🔗 ユーザー割当で紐付け →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr"/>
-    </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>続けてメンバーに割り当てる場合は、「保存」ではなく「🔗 ユーザー割当で紐付け →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる</t>
         </is>
       </c>
-      <c r="C114" s="10" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr"/>
+      <c r="C115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B116" s="17" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="inlineStr"/>
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。始める画面と、保存後に開く画面がそれぞれ違います。</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr"/>
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>方法 ｜ 始める画面 ｜ 保存後に開く画面</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
+          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr"/>
@@ -2185,12 +2185,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
+          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
@@ -2198,79 +2198,67 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑥】</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="inlineStr">
-        <is>
-          <t>まとめて割り当てる画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>&gt; すでに別の権限をお持ちの方</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 対象の絞り込み</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
-        </is>
-      </c>
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B124" s="17" t="inlineStr">
-        <is>
-          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="inlineStr"/>
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -2280,79 +2268,87 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
+          <t>4. 「保存」を選択します。役割サマリが開き、割り当てた権限が強調表示されます。</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑥】</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr">
+        <is>
+          <t>まとめて割り当てる画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>&gt; すでに別の権限をお持ちの方</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 対象の絞り込み</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
+        </is>
+      </c>
+      <c r="C129" s="16" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
           <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>3. 権限を1つ選びます。</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B129" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C129" s="15" t="inlineStr">
-        <is>
-          <t>メンバーごとの割当編集画面</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="inlineStr"/>
+      <c r="C130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -2362,7 +2358,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
+          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr"/>
@@ -2375,7 +2371,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の権限の「割当へ →」を選択します。</t>
+          <t>3. 権限を1つ選びます。</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
@@ -2388,46 +2384,50 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態で一覧が表示されます。</t>
+          <t>4. 「保存」を選択します。ユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B134" s="11" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C134" s="10" t="inlineStr"/>
+      <c r="A134" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B134" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>メンバーごとの割当編集画面</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr"/>
+      <c r="A135" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B135" s="17" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+        </is>
+      </c>
+      <c r="C135" s="16" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr"/>
@@ -2435,12 +2435,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+          <t>2. 対象の権限の「割当へ →」を選択します。</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開きます。</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr"/>
@@ -2466,139 +2466,131 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+          <t>4. 対象の方の行で「割当を編集」→「保存」を選択します。絞り込みは保たれたままです。</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
-        </is>
-      </c>
-      <c r="C140" s="4" t="inlineStr"/>
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B140" s="11" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択します。</t>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B142" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑧】</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面</t>
-        </is>
-      </c>
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗の反映について</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B147" s="11" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr"/>
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択します。ユーザー割当に戻ります。</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="inlineStr"/>
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -2608,87 +2600,83 @@
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>&gt; 設定の反映について</t>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr"/>
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗の反映について</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
+          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B153" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C153" s="15" t="inlineStr">
-        <is>
-          <t>指標一覧の画面</t>
-        </is>
-      </c>
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 初期値は自動で設定されます</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
-        </is>
-      </c>
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -2698,98 +2686,110 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。「適用して指標一覧へ」で反映され、「キャンセル」では反映されません。</t>
+          <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr"/>
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 設定の反映について</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B157" s="11" t="inlineStr">
-        <is>
-          <t>作成した権限を修正する</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr"/>
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B159" s="13" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C159" s="12" t="inlineStr"/>
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr"/>
+      <c r="A160" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B160" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑨】</t>
+        </is>
+      </c>
+      <c r="C160" s="15" t="inlineStr">
+        <is>
+          <t>指標一覧の画面</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr"/>
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 初期値は自動で設定されます</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr"/>
@@ -2797,115 +2797,103 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr"/>
+      <c r="A164" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B164" s="11" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B165" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑤】</t>
-        </is>
-      </c>
-      <c r="C165" s="15" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ</t>
-        </is>
-      </c>
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
-        <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C166" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
+      <c r="A166" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B166" s="13" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C169" s="10" t="inlineStr"/>
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr"/>
@@ -2918,49 +2906,61 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B172" s="9" t="inlineStr">
-        <is>
-          <t>別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C172" s="8" t="inlineStr"/>
+      <c r="A172" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B172" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑤】</t>
+        </is>
+      </c>
+      <c r="C172" s="15" t="inlineStr">
+        <is>
+          <t>マス目を選択して該当箇所へ移動したところ</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr"/>
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>&gt; マス目を選択すると該当箇所が開きます</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B174" s="9" t="inlineStr">
-        <is>
-          <t>権限を外す</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr"/>
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -2970,40 +2970,36 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。</t>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B176" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
+      <c r="A176" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B176" s="11" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B177" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C177" s="10" t="inlineStr"/>
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -3013,49 +3009,49 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B179" s="13" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C179" s="12" t="inlineStr"/>
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B179" s="9" t="inlineStr">
+        <is>
+          <t>別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr"/>
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>権限を外す</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -3065,36 +3061,40 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="10" t="inlineStr">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B183" s="11" t="inlineStr">
-        <is>
-          <t>設定内容を確認する</t>
-        </is>
-      </c>
-      <c r="C183" s="10" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr"/>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -3104,53 +3104,49 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr"/>
+      <c r="A186" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B186" s="13" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B187" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑩】</t>
-        </is>
-      </c>
-      <c r="C187" s="15" t="inlineStr">
-        <is>
-          <t>役割サマリの画面</t>
-        </is>
-      </c>
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B188" s="11" t="inlineStr">
-        <is>
-          <t>ケース別のやり方</t>
-        </is>
-      </c>
-      <c r="C188" s="10" t="inlineStr"/>
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -3160,33 +3156,33 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>ここまでの操作手順を、よくあるケースに当てはめた設定例です。どのケースも、まず「権限を作成する」で権限を作り、次に「権限をメンバーに割り当てる」で人に付けます。 区分が「店舗」の場合は、あわせて「担当店舗を設定する」を行ってください。</t>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B190" s="13" t="inlineStr">
-        <is>
-          <t>ケース ｜ 区分 ｜ 選ぶ雛形 ｜ 「なし」にする画面 ｜ 担当店舗</t>
-        </is>
-      </c>
-      <c r="C190" s="12" t="inlineStr"/>
+      <c r="A190" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B190" s="11" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C190" s="10" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>経理担当に、売上とお支払だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 従業員（閲覧）・従業員管理・ユーザー ｜ 不要</t>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
@@ -3194,12 +3190,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>人事担当に、従業員情報だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 売上分析・仕入分析・詳細分析・集計・お支払い ｜ 不要</t>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
@@ -3207,237 +3203,213 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに、一部の画面だけ見せたい ｜ 店舗 ｜ 店長 ｜ 仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定 ｜ 所属店舗</t>
+          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>複数の店舗をまとめて見せたい（エリアマネージャー） ｜ 店舗 ｜ 店長 ｜ なし（画面はそのまま） ｜ 担当する店舗を複数選ぶ</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr"/>
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑩】</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>役割サマリの画面</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>新しく入った方には、まず最小限から始めたい ｜ 店舗 ｜ まっさら（なし） ｜ ダッシュボード以外すべて ｜ 所属店舗</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr"/>
+      <c r="A195" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B196" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 経理担当は、会社と店舗で権限を2つ作ります</t>
-        </is>
-      </c>
-      <c r="C196" s="5" t="inlineStr">
-        <is>
-          <t>お支払いは会社の画面、費用設定・予算設定は店舗の画面です。1つの権限で両方は扱えないため、「経理（会社）」と「経理（店舗）」の2つを作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>ここまでの操作手順を、よくあるケースに当てはめた設定例です。どのケースも、まず「権限を作成する」で権限を作り、次に「権限をメンバーに割り当てる」で人に付けます。 区分が「店舗」の場合は、あわせて「担当店舗を設定する」を行ってください。</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>&gt; エリアマネージャーは雛形にありません</t>
-        </is>
-      </c>
-      <c r="C197" s="5" t="inlineStr">
-        <is>
-          <t>「店長」を雛形に選び、権限名を「エリアマネージャー」に変えて、担当店舗を複数紐付けてください。担当する店舗数は組織によって変わるため、権限は共通のものを使い、店舗はメンバーごとに設定します。</t>
-        </is>
-      </c>
+      <c r="A197" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B197" s="13" t="inlineStr">
+        <is>
+          <t>ケース ｜ 区分 ｜ 選ぶ雛形 ｜ 「なし」にする画面 ｜ 担当店舗</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 画面の名前は区分によって変わります</t>
-        </is>
-      </c>
-      <c r="C198" s="5" t="inlineStr">
-        <is>
-          <t>上の表の画面名は、区分「会社」と区分「店舗」で一部が異なります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。</t>
-        </is>
-      </c>
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>経理担当に、売上とお支払だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 従業員（閲覧）・従業員管理・ユーザー ｜ 不要</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B199" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C199" s="10" t="inlineStr"/>
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 売上分析・仕入分析・詳細分析・集計・お支払い ｜ 不要</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい ｜ 店舗 ｜ 店長 ｜ 仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定 ｜ 所属店舗</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー） ｜ 店舗 ｜ 店長 ｜ なし（画面はそのまま） ｜ 担当する店舗を複数選ぶ</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>新しく入った方には、まず最小限から始めたい ｜ 店舗 ｜ まっさら（なし） ｜ ダッシュボード以外すべて ｜ 所属店舗</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 経理担当は、会社と店舗で権限を2つ作ります</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>お支払いは会社の画面、費用設定・予算設定は店舗の画面です。1つの権限で両方は扱えないため、「経理（会社）」と「経理（店舗）」の2つを作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>&gt; エリアマネージャーは雛形にありません</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>「店長」を雛形に選び、権限名を「エリアマネージャー」に変えて、担当店舗を複数紐付けてください。担当する店舗数は組織によって変わるため、権限は共通のものを使い、店舗はメンバーごとに設定します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 画面の名前は区分によって変わります</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>上の表の画面名は、区分「会社」と区分「店舗」で一部が異なります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C206" s="10" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
           <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
-      <c r="C200" s="4" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B201" s="18" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C201" s="18" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B202" s="18" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C202" s="18" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B203" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C203" s="18" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B204" s="18" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C204" s="18" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B205" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C205" s="18" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B206" s="18" t="inlineStr">
-        <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
-        </is>
-      </c>
-      <c r="C206" s="18" t="inlineStr">
-        <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B207" s="18" t="inlineStr">
-        <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
-        </is>
-      </c>
-      <c r="C207" s="18" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="C207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
@@ -3447,12 +3419,12 @@
       </c>
       <c r="B208" s="18" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C208" s="18" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3436,12 @@
       </c>
       <c r="B209" s="18" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C209" s="18" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3453,12 @@
       </c>
       <c r="B210" s="18" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C210" s="18" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3470,12 @@
       </c>
       <c r="B211" s="18" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C211" s="18" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -3515,82 +3487,201 @@
       </c>
       <c r="B212" s="18" t="inlineStr">
         <is>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
+        </is>
+      </c>
+      <c r="C212" s="18" t="inlineStr">
+        <is>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B213" s="18" t="inlineStr">
+        <is>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+        </is>
+      </c>
+      <c r="C213" s="18" t="inlineStr">
+        <is>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B214" s="18" t="inlineStr">
+        <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C214" s="18" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B215" s="18" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C215" s="18" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B216" s="18" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C216" s="18" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B217" s="18" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C217" s="18" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B218" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C218" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B219" s="18" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C212" s="18" t="inlineStr">
+      <c r="C219" s="18" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="10" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B213" s="11" t="inlineStr">
+      <c r="B220" s="11" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C213" s="10" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
+      <c r="C220" s="10" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B214" s="4" t="inlineStr">
+      <c r="B221" s="4" t="inlineStr">
         <is>
           <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
-      <c r="C214" s="4" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B215" s="4" t="inlineStr">
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
         </is>
       </c>
-      <c r="C215" s="4" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B216" s="4" t="inlineStr">
+      <c r="B223" s="4" t="inlineStr">
         <is>
           <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
         </is>
       </c>
-      <c r="C216" s="4" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
+      <c r="C223" s="4" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C217" s="4" t="inlineStr"/>
+      <c r="C224" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C217"/>
+  <autoFilter ref="A2:C224"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$236</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C224"/>
+  <dimension ref="A1:C236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -809,7 +809,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ケース別のやり方　経理担当 ／ 人事担当 ／ アルバイトリーダー ／ エリアマネージャー ／ 最小限から始める</t>
+          <t>ケース別のやり方　経理担当 ／ 人事担当 ／ アルバイトリーダー ／ エリアマネージャー ／ 最小限から始める ／ 会社と店舗の両方</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>よくあるご質問　兼務する方の権限、会社と店舗の両方を使わせたいとき、画面が開けなくなったとき など</t>
+          <t>よくあるご質問　兼務する方の権限、設定を誤って画面が開けなくなったとき、役職との違い など</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -3244,40 +3244,40 @@
       <c r="C195" s="10" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>ここまでの操作手順を、よくあるケースに当てはめた設定例です。どのケースも、まず「権限を作成する」で権限を作り、次に「権限をメンバーに割り当てる」で人に付けます。 区分が「店舗」の場合は、あわせて「担当店舗を設定する」を行ってください。</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr"/>
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B196" s="17" t="inlineStr">
+        <is>
+          <t>どのケースも共通の登録手順</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B197" s="13" t="inlineStr">
-        <is>
-          <t>ケース ｜ 区分 ｜ 選ぶ雛形 ｜ 「なし」にする画面 ｜ 担当店舗</t>
-        </is>
-      </c>
-      <c r="C197" s="12" t="inlineStr"/>
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>経理担当に、売上とお支払だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 従業員（閲覧）・従業員管理・ユーザー ｜ 不要</t>
+          <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr"/>
@@ -3285,12 +3285,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>人事担当に、従業員情報だけ見せたい ｜ 会社 ｜ 本部管理 ｜ 売上分析・仕入分析・詳細分析・集計・お支払い ｜ 不要</t>
+          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr"/>
@@ -3298,12 +3298,12 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに、一部の画面だけ見せたい ｜ 店舗 ｜ 店長 ｜ 仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定 ｜ 所属店舗</t>
+          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr"/>
@@ -3311,92 +3311,80 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>複数の店舗をまとめて見せたい（エリアマネージャー） ｜ 店舗 ｜ 店長 ｜ なし（画面はそのまま） ｜ 担当する店舗を複数選ぶ</t>
+          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>新しく入った方には、まず最小限から始めたい ｜ 店舗 ｜ まっさら（なし） ｜ ダッシュボード以外すべて ｜ 所属店舗</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr"/>
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B202" s="17" t="inlineStr">
+        <is>
+          <t>ケース別の設定</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B203" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 経理担当は、会社と店舗で権限を2つ作ります</t>
-        </is>
-      </c>
-      <c r="C203" s="5" t="inlineStr">
-        <is>
-          <t>お支払いは会社の画面、費用設定・予算設定は店舗の画面です。1つの権限で両方は扱えないため、「経理（会社）」と「経理（店舗）」の2つを作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B203" s="9" t="inlineStr">
+        <is>
+          <t>経理担当に、売上とお支払だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B204" s="6" t="inlineStr">
-        <is>
-          <t>&gt; エリアマネージャーは雛形にありません</t>
-        </is>
-      </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>「店長」を雛形に選び、権限名を「エリアマネージャー」に変えて、担当店舗を複数紐付けてください。担当する店舗数は組織によって変わるため、権限は共通のものを使い、店舗はメンバーごとに設定します。</t>
-        </is>
-      </c>
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 画面の名前は区分によって変わります</t>
-        </is>
-      </c>
-      <c r="C205" s="5" t="inlineStr">
-        <is>
-          <t>上の表の画面名は、区分「会社」と区分「店舗」で一部が異なります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。</t>
-        </is>
-      </c>
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B206" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C206" s="10" t="inlineStr"/>
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B206" s="9" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C206" s="8" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -3406,282 +3394,442 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B208" s="9" t="inlineStr">
+        <is>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C208" s="8" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B210" s="9" t="inlineStr">
+        <is>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
+        </is>
+      </c>
+      <c r="C210" s="8" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B213" s="9" t="inlineStr">
+        <is>
+          <t>新しく入った方には、まず最小限から始めたい</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>会社と店舗の両方の画面を使わせたい</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 画面の名前は区分によって変わります</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C218" s="10" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
           <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="18" t="inlineStr">
+      <c r="C219" s="4" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B208" s="18" t="inlineStr">
+      <c r="B220" s="18" t="inlineStr">
         <is>
           <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
-      <c r="C208" s="18" t="inlineStr">
+      <c r="C220" s="18" t="inlineStr">
         <is>
           <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="18" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B209" s="18" t="inlineStr">
+      <c r="B221" s="18" t="inlineStr">
         <is>
           <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
-      <c r="C209" s="18" t="inlineStr">
+      <c r="C221" s="18" t="inlineStr">
         <is>
           <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="18" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B210" s="18" t="inlineStr">
+      <c r="B222" s="18" t="inlineStr">
         <is>
           <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
-      <c r="C210" s="18" t="inlineStr">
+      <c r="C222" s="18" t="inlineStr">
         <is>
           <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="18" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B211" s="18" t="inlineStr">
+      <c r="B223" s="18" t="inlineStr">
         <is>
           <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
-      <c r="C211" s="18" t="inlineStr">
+      <c r="C223" s="18" t="inlineStr">
         <is>
           <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="18" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B212" s="18" t="inlineStr">
+      <c r="B224" s="18" t="inlineStr">
         <is>
           <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
-      <c r="C212" s="18" t="inlineStr">
+      <c r="C224" s="18" t="inlineStr">
         <is>
           <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="18" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B213" s="18" t="inlineStr">
+      <c r="B225" s="18" t="inlineStr">
         <is>
           <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
         </is>
       </c>
-      <c r="C213" s="18" t="inlineStr">
+      <c r="C225" s="18" t="inlineStr">
         <is>
           <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="18" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B214" s="18" t="inlineStr">
+      <c r="B226" s="18" t="inlineStr">
         <is>
           <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
         </is>
       </c>
-      <c r="C214" s="18" t="inlineStr">
+      <c r="C226" s="18" t="inlineStr">
         <is>
           <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="18" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B215" s="18" t="inlineStr">
+      <c r="B227" s="18" t="inlineStr">
         <is>
           <t>Q. 役職を変更すると権限も変わりますか？</t>
         </is>
       </c>
-      <c r="C215" s="18" t="inlineStr">
+      <c r="C227" s="18" t="inlineStr">
         <is>
           <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="18" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B216" s="18" t="inlineStr">
+      <c r="B228" s="18" t="inlineStr">
         <is>
           <t>Q. 自分の権限を変更できますか？</t>
         </is>
       </c>
-      <c r="C216" s="18" t="inlineStr">
+      <c r="C228" s="18" t="inlineStr">
         <is>
           <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="18" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B217" s="18" t="inlineStr">
+      <c r="B229" s="18" t="inlineStr">
         <is>
           <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
         </is>
       </c>
-      <c r="C217" s="18" t="inlineStr">
+      <c r="C229" s="18" t="inlineStr">
         <is>
           <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="18" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B218" s="18" t="inlineStr">
+      <c r="B230" s="18" t="inlineStr">
         <is>
           <t>Q. 権限が未設定の方はどうなりますか？</t>
         </is>
       </c>
-      <c r="C218" s="18" t="inlineStr">
+      <c r="C230" s="18" t="inlineStr">
         <is>
           <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="18" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="18" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="B219" s="18" t="inlineStr">
+      <c r="B231" s="18" t="inlineStr">
         <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C219" s="18" t="inlineStr">
+      <c r="C231" s="18" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="10" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B220" s="11" t="inlineStr">
+      <c r="B232" s="11" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C220" s="10" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
+      <c r="C232" s="10" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr">
+      <c r="B233" s="4" t="inlineStr">
         <is>
           <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
-      <c r="C221" s="4" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="4" t="inlineStr">
+      <c r="C233" s="4" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B222" s="4" t="inlineStr">
+      <c r="B234" s="4" t="inlineStr">
         <is>
           <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
         </is>
       </c>
-      <c r="C222" s="4" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="4" t="inlineStr">
+      <c r="C234" s="4" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B223" s="4" t="inlineStr">
+      <c r="B235" s="4" t="inlineStr">
         <is>
           <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
         </is>
       </c>
-      <c r="C223" s="4" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
+      <c r="C235" s="4" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C224" s="4" t="inlineStr"/>
+      <c r="C236" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C224"/>
+  <autoFilter ref="A2:C236"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>権限と担当店舗の関係（help/figures/ のSVGを掲載）</t>
+          <t>権限と担当店舗の関係　※作成済み。help/figures/ の SVG または PNG を掲載</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>ご利用の流れ（help/figures/ のSVGを掲載）</t>
+          <t>ご利用の流れ　※作成済み。help/figures/ の SVG または PNG を掲載</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>権限テンプレートの画面</t>
+          <t>権限テンプレートの画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>権限設定の一覧画面</t>
+          <t>権限設定の一覧画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>雛形（ベース）の選択画面</t>
+          <t>雛形（ベース）の選択画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>会社と店舗の区分（help/figures/ のSVGを掲載）</t>
+          <t>会社と店舗の区分　※作成済み。help/figures/ の SVG または PNG を掲載</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>画面ごとの設定（操作／閲覧／なし）</t>
+          <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>まとめて割り当てる画面</t>
+          <t>まとめて割り当てる画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>メンバーごとの割当編集画面</t>
+          <t>メンバーごとの割当編集画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>担当店舗の選択画面</t>
+          <t>担当店舗の選択画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>指標一覧の画面</t>
+          <t>指標一覧の画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="C172" s="15" t="inlineStr">
         <is>
-          <t>マス目を選択して該当箇所へ移動したところ</t>
+          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C194" s="15" t="inlineStr">
         <is>
-          <t>役割サマリの画面</t>
+          <t>役割サマリの画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>

--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインします。</t>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインする</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択します。</t>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択する</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択します。</t>
+          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択する</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>1. 「＋ 権限を新規作成」を選択します。</t>
+          <t>1. 「＋ 権限を新規作成」を選択する</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -1768,36 +1768,36 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>2. 雛形（ベース）を選びます。近いものを選ぶと、あとの設定が少なくて済みます。</t>
+          <t>2. 雛形（ベース）を選ぶ</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>近いものを選ぶと、あとの設定が少なくて済みます。</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>雛形 ｜ 内容</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr"/>
+      <c r="C91" s="12" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>従業員 ｜ 閲覧が中心です</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -1846,70 +1846,70 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
           <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="15" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B96" s="15" t="inlineStr">
+      <c r="B97" s="15" t="inlineStr">
         <is>
           <t>【画像③】</t>
         </is>
       </c>
-      <c r="C96" s="15" t="inlineStr">
+      <c r="C97" s="15" t="inlineStr">
         <is>
           <t>雛形（ベース）の選択画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>&gt; ゼロから設定する必要はありません</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。 たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="16" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B98" s="17" t="inlineStr">
+      <c r="B99" s="17" t="inlineStr">
         <is>
           <t>STEP 3　権限名と区分を決める</t>
         </is>
       </c>
-      <c r="C98" s="16" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr"/>
+      <c r="C99" s="16" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -1919,42 +1919,38 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>2. 区分を選びます。</t>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="14" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2. 区分を選ぶ</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
         <is>
           <t>図</t>
         </is>
       </c>
-      <c r="B101" s="14" t="inlineStr">
+      <c r="B102" s="14" t="inlineStr">
         <is>
           <t>【図3】</t>
         </is>
       </c>
-      <c r="C101" s="14" t="inlineStr">
+      <c r="C102" s="14" t="inlineStr">
         <is>
           <t>会社と店舗の区分　※作成済み。help/figures/ の SVG または PNG を掲載</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
         </is>
       </c>
     </row>
@@ -1966,66 +1962,70 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
+          <t>&gt; 区分は先に決めてください</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
           <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="16" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B104" s="17" t="inlineStr">
+      <c r="B105" s="17" t="inlineStr">
         <is>
           <t>STEP 4　画面ごとに設定して保存する</t>
         </is>
       </c>
-      <c r="C104" s="16" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="C105" s="16" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>画面ごとに「操作」「閲覧」「なし」を選び、「保存」を選択します。保存すると権限一覧に戻ります。</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="12" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B106" s="13" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>設定 ｜ できること</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
-        </is>
-      </c>
-      <c r="C107" s="4" t="inlineStr"/>
+      <c r="C107" s="12" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>閲覧 ｜ 画面を開けます</t>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
@@ -2048,139 +2048,139 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
+          <t>閲覧 ｜ 画面を開けます</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
           <t>なし ｜ 画面が表示されません</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>&gt; 「閲覧」と「操作」の違いについて</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B111" s="4" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="15" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B112" s="15" t="inlineStr">
+      <c r="B113" s="15" t="inlineStr">
         <is>
           <t>【画像④】</t>
         </is>
       </c>
-      <c r="C112" s="15" t="inlineStr">
+      <c r="C113" s="15" t="inlineStr">
         <is>
           <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>&gt; さらに細かく設定するには</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>続けてメンバーに割り当てる場合は、「保存」ではなく「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B115" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる</t>
         </is>
       </c>
-      <c r="C115" s="10" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="C116" s="10" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。始める画面と、保存後に開く画面がそれぞれ違います。</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="12" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B117" s="13" t="inlineStr">
+      <c r="B118" s="13" t="inlineStr">
         <is>
           <t>方法 ｜ 始める画面 ｜ 保存後に開く画面</t>
         </is>
       </c>
-      <c r="C117" s="12" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr"/>
+      <c r="C118" s="12" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
+          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
@@ -2203,36 +2203,36 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
+          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
           <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="16" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B121" s="17" t="inlineStr">
+      <c r="B122" s="17" t="inlineStr">
         <is>
           <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
         </is>
       </c>
-      <c r="C121" s="16" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr"/>
+      <c r="C122" s="16" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>2. メンバーの一覧が表示されます。割り当てる方の「含める」にチェックを入れます。</t>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択する</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選びます。</t>
+          <t>2. 割り当てる方の「含める」にチェックを入れる</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr"/>
@@ -2268,100 +2268,100 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択します。役割サマリが開き、割り当てた権限が強調表示されます。</t>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選ぶ</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="15" t="inlineStr">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>保存すると役割サマリが開き、割り当てた権限が強調表示されます。</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B126" s="15" t="inlineStr">
+      <c r="B128" s="15" t="inlineStr">
         <is>
           <t>【画像⑥】</t>
         </is>
       </c>
-      <c r="C126" s="15" t="inlineStr">
+      <c r="C128" s="15" t="inlineStr">
         <is>
           <t>まとめて割り当てる画面　※スクリーンショット未取得</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>&gt; すでに別の権限をお持ちの方</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>&gt; 対象の絞り込み</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C130" s="5" t="inlineStr">
         <is>
           <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B129" s="17" t="inlineStr">
+      <c r="B131" s="17" t="inlineStr">
         <is>
           <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
         </is>
       </c>
-      <c r="C129" s="16" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択します。</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>2. 対象の方の行で「割当を編集」を選択します。</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr"/>
+      <c r="C131" s="16" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>3. 権限を1つ選びます。</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択する</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
@@ -2384,79 +2384,79 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択します。ユーザー割当に戻ります。</t>
+          <t>2. 対象の方の行で「割当を編集」を選択する</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B134" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C134" s="15" t="inlineStr">
-        <is>
-          <t>メンバーごとの割当編集画面　※スクリーンショット未取得</t>
-        </is>
-      </c>
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>3. 権限を1つ選ぶ</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B135" s="17" t="inlineStr">
-        <is>
-          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
-        </is>
-      </c>
-      <c r="C135" s="16" t="inlineStr"/>
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択します。</t>
+          <t>保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>2. 対象の権限の「割当へ →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C137" s="4" t="inlineStr"/>
+      <c r="A137" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B137" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="inlineStr">
+        <is>
+          <t>メンバーごとの割当編集画面　※スクリーンショット未取得</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B138" s="4" t="inlineStr">
-        <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開きます。</t>
-        </is>
-      </c>
-      <c r="C138" s="4" t="inlineStr"/>
+      <c r="A138" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+        </is>
+      </c>
+      <c r="C138" s="16" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -2466,33 +2466,33 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>4. 対象の方の行で「割当を編集」→「保存」を選択します。絞り込みは保たれたままです。</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択する</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B140" s="11" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C140" s="10" t="inlineStr"/>
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>2. 対象の権限の「割当へ →」を選択する</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開く</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr"/>
@@ -2500,12 +2500,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
+          <t>4. 対象の方の行で「割当を編集」→「保存」を選択する</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr"/>
@@ -2518,33 +2518,33 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+          <t>絞り込みは保たれたままです。</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択します。</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr"/>
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選びます。複数選択できます。</t>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr"/>
@@ -2552,12 +2552,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れます。</t>
+          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr"/>
@@ -2565,79 +2565,67 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>4. 「保存」を選択します。ユーザー割当に戻ります。</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B148" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑧】</t>
-        </is>
-      </c>
-      <c r="C148" s="15" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面　※スクリーンショット未取得</t>
-        </is>
-      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>1. 割当編集の画面で、店舗の権限を選択する</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>2. 「対象店舗」で担当店舗を選ぶ</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れる</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗の反映について</t>
-        </is>
-      </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -2647,36 +2635,44 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
+          <t>担当店舗は複数選択できます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B153" s="11" t="inlineStr">
-        <is>
-          <t>表示する数字を選ぶ</t>
-        </is>
-      </c>
-      <c r="C153" s="10" t="inlineStr"/>
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B153" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C153" s="15" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面　※スクリーンショット未取得</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr"/>
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -2686,7 +2682,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
+          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr"/>
@@ -2699,70 +2695,66 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>&gt; 設定の反映について</t>
+          <t>&gt; 担当店舗の反映について</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択します。</t>
+          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替えます。</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr"/>
+      <c r="A158" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B158" s="11" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C158" s="10" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替えます。保存操作は不要で、その場で反映されます。</t>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B160" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C160" s="15" t="inlineStr">
-        <is>
-          <t>指標一覧の画面　※スクリーンショット未取得</t>
-        </is>
-      </c>
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -2772,24 +2764,24 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>&gt; 初期値は自動で設定されます</t>
+          <t>&gt; 設定の反映について</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択する</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr"/>
@@ -2797,28 +2789,28 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替える</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t>作成した権限を修正する</t>
-        </is>
-      </c>
-      <c r="C164" s="10" t="inlineStr"/>
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>3. 各項目を選択して、表示／非表示を切り替える</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -2828,46 +2820,54 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+          <t>保存操作は不要で、その場で反映されます。</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B166" s="13" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C166" s="12" t="inlineStr"/>
+      <c r="A166" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B166" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑨】</t>
+        </is>
+      </c>
+      <c r="C166" s="15" t="inlineStr">
+        <is>
+          <t>指標一覧の画面　※スクリーンショット未取得</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr"/>
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 初期値は自動で設定されます</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr"/>
@@ -2875,28 +2875,28 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr"/>
+      <c r="A170" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="inlineStr">
+        <is>
+          <t>作成した権限を修正する</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -2906,87 +2906,75 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B172" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑤】</t>
-        </is>
-      </c>
-      <c r="C172" s="15" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得</t>
-        </is>
-      </c>
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B172" s="13" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B174" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B176" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C176" s="10" t="inlineStr"/>
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -2996,170 +2984,182 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
+          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B178" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑤】</t>
+        </is>
+      </c>
+      <c r="C178" s="15" t="inlineStr">
+        <is>
+          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>&gt; マス目を選択すると該当箇所が開きます</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B182" s="11" t="inlineStr">
+        <is>
+          <t>権限を変更・解除する</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
           <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="C183" s="4" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
         <is>
           <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="8" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B179" s="9" t="inlineStr">
+      <c r="B185" s="9" t="inlineStr">
         <is>
           <t>別の権限に変更する</t>
         </is>
       </c>
-      <c r="C179" s="8" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="C185" s="8" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="8" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B181" s="9" t="inlineStr">
+      <c r="B187" s="9" t="inlineStr">
         <is>
           <t>権限を外す</t>
         </is>
       </c>
-      <c r="C181" s="8" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B183" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B184" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C184" s="10" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B186" s="13" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C186" s="12" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr"/>
+      <c r="C187" s="8" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr"/>
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="B190" s="11" t="inlineStr">
         <is>
-          <t>設定内容を確認する</t>
+          <t>オーナーだけができること</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr"/>
@@ -3182,79 +3182,75 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr"/>
+      <c r="A192" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B194" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑩】</t>
-        </is>
-      </c>
-      <c r="C194" s="15" t="inlineStr">
-        <is>
-          <t>役割サマリの画面　※スクリーンショット未取得</t>
-        </is>
-      </c>
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="10" t="inlineStr">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B195" s="11" t="inlineStr">
-        <is>
-          <t>ケース別のやり方</t>
-        </is>
-      </c>
-      <c r="C195" s="10" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B196" s="17" t="inlineStr">
-        <is>
-          <t>どのケースも共通の登録手順</t>
-        </is>
-      </c>
-      <c r="C196" s="16" t="inlineStr"/>
+      <c r="B196" s="11" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -3264,7 +3260,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr"/>
@@ -3272,12 +3268,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr"/>
@@ -3285,41 +3281,45 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
+          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr"/>
+      <c r="A200" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B200" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑩】</t>
+        </is>
+      </c>
+      <c r="C200" s="15" t="inlineStr">
+        <is>
+          <t>役割サマリの画面　※スクリーンショット未取得</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr"/>
+      <c r="A201" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="C201" s="10" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="16" t="inlineStr">
@@ -3329,33 +3329,33 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>ケース別の設定</t>
+          <t>どのケースも共通の登録手順</t>
         </is>
       </c>
       <c r="C202" s="16" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B203" s="9" t="inlineStr">
-        <is>
-          <t>経理担当に、売上とお支払だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C203" s="8" t="inlineStr"/>
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
+          <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr"/>
@@ -3363,28 +3363,28 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B206" s="9" t="inlineStr">
-        <is>
-          <t>人事担当に、従業員情報だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C206" s="8" t="inlineStr"/>
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -3394,49 +3394,49 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
+          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="8" t="inlineStr">
+      <c r="A208" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B208" s="17" t="inlineStr">
+        <is>
+          <t>ケース別の設定</t>
+        </is>
+      </c>
+      <c r="C208" s="16" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B208" s="9" t="inlineStr">
-        <is>
-          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C208" s="8" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr"/>
+      <c r="B209" s="9" t="inlineStr">
+        <is>
+          <t>経理担当に、売上とお支払だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B210" s="9" t="inlineStr">
-        <is>
-          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
-        </is>
-      </c>
-      <c r="C210" s="8" t="inlineStr"/>
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -3446,220 +3446,196 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
+          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B212" s="9" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C212" s="8" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B214" s="9" t="inlineStr">
+        <is>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B216" s="9" t="inlineStr">
+        <is>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
           <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
         </is>
       </c>
-      <c r="C211" s="4" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
+      <c r="C217" s="4" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
         </is>
       </c>
-      <c r="C212" s="4" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="8" t="inlineStr">
+      <c r="C218" s="4" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B213" s="9" t="inlineStr">
+      <c r="B219" s="9" t="inlineStr">
         <is>
           <t>新しく入った方には、まず最小限から始めたい</t>
         </is>
       </c>
-      <c r="C213" s="8" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
+      <c r="C219" s="8" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
         </is>
       </c>
-      <c r="C214" s="4" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="8" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B215" s="9" t="inlineStr">
+      <c r="B221" s="9" t="inlineStr">
         <is>
           <t>会社と店舗の両方の画面を使わせたい</t>
         </is>
       </c>
-      <c r="C215" s="8" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B216" s="4" t="inlineStr">
+      <c r="C221" s="8" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
-      <c r="C216" s="4" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="5" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="B223" s="6" t="inlineStr">
         <is>
           <t>&gt; 画面の名前は区分によって変わります</t>
         </is>
       </c>
-      <c r="C217" s="5" t="inlineStr">
+      <c r="C223" s="5" t="inlineStr">
         <is>
           <t>会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="10" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B218" s="11" t="inlineStr">
+      <c r="B224" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
-      <c r="C218" s="10" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
+      <c r="C224" s="10" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
         <is>
           <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
-      <c r="C219" s="4" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B220" s="18" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C220" s="18" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B221" s="18" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C221" s="18" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B222" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C222" s="18" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B223" s="18" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C223" s="18" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B224" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C224" s="18" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B225" s="18" t="inlineStr">
-        <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
-        </is>
-      </c>
-      <c r="C225" s="18" t="inlineStr">
-        <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="C225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
@@ -3669,12 +3645,12 @@
       </c>
       <c r="B226" s="18" t="inlineStr">
         <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C226" s="18" t="inlineStr">
         <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3662,12 @@
       </c>
       <c r="B227" s="18" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C227" s="18" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3679,12 @@
       </c>
       <c r="B228" s="18" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C228" s="18" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3696,12 @@
       </c>
       <c r="B229" s="18" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C229" s="18" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -3737,12 +3713,12 @@
       </c>
       <c r="B230" s="18" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
       <c r="C230" s="18" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
@@ -3754,82 +3730,171 @@
       </c>
       <c r="B231" s="18" t="inlineStr">
         <is>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+        </is>
+      </c>
+      <c r="C231" s="18" t="inlineStr">
+        <is>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B232" s="18" t="inlineStr">
+        <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C232" s="18" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B233" s="18" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C233" s="18" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B234" s="18" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C234" s="18" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B235" s="18" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C235" s="18" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B236" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C236" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B237" s="18" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C231" s="18" t="inlineStr">
+      <c r="C237" s="18" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="10" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B232" s="11" t="inlineStr">
+      <c r="B238" s="11" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C232" s="10" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="4" t="inlineStr">
+      <c r="C238" s="10" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B233" s="4" t="inlineStr">
+      <c r="B239" s="4" t="inlineStr">
         <is>
           <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
+      <c r="C239" s="4" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
         <is>
           <t>箇条書き</t>
         </is>
       </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>・[従業員の登録方法](https://help.rakmy.jp/management/従業員)</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B235" s="4" t="inlineStr">
+      <c r="B240" s="4" t="inlineStr">
         <is>
           <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
         </is>
       </c>
-      <c r="C235" s="4" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
+      <c r="C240" s="4" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
         <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C236" s="4" t="inlineStr"/>
+      <c r="C241" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C236"/>
+  <autoFilter ref="A2:C241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -636,12 +636,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>&gt; このページの対象</t>
+          <t>&gt; このページはオーナー・本部管理者の方向けの説明です。権限の設定はこのお二方のみが行えます。一部の操作（すべての数字の確認、全権の委譲）はオーナーのみ行えます。</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>オーナー・本部管理者の方向けの説明です。権限の設定はこのお二方のみが行えます。一部の操作（すべての数字の確認、全権の委譲）はオーナーのみ行えます。 はじめて設定される方は「導入時の初期設定」からお読みください。</t>
+          <t>はじめて設定される方は「導入時の初期設定」からお読みください。</t>
         </is>
       </c>
     </row>
@@ -926,14 +926,10 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>&gt; 今回のリリースでできること</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
-        </is>
-      </c>
+          <t>&gt; 今回のリリースで設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -1402,14 +1398,10 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
-        </is>
-      </c>
+          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます。権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -1596,14 +1588,10 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>&gt; 途中で中断できます／やり直せます</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
-        </is>
-      </c>
+          <t>&gt; 途中で中断できます。「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -1613,14 +1601,10 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>&gt; まず土台を作り、あとで分けるのがおすすめです</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
-        </is>
-      </c>
+          <t>&gt; まず土台を作り、あとで分けるのがおすすめです。導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
@@ -1725,14 +1709,10 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>&gt; スコープによって表示が変わります</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
-        </is>
-      </c>
+          <t>&gt; スコープによって表示が変わります。会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -1889,12 +1869,12 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>&gt; ゼロから設定する必要はありません</t>
+          <t>&gt; ゼロから設定する必要はありません。設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。 たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
+          <t>たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
         </is>
       </c>
     </row>
@@ -1962,14 +1942,10 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>&gt; 区分は先に決めてください</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
+          <t>&gt; 区分は先に決めてください。区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -1979,14 +1955,10 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t>1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
+          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください。1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
@@ -2074,14 +2046,10 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>&gt; 「閲覧」と「操作」の違いについて</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、どちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
-        </is>
-      </c>
+          <t>&gt; 「閲覧」と「操作」は、今回のリリースではどちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -2121,14 +2089,10 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>&gt; さらに細かく設定するには</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t>画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
-        </is>
-      </c>
+          <t>&gt; さらに細かく設定することもできます。画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -2324,14 +2288,10 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>&gt; すでに別の権限をお持ちの方</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>1人が持てる権限は1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
+          <t>&gt; すでに別の権限をお持ちの方については、1人が持てる権限が1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -2341,14 +2301,10 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>&gt; 対象の絞り込み</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
-        </is>
-      </c>
+          <t>&gt; 対象は自動で絞り込まれます。店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
@@ -2665,14 +2621,10 @@
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください。店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -2695,14 +2647,10 @@
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>&gt; 担当店舗の反映について</t>
-        </is>
-      </c>
-      <c r="C156" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+          <t>&gt; 今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -2764,14 +2712,10 @@
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>&gt; 設定の反映について</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
-        </is>
-      </c>
+          <t>&gt; 今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -2850,14 +2794,10 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>&gt; 初期値は自動で設定されます</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="inlineStr">
-        <is>
-          <t>権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
-        </is>
-      </c>
+          <t>&gt; 初期値は自動で設定されます。権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -3014,14 +2954,10 @@
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>&gt; マス目を選択すると該当箇所が開きます</t>
-        </is>
-      </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
+          <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -3031,14 +2967,10 @@
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>&gt; ⚠️ 修正はその権限をお持ちの全員に反映されます</t>
-        </is>
-      </c>
-      <c r="C180" s="5" t="inlineStr">
-        <is>
-          <t>特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
+          <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -3152,14 +3084,10 @@
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>&gt; ⚠️ 権限を外した方はログインしても画面が表示されません</t>
-        </is>
-      </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
+          <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -3602,14 +3530,10 @@
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>&gt; 画面の名前は区分によって変わります</t>
-        </is>
-      </c>
-      <c r="C223" s="5" t="inlineStr">
-        <is>
-          <t>会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
-        </is>
-      </c>
+          <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="10" t="inlineStr">

--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>権限テンプレートの画面　※スクリーンショット未取得</t>
+          <t>権限テンプレートの画面　※スクリーンショット未取得（撮影リスト ① 番）</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>権限設定の一覧画面　※スクリーンショット未取得</t>
+          <t>権限設定の一覧画面　※スクリーンショット未取得（撮影リスト ② 番）</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>雛形（ベース）の選択画面　※スクリーンショット未取得</t>
+          <t>雛形（ベース）の選択画面　※スクリーンショット未取得（撮影リスト ③ 番）</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得</t>
+          <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得（撮影リスト ④ 番）</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>【画像⑥】</t>
+          <t>【画像⑤】</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>まとめて割り当てる画面　※スクリーンショット未取得</t>
+          <t>まとめて割り当てる画面　※スクリーンショット未取得（撮影リスト ⑤ 番）</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2392,12 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>【画像⑦】</t>
+          <t>【画像⑥】</t>
         </is>
       </c>
       <c r="C137" s="15" t="inlineStr">
         <is>
-          <t>メンバーごとの割当編集画面　※スクリーンショット未取得</t>
+          <t>メンバーごとの割当編集画面　※スクリーンショット未取得（撮影リスト ⑥ 番）</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>【画像⑧】</t>
+          <t>【画像⑦】</t>
         </is>
       </c>
       <c r="C153" s="15" t="inlineStr">
         <is>
-          <t>担当店舗の選択画面　※スクリーンショット未取得</t>
+          <t>担当店舗の選択画面　※スクリーンショット未取得（撮影リスト ⑦ 番）</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>【画像⑨】</t>
+          <t>【画像⑧】</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>指標一覧の画面　※スクリーンショット未取得</t>
+          <t>指標一覧の画面　※スクリーンショット未取得（撮影リスト ⑧ 番）</t>
         </is>
       </c>
     </row>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>【画像⑤】</t>
+          <t>【画像⑨】</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr">
         <is>
-          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得</t>
+          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得（撮影リスト ⑨ 番）</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="C200" s="15" t="inlineStr">
         <is>
-          <t>役割サマリの画面　※スクリーンショット未取得</t>
+          <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
         </is>
       </c>
     </row>

--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C241"/>
+  <dimension ref="A1:C242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>はじめて設定される方は「導入時の初期設定」からお読みください。</t>
+          <t>はじめて設定される方は「導入時の初期設定」からお読みください。画面に出てくる言葉の意味は、ページの最後の「用語の説明」にまとめています。</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>共通項目　権限設定でできること ／ ご利用の前提条件 ／ 用語の説明 ／ ご利用の流れ</t>
+          <t>共通項目　権限設定でできること ／ ご利用の前提条件 ／ ご利用の流れ</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -828,56 +828,56 @@
       <c r="C19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>用語の説明　画面に出てくる言葉の意味（権限／区分／担当店舗／スコープ選択 など9語）。ページの最後にまとめています</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>権限設定でできること</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>貴社の体制に合わせて、メンバーごとに見える範囲を変えられます。</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>こんなときに ｜ 設定例</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>経理担当に売上や支払は見せたいが、従業員情報は見せたくない ｜ 分析画面と支払を「閲覧」、従業員管理を「なし」</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
+      <c r="C23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>人事担当に従業員情報だけ見せたい ｜ 従業員関連を「閲覧」、売上系を「なし」</t>
+          <t>経理担当に売上や支払は見せたいが、従業員情報は見せたくない ｜ 分析画面と支払を「閲覧」、従業員管理を「なし」</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>アルバイトリーダーに売上画面だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
+          <t>人事担当に従業員情報だけ見せたい ｜ 従業員関連を「閲覧」、売上系を「なし」</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -913,75 +913,75 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
+          <t>アルバイトリーダーに売上画面だけ見せたい ｜ 売上分析を「閲覧」、それ以外を「なし」</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>新入社員にはまず最小限から始めたい ｜ ダッシュボード以外を「なし」</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>&gt; 今回のリリースで設定できるのは画面を開けるかどうかです。画面の中の一部の数字だけを隠したり、画面は開けるが変更だけを禁止したりする設定は、今回のリリースには含まれていません。</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>ご利用の前提条件</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>この画面で何ができるかは、ご自身の権限によって変わります。</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve"> ｜ オーナー ｜ 本部管理者</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>権限を作る・直す ｜ できる ｜ できる</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>メンバーに割り当てる ｜ できる ｜ できる</t>
+          <t>権限を作る・直す ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>担当店舗を設定する ｜ できる ｜ できる</t>
+          <t>メンバーに割り当てる ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>表示する数字を選ぶ ｜ できる ｜ できる</t>
+          <t>担当店舗を設定する ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>すべての数字を確認する ｜ できる ｜ できない</t>
+          <t>表示する数字を選ぶ ｜ できる ｜ できる</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>全権を他の方に委ねる ｜ できる ｜ できない</t>
+          <t>すべての数字を確認する ｜ できる ｜ できない</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>オーナーの権限を変更する ｜ できない（全権で固定） ｜ できない</t>
+          <t>全権を他の方に委ねる ｜ できる ｜ できない</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -1064,12 +1064,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>箇条書き</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>・操作できるのはオーナーと本部管理者のみです。</t>
+          <t>オーナーの権限を変更する ｜ できない（全権で固定） ｜ できない</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
+          <t>・操作できるのはオーナーと本部管理者のみです。</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
+          <t>・権限を割り当てられるのは、ラクミー経営管理クラウドにログインする方です。従業員情報に登録されていても、ログインしない方は対象外です。</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -1108,62 +1108,62 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>・1人が持てる権限は1つです。別の権限を割り当てると、それまでの権限は自動的に外れます。</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>箇条書き</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>・権限は会社／店舗の区分で分かれます。区分によって設定できる画面が変わります。</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>用語の説明</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>画面に出てくる言葉です。読み進めていて分からない言葉が出たら、ここに戻ってきてください。</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr"/>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>ご利用の流れ</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>用語 ｜ 意味</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr"/>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>画面 ｜ ここで何をするか</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
+          <t>権限設定 ｜ 権限を作る・直す</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
+          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -1199,72 +1199,76 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
+          <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr"/>
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます。権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>【図1】</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>ご利用の流れ　※作成済み。help/figures/ の SVG または PNG を掲載</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>導入時の初期設定</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -1277,79 +1281,75 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>権限と担当店舗は別々に設定します。 同じ権限でも、担当する店舗は人によって異なるためです。権限は共通のものを使い、担当店舗はメンバーごとに紐付けます。</t>
+          <t>流れ — 権限テンプレート → 用意する権限を選ぶ → 初期値を選ぶ →「適用」→ 権限一覧に登録される</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>図</t>
-        </is>
-      </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>【図2】</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>権限と担当店舗の関係　※作成済み。help/figures/ の SVG または PNG を掲載</t>
-        </is>
-      </c>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>登録できる権限は次の4つです。初期状態ではすべて選択されています。</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr"/>
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>権限 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>ご利用の流れ</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr"/>
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>権限の設定は、次の3つの画面を行き来しながら進めます。</t>
+          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>画面 ｜ ここで何をするか</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr"/>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>権限設定 ｜ 権限を作る・直す</t>
+          <t>従業員 ｜ 閲覧が中心です</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -1367,28 +1367,32 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>ユーザー割当 ｜ 権限をメンバーに割り当て、担当店舗を紐付ける</t>
+          <t>「適用」を選択すると権限一覧が開き、登録された権限が並びます。</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 誰が何の権限を持っているかを確認する</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>【画像①】</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>権限テンプレートの画面　※スクリーンショット未取得（撮影リスト ① 番）</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -1398,76 +1402,72 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>&gt; 権限設定とユーザー割当は、どちらからでも行き来できます。権限を作った直後にそのまま割り当てに進むことも、メンバーの設定中に権限そのものを直したり、新しい権限をその場で作ったりすることもできます。すでに割り当て済みの方には、その旨が一覧の行に表示されます。</t>
+          <t>&gt; 途中で中断できます。「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>はじめて設定する場合は、次の順番がおすすめです。</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>&gt; まず土台を作り、あとで分けるのがおすすめです。導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>図</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>【図1】</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>ご利用の流れ　※作成済み。help/figures/ の SVG または PNG を掲載</t>
-        </is>
-      </c>
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>権限を作成する</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>導入時の初期設定</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr"/>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>流れ — 権限設定 →「＋ 権限を新規作成」→ 雛形を選ぶ → 権限名と区分 → 画面ごとに設定 →「保存」→ 権限一覧に戻る</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>はじめて権限設定を開くと、権限テンプレートの画面が表示されます。よく使う権限をまとめて登録できます。</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr"/>
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>STEP 1　権限設定画面を開く</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>流れ — 権限テンプレート → 用意する権限を選ぶ → 初期値を選ぶ →「適用」→ 権限一覧に登録される</t>
+          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインする</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -1475,77 +1475,81 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>登録できる権限は次の4つです。初期状態ではすべて選択されています。</t>
+          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択する</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>権限 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="inlineStr"/>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択する</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>オーナー（全権） ｜ すべての操作ができます（変更不可）</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr"/>
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>【画像②】</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>権限設定の一覧画面　※スクリーンショット未取得（撮影リスト ② 番）</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>会社ロール（権限母体） ｜ 本部・全社向けの土台。経理・人事などはここから作ります</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr"/>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>&gt; スコープによって表示が変わります。会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>店長（権限母体） ｜ 店舗運営の土台。エリアマネージャーなどはここから作ります</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr"/>
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>STEP 2　雛形を選ぶ</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>1. 「＋ 権限を新規作成」を選択する</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -1553,257 +1557,261 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>「適用」を選択すると権限一覧が開き、登録された権限が並びます。</t>
+          <t>2. 雛形（ベース）を選ぶ</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>【画像①】</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>権限テンプレートの画面　※スクリーンショット未取得（撮影リスト ① 番）</t>
-        </is>
-      </c>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>近いものを選ぶと、あとの設定が少なくて済みます。</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 途中で中断できます。「一時保存」を選択すると選んだ内容が保存され、次に開いたときに続きから設定できます。最初からやり直す場合は「下書きを破棄」を選択すると初期状態に戻ります。</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr"/>
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>雛形 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>&gt; まず土台を作り、あとで分けるのがおすすめです。導入時は「会社ロール（権限母体）」をひとつの土台として作り、運用が始まってから「経理」「人事」に分けていく進め方をおすすめしています。最初から細かく分けると、運用が固まる前に線引きを決めてしまうことになります。</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr"/>
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>権限を作成する</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr"/>
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>流れ — 権限設定 →「＋ 権限を新規作成」→ 雛形を選ぶ → 権限名と区分 → 画面ごとに設定 →「保存」→ 権限一覧に戻る</t>
+          <t>従業員 ｜ 閲覧が中心です</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B81" s="17" t="inlineStr">
-        <is>
-          <t>STEP 1　権限設定画面を開く</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr"/>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>【画像③】</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>雛形（ベース）の選択画面　※スクリーンショット未取得（撮影リスト ③ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>&gt; ゼロから設定する必要はありません。設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>STEP 3　権限名と区分を決める</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>1. [ラクミー経営管理画面](https://manager.rakmy.jp/users/sign_in)にログインする</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>2. 画面上部のスコープ選択で、設定したい会社または店舗を選択する</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>3. 左側のメニューバーで「設定」＞「権限設定」を選択する</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>【画像②】</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>権限設定の一覧画面　※スクリーンショット未取得（撮影リスト ② 番）</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2. 区分を選ぶ</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>【図3】</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>会社と店舗の区分　※作成済み。help/figures/ の SVG または PNG を掲載</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>&gt; スコープによって表示が変わります。会社を選択すると会社向けの権限と画面が、店舗を選択すると店舗向けの権限と画面が表示されます。</t>
-        </is>
-      </c>
-      <c r="C86" s="5" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 区分は先に決めてください。区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください。1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>STEP 2　雛形を選ぶ</t>
-        </is>
-      </c>
-      <c r="C87" s="16" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>1. 「＋ 権限を新規作成」を選択する</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>2. 雛形（ベース）を選ぶ</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>近いものを選ぶと、あとの設定が少なくて済みます。</t>
-        </is>
-      </c>
-      <c r="C90" s="4" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>雛形 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="inlineStr"/>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>STEP 4　画面ごとに設定して保存する</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>本部管理 ｜ 全社の設定・一覧を操作／閲覧できます</t>
+          <t>画面ごとに「操作」「閲覧」「なし」を選び、「保存」を選択します。保存すると権限一覧に戻ります。</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>店長 ｜ 自店舗の設定・一覧を操作／閲覧できます</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr"/>
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>設定 ｜ できること</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -1813,7 +1821,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>従業員 ｜ 閲覧が中心です</t>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -1826,7 +1834,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>既存の権限をコピー ｜ 運用中の権限を複製して、一部だけ変更できます</t>
+          <t>閲覧 ｜ 画面を開けます</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -1839,322 +1847,314 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
+          <t>なし ｜ 画面が表示されません</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 「閲覧」と「操作」は、今回のリリースではどちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B97" s="15" t="inlineStr">
-        <is>
-          <t>【画像③】</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>雛形（ベース）の選択画面　※スクリーンショット未取得（撮影リスト ③ 番）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>【画像④】</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得（撮影リスト ④ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>&gt; ゼロから設定する必要はありません。設定できる画面は27種類あります。近い雛形を選び、違うところだけ変更するのがおすすめです。</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>たとえばエリアマネージャーは、雛形の一覧にはありませんが「店長」を選んで権限名を変え、担当店舗を複数紐付ければ作れます。組織によって中身が変わるため、雛形としては用意していません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>STEP 3　権限名と区分を決める</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限名を入力します（例：経理担当、エリアマネージャー）。</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>&gt; さらに細かく設定することもできます。画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>2. 区分を選ぶ</t>
+          <t>続けてメンバーに割り当てる場合は、「保存」ではなく「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="14" t="inlineStr">
-        <is>
-          <t>図</t>
-        </is>
-      </c>
-      <c r="B102" s="14" t="inlineStr">
-        <is>
-          <t>【図3】</t>
-        </is>
-      </c>
-      <c r="C102" s="14" t="inlineStr">
-        <is>
-          <t>会社と店舗の区分　※作成済み。help/figures/ の SVG または PNG を掲載</t>
-        </is>
-      </c>
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>権限をメンバーに割り当てる</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください。区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr"/>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。始める画面と、保存後に開く画面がそれぞれ違います。</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください。1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr"/>
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>方法 ｜ 始める画面 ｜ 保存後に開く画面</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>STEP 4　画面ごとに設定して保存する</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr"/>
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>画面ごとに「操作」「閲覧」「なし」を選び、「保存」を選択します。保存すると権限一覧に戻ります。</t>
+          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>設定 ｜ できること</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="inlineStr"/>
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
+          <t>「役割サマリ」は、権限ごとに何名へ割り当てているかを確認する画面です。</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>閲覧 ｜ 画面を開けます</t>
-        </is>
-      </c>
-      <c r="C109" s="4" t="inlineStr"/>
+      <c r="A109" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>なし ｜ 画面が表示されません</t>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択する</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 「閲覧」と「操作」は、今回のリリースではどちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr"/>
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>2. 割り当てる方の「含める」にチェックを入れる</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選ぶ</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="15" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>保存すると役割サマリが開き、割り当てた権限が強調表示されます。</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B113" s="15" t="inlineStr">
-        <is>
-          <t>【画像④】</t>
-        </is>
-      </c>
-      <c r="C113" s="15" t="inlineStr">
-        <is>
-          <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得（撮影リスト ④ 番）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="B115" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑤】</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>まとめて割り当てる画面　※スクリーンショット未取得（撮影リスト ⑤ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>&gt; さらに細かく設定することもできます。画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>続けてメンバーに割り当てる場合は、「保存」ではなく「🔗 ユーザー割当で紐付け →」を選択します。</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B116" s="11" t="inlineStr">
-        <is>
-          <t>権限をメンバーに割り当てる</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr"/>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>&gt; すでに別の権限をお持ちの方については、1人が持てる権限が1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。始める画面と、保存後に開く画面がそれぞれ違います。</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr"/>
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 対象は自動で絞り込まれます。店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B118" s="13" t="inlineStr">
-        <is>
-          <t>方法 ｜ 始める画面 ｜ 保存後に開く画面</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="inlineStr"/>
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択する</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr"/>
@@ -2162,12 +2162,12 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
+          <t>2. 対象の方の行で「割当を編集」を選択する</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
@@ -2175,67 +2175,71 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
+          <t>3. 権限を1つ選ぶ</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
-        </is>
-      </c>
-      <c r="C122" s="16" t="inlineStr"/>
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択する</t>
+          <t>保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>2. 割り当てる方の「含める」にチェックを入れる</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr"/>
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑥】</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr">
+        <is>
+          <t>メンバーごとの割当編集画面　※スクリーンショット未取得（撮影リスト ⑥ 番）</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選ぶ</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr"/>
+      <c r="A125" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="inlineStr">
+        <is>
+          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -2245,7 +2249,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択する</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr"/>
@@ -2253,81 +2257,77 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>保存すると役割サマリが開き、割り当てた権限が強調表示されます。</t>
+          <t>2. 対象の権限の「割当へ →」を選択する</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B128" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑤】</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="inlineStr">
-        <is>
-          <t>まとめて割り当てる画面　※スクリーンショット未取得（撮影リスト ⑤ 番）</t>
-        </is>
-      </c>
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開く</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>&gt; すでに別の権限をお持ちの方については、1人が持てる権限が1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr"/>
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>4. 対象の方の行で「割当を編集」→「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 対象は自動で絞り込まれます。店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr"/>
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>絞り込みは保たれたままです。</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B131" s="17" t="inlineStr">
-        <is>
-          <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr"/>
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>担当店舗を設定する</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択する</t>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr"/>
@@ -2335,38 +2335,42 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の方の行で「割当を編集」を選択する</t>
+          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B134" s="4" t="inlineStr">
-        <is>
-          <t>3. 権限を1つ選ぶ</t>
-        </is>
-      </c>
-      <c r="C134" s="4" t="inlineStr"/>
+      <c r="A134" s="14" t="inlineStr">
+        <is>
+          <t>図</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>【図2】</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr">
+        <is>
+          <t>権限と担当店舗の関係　※作成済み。help/figures/ の SVG または PNG を掲載</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr"/>
@@ -2374,45 +2378,41 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>保存するとユーザー割当に戻ります。</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択する</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B137" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑥】</t>
-        </is>
-      </c>
-      <c r="C137" s="15" t="inlineStr">
-        <is>
-          <t>メンバーごとの割当編集画面　※スクリーンショット未取得（撮影リスト ⑥ 番）</t>
-        </is>
-      </c>
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>2. 「対象店舗」で担当店舗を選ぶ</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B138" s="17" t="inlineStr">
-        <is>
-          <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
-        </is>
-      </c>
-      <c r="C138" s="16" t="inlineStr"/>
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れる</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択する</t>
+          <t>4. 「保存」を選択する</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr"/>
@@ -2430,41 +2430,45 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の権限の「割当へ →」を選択する</t>
+          <t>担当店舗は複数選択できます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開く</t>
-        </is>
-      </c>
-      <c r="C141" s="4" t="inlineStr"/>
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑦】</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="inlineStr">
+        <is>
+          <t>担当店舗の選択画面　※スクリーンショット未取得（撮影リスト ⑦ 番）</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>4. 対象の方の行で「割当を編集」→「保存」を選択する</t>
-        </is>
-      </c>
-      <c r="C142" s="4" t="inlineStr"/>
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 担当店舗は必ず1つ以上お選びください。店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -2474,23 +2478,23 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>絞り込みは保たれたままです。</t>
+          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B144" s="11" t="inlineStr">
-        <is>
-          <t>担当店舗を設定する</t>
-        </is>
-      </c>
-      <c r="C144" s="10" t="inlineStr"/>
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -2500,23 +2504,23 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="inlineStr">
-        <is>
-          <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr"/>
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="inlineStr">
+        <is>
+          <t>表示する数字を選ぶ</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -2526,7 +2530,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr"/>
@@ -2534,28 +2538,28 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択する</t>
+          <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>2. 「対象店舗」で担当店舗を選ぶ</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr"/>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -2565,7 +2569,7 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れる</t>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択する</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr"/>
@@ -2578,7 +2582,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替える</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr"/>
@@ -2586,71 +2590,71 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>担当店舗は複数選択できます。保存するとユーザー割当に戻ります。</t>
+          <t>3. 各項目を選択して、表示／非表示を切り替える</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="15" t="inlineStr">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>保存操作は不要で、その場で反映されます。</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B153" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑦】</t>
-        </is>
-      </c>
-      <c r="C153" s="15" t="inlineStr">
-        <is>
-          <t>担当店舗の選択画面　※スクリーンショット未取得（撮影リスト ⑦ 番）</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="5" t="inlineStr">
+      <c r="B154" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑧】</t>
+        </is>
+      </c>
+      <c r="C154" s="15" t="inlineStr">
+        <is>
+          <t>指標一覧の画面　※スクリーンショット未取得（撮影リスト ⑧ 番）</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B154" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 担当店舗は必ず1つ以上お選びください。店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr"/>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 初期値は自動で設定されます。権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B156" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
-      <c r="C156" s="5" t="inlineStr"/>
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -2660,7 +2664,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
+          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr"/>
@@ -2673,7 +2677,7 @@
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>表示する数字を選ぶ</t>
+          <t>作成した権限を修正する</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr"/>
@@ -2686,46 +2690,46 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr"/>
+      <c r="A160" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B160" s="13" t="inlineStr">
+        <is>
+          <t>入口 ｜ 操作 ｜ こんなときに</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="inlineStr"/>
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択する</t>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr"/>
@@ -2733,12 +2737,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替える</t>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
@@ -2746,12 +2750,12 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替える</t>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr"/>
@@ -2764,7 +2768,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>保存操作は不要で、その場で反映されます。</t>
+          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr"/>
@@ -2777,12 +2781,12 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>【画像⑧】</t>
+          <t>【画像⑨】</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>指標一覧の画面　※スクリーンショット未取得（撮影リスト ⑧ 番）</t>
+          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得（撮影リスト ⑨ 番）</t>
         </is>
       </c>
     </row>
@@ -2794,23 +2798,23 @@
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>&gt; 初期値は自動で設定されます。権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
+          <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr"/>
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -2820,7 +2824,7 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
+          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr"/>
@@ -2833,7 +2837,7 @@
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>作成した権限を修正する</t>
+          <t>権限を変更・解除する</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr"/>
@@ -2846,157 +2850,153 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B172" s="13" t="inlineStr">
-        <is>
-          <t>入口 ｜ 操作 ｜ こんなときに</t>
-        </is>
-      </c>
-      <c r="C172" s="12" t="inlineStr"/>
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr"/>
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>別の権限に変更する</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr"/>
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="inlineStr">
+        <is>
+          <t>権限を外す</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr"/>
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B178" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑨】</t>
-        </is>
-      </c>
-      <c r="C178" s="15" t="inlineStr">
-        <is>
-          <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得（撮影リスト ⑨ 番）</t>
-        </is>
-      </c>
+      <c r="A178" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B178" s="11" t="inlineStr">
+        <is>
+          <t>オーナーだけができること</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B179" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
-      <c r="C179" s="5" t="inlineStr"/>
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
-      <c r="C180" s="5" t="inlineStr"/>
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B180" s="13" t="inlineStr">
+        <is>
+          <t>操作 ｜ 内容</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B182" s="11" t="inlineStr">
-        <is>
-          <t>権限を変更・解除する</t>
-        </is>
-      </c>
-      <c r="C182" s="10" t="inlineStr"/>
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -3006,36 +3006,36 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr"/>
+      <c r="A184" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="inlineStr">
+        <is>
+          <t>設定内容を確認する</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="inlineStr">
-        <is>
-          <t>別の権限に変更する</t>
-        </is>
-      </c>
-      <c r="C185" s="8" t="inlineStr"/>
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -3045,62 +3045,66 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>権限を外す</t>
-        </is>
-      </c>
-      <c r="C187" s="8" t="inlineStr"/>
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr"/>
+      <c r="A188" s="15" t="inlineStr">
+        <is>
+          <t>画像</t>
+        </is>
+      </c>
+      <c r="B188" s="15" t="inlineStr">
+        <is>
+          <t>【画像⑩】</t>
+        </is>
+      </c>
+      <c r="C188" s="15" t="inlineStr">
+        <is>
+          <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
+        </is>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
-        </is>
-      </c>
-      <c r="C189" s="5" t="inlineStr"/>
+      <c r="A189" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
+          <t>ケース別のやり方</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>オーナーだけができること</t>
-        </is>
-      </c>
-      <c r="C190" s="10" t="inlineStr"/>
+      <c r="A190" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B190" s="17" t="inlineStr">
+        <is>
+          <t>どのケースも共通の登録手順</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -3110,33 +3114,33 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
+          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="12" t="inlineStr">
-        <is>
-          <t>表 見出し</t>
-        </is>
-      </c>
-      <c r="B192" s="13" t="inlineStr">
-        <is>
-          <t>操作 ｜ 内容</t>
-        </is>
-      </c>
-      <c r="C192" s="12" t="inlineStr"/>
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
+          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr"/>
@@ -3144,12 +3148,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>表 行</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr"/>
@@ -3162,36 +3166,36 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
+          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B196" s="11" t="inlineStr">
-        <is>
-          <t>設定内容を確認する</t>
-        </is>
-      </c>
-      <c r="C196" s="10" t="inlineStr"/>
+      <c r="A196" s="16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="B196" s="17" t="inlineStr">
+        <is>
+          <t>ケース別の設定</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr"/>
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>経理担当に、売上とお支払だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -3201,7 +3205,7 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr"/>
@@ -3214,53 +3218,49 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
+          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="15" t="inlineStr">
-        <is>
-          <t>画像</t>
-        </is>
-      </c>
-      <c r="B200" s="15" t="inlineStr">
-        <is>
-          <t>【画像⑩】</t>
-        </is>
-      </c>
-      <c r="C200" s="15" t="inlineStr">
-        <is>
-          <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
-        </is>
-      </c>
+      <c r="A200" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B200" s="9" t="inlineStr">
+        <is>
+          <t>人事担当に、従業員情報だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C200" s="8" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="10" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B201" s="11" t="inlineStr">
-        <is>
-          <t>ケース別のやり方</t>
-        </is>
-      </c>
-      <c r="C201" s="10" t="inlineStr"/>
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B202" s="17" t="inlineStr">
-        <is>
-          <t>どのケースも共通の登録手順</t>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr"/>
+      <c r="A202" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B202" s="9" t="inlineStr">
+        <is>
+          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -3270,33 +3270,33 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
+          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr"/>
+      <c r="A204" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B204" s="9" t="inlineStr">
+        <is>
+          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
+          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr"/>
@@ -3304,41 +3304,41 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
+          <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr"/>
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>小見出し</t>
+        </is>
+      </c>
+      <c r="B207" s="9" t="inlineStr">
+        <is>
+          <t>新しく入った方には、まず最小限から始めたい</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="16" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="B208" s="17" t="inlineStr">
-        <is>
-          <t>ケース別の設定</t>
-        </is>
-      </c>
-      <c r="C208" s="16" t="inlineStr"/>
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="8" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>経理担当に、売上とお支払だけ見せたい</t>
+          <t>会社と店舗の両方の画面を使わせたい</t>
         </is>
       </c>
       <c r="C209" s="8" t="inlineStr"/>
@@ -3361,36 +3361,36 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
+          <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr"/>
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B212" s="9" t="inlineStr">
-        <is>
-          <t>人事担当に、従業員情報だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C212" s="8" t="inlineStr"/>
+      <c r="A212" s="10" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C212" s="10" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -3400,396 +3400,396 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
+          <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B214" s="9" t="inlineStr">
-        <is>
-          <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
-        </is>
-      </c>
-      <c r="C214" s="8" t="inlineStr"/>
+      <c r="A214" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B214" s="18" t="inlineStr">
+        <is>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
+        </is>
+      </c>
+      <c r="C214" s="18" t="inlineStr">
+        <is>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
+        </is>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr"/>
+      <c r="A215" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B215" s="18" t="inlineStr">
+        <is>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
+        </is>
+      </c>
+      <c r="C215" s="18" t="inlineStr">
+        <is>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
+        </is>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B216" s="9" t="inlineStr">
-        <is>
-          <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
-        </is>
-      </c>
-      <c r="C216" s="8" t="inlineStr"/>
+      <c r="A216" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B216" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
+        </is>
+      </c>
+      <c r="C216" s="18" t="inlineStr">
+        <is>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+        </is>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C217" s="4" t="inlineStr"/>
+      <c r="A217" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B217" s="18" t="inlineStr">
+        <is>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
+        </is>
+      </c>
+      <c r="C217" s="18" t="inlineStr">
+        <is>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
+        </is>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
-        </is>
-      </c>
-      <c r="C218" s="4" t="inlineStr"/>
+      <c r="A218" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B218" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
+        </is>
+      </c>
+      <c r="C218" s="18" t="inlineStr">
+        <is>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
+        </is>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B219" s="9" t="inlineStr">
-        <is>
-          <t>新しく入った方には、まず最小限から始めたい</t>
-        </is>
-      </c>
-      <c r="C219" s="8" t="inlineStr"/>
+      <c r="A219" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B219" s="18" t="inlineStr">
+        <is>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+        </is>
+      </c>
+      <c r="C219" s="18" t="inlineStr">
+        <is>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr"/>
+      <c r="A220" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B220" s="18" t="inlineStr">
+        <is>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+        </is>
+      </c>
+      <c r="C220" s="18" t="inlineStr">
+        <is>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+        </is>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="8" t="inlineStr">
-        <is>
-          <t>小見出し</t>
-        </is>
-      </c>
-      <c r="B221" s="9" t="inlineStr">
-        <is>
-          <t>会社と店舗の両方の画面を使わせたい</t>
-        </is>
-      </c>
-      <c r="C221" s="8" t="inlineStr"/>
+      <c r="A221" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B221" s="18" t="inlineStr">
+        <is>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="inlineStr">
+        <is>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr"/>
+      <c r="A222" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B222" s="18" t="inlineStr">
+        <is>
+          <t>Q. 自分の権限を変更できますか？</t>
+        </is>
+      </c>
+      <c r="C222" s="18" t="inlineStr">
+        <is>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+        </is>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
-        </is>
-      </c>
-      <c r="C223" s="5" t="inlineStr"/>
+      <c r="A223" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B223" s="18" t="inlineStr">
+        <is>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+        </is>
+      </c>
+      <c r="C223" s="18" t="inlineStr">
+        <is>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+        </is>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="10" t="inlineStr">
+      <c r="A224" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B224" s="18" t="inlineStr">
+        <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C224" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B225" s="18" t="inlineStr">
+        <is>
+          <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C225" s="18" t="inlineStr">
+        <is>
+          <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B224" s="11" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C224" s="10" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B226" s="18" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C226" s="18" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
+      <c r="B226" s="11" t="inlineStr">
+        <is>
+          <t>用語の説明</t>
+        </is>
+      </c>
+      <c r="C226" s="10" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B227" s="18" t="inlineStr">
-        <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
-        </is>
-      </c>
-      <c r="C227" s="18" t="inlineStr">
-        <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
-        </is>
-      </c>
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>画面に出てくる言葉の意味です。読んでいて分からない言葉が出たときにご覧ください。</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B228" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
-        </is>
-      </c>
-      <c r="C228" s="18" t="inlineStr">
-        <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
-        </is>
-      </c>
+      <c r="A228" s="12" t="inlineStr">
+        <is>
+          <t>表 見出し</t>
+        </is>
+      </c>
+      <c r="B228" s="13" t="inlineStr">
+        <is>
+          <t>用語 ｜ 意味</t>
+        </is>
+      </c>
+      <c r="C228" s="12" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B229" s="18" t="inlineStr">
-        <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
-        </is>
-      </c>
-      <c r="C229" s="18" t="inlineStr">
-        <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
-        </is>
-      </c>
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B230" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
-        </is>
-      </c>
-      <c r="C230" s="18" t="inlineStr">
-        <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
-        </is>
-      </c>
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B231" s="18" t="inlineStr">
-        <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
-        </is>
-      </c>
-      <c r="C231" s="18" t="inlineStr">
-        <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B232" s="18" t="inlineStr">
-        <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
-        </is>
-      </c>
-      <c r="C232" s="18" t="inlineStr">
-        <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
-        </is>
-      </c>
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B233" s="18" t="inlineStr">
-        <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
-        </is>
-      </c>
-      <c r="C233" s="18" t="inlineStr">
-        <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
-        </is>
-      </c>
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B234" s="18" t="inlineStr">
-        <is>
-          <t>Q. 自分の権限を変更できますか？</t>
-        </is>
-      </c>
-      <c r="C234" s="18" t="inlineStr">
-        <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
-        </is>
-      </c>
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B235" s="18" t="inlineStr">
-        <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
-        </is>
-      </c>
-      <c r="C235" s="18" t="inlineStr">
-        <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
-        </is>
-      </c>
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B236" s="18" t="inlineStr">
-        <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
-        </is>
-      </c>
-      <c r="C236" s="18" t="inlineStr">
-        <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
-        </is>
-      </c>
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B237" s="18" t="inlineStr">
-        <is>
-          <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
-        </is>
-      </c>
-      <c r="C237" s="18" t="inlineStr">
-        <is>
-          <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
-        </is>
-      </c>
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="10" t="inlineStr">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B238" s="11" t="inlineStr">
+      <c r="B239" s="11" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C238" s="10" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="inlineStr"/>
+      <c r="C239" s="10" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr"/>
@@ -3807,18 +3807,31 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
+          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C241" s="4" t="inlineStr"/>
+      <c r="C242" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C241"/>
+  <autoFilter ref="A2:C242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>新規作成 ｜ すべて「なし」の状態から設定します</t>
+          <t>まっさら（なし） ｜ すべて「なし」の状態から設定します</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>

--- a/20260805_権限設定_ヘルプページ.xlsx
+++ b/20260805_権限設定_ヘルプページ.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ヘルプページ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ヘルプページ'!$A$2:$C$243</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C242"/>
+  <dimension ref="A1:C243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1749,17 +1749,17 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 区分は先に決めてください。区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr"/>
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>会社の画面は会社情報・お支払い・店舗（管理）・ダウンロードの4つ、店舗の画面は発注先&amp;仕入商品・店舗情報・連携設定・費用設定・休業日設定・予算設定の6つです。どちらの区分でも共通の画面17は設定できます。</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -1769,62 +1769,62 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
+          <t>&gt; 区分は先に決めてください。区分によって次の画面に表示される項目が変わります。あとから区分を変更すると、設定をやり直していただく場合があります。</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
           <t>&gt; 会社と店舗の両方の画面を使う場合は、権限を2つ作ってください。1つの権限で会社画面と店舗画面の両方を扱うことはできません。たとえば経理の方が「お支払い（会社画面）」と「費用設定・予算設定（店舗画面）」の両方を見る場合、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当てます。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B91" s="17" t="inlineStr">
+      <c r="B92" s="17" t="inlineStr">
         <is>
           <t>STEP 4　画面ごとに設定して保存する</t>
         </is>
       </c>
-      <c r="C91" s="16" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="C92" s="16" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>画面ごとに「操作」「閲覧」「なし」を選び、「保存」を選択します。保存すると権限一覧に戻ります。</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="12" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B93" s="13" t="inlineStr">
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>設定 ｜ できること</t>
         </is>
       </c>
-      <c r="C93" s="12" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr"/>
+      <c r="C94" s="12" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>閲覧 ｜ 画面を開けます</t>
+          <t>操作 ｜ 画面を開けて、登録・編集・削除ができます</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -1847,131 +1847,131 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
+          <t>閲覧 ｜ 画面を開けます</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>表 行</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
           <t>なし ｜ 画面が表示されません</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>&gt; 「閲覧」と「操作」は、今回のリリースではどちらも画面を開けるかどうかの設定として動作します。「閲覧」を選んだ場合に画面内の変更操作を禁止する制御は、次回以降のリリースで対応予定です。変更させたくない方には、その画面を「なし」に設定してください。</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>「操作」は「閲覧」を含みます。「操作」を選ぶと「閲覧」も自動的に有効になります。</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="15" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B99" s="15" t="inlineStr">
+      <c r="B100" s="15" t="inlineStr">
         <is>
           <t>【画像④】</t>
         </is>
       </c>
-      <c r="C99" s="15" t="inlineStr">
+      <c r="C100" s="15" t="inlineStr">
         <is>
           <t>画面ごとの設定（操作／閲覧／なし）　※スクリーンショット未取得（撮影リスト ④ 番）</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>&gt; さらに細かく設定することもできます。画面名を選択すると、その画面の中の機能や、表示する数字（指標）を個別に設定できます。</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>続けてメンバーに割り当てる場合は、「保存」ではなく「🔗 ユーザー割当で紐付け →」を選択します。</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>権限をメンバーに割り当てる</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="C103" s="10" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>作成した権限は、メンバーに割り当てて初めて有効になります。割り当て方法は3つあり、目的に応じて使い分けます。始める画面と、保存後に開く画面がそれぞれ違います。</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="12" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B104" s="13" t="inlineStr">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>方法 ｜ 始める画面 ｜ 保存後に開く画面</t>
         </is>
       </c>
-      <c r="C104" s="12" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr"/>
+      <c r="C105" s="12" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
+          <t>方法1　まとめて割り当てる ｜ 権限の設定画面 ｜ 役割サマリ</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
+          <t>方法2　メンバーを選んで割り当てる ｜ ユーザー割当 ｜ ユーザー割当</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -2002,41 +2002,41 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
+          <t>方法3　権限から探して割り当てる ｜ 役割サマリ ｜ ユーザー割当（絞り込みは保たれます）</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
           <t>「役割サマリ」は、権限ごとに何名へ割り当てているかを確認する画面です。</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="16" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B109" s="17" t="inlineStr">
+      <c r="B110" s="17" t="inlineStr">
         <is>
           <t>方法1　まとめて割り当てる（権限を作った直後におすすめ）</t>
         </is>
       </c>
-      <c r="C109" s="16" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択する</t>
-        </is>
-      </c>
-      <c r="C110" s="4" t="inlineStr"/>
+      <c r="C110" s="16" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>2. 割り当てる方の「含める」にチェックを入れる</t>
+          <t>1. 権限の設定画面の下部で「🔗 ユーザー割当で紐付け →」を選択する</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr"/>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>3. 店舗の権限の場合は、あわせて担当店舗を選ぶ</t>
+          <t>2. 割り当てる方の「含める」にチェックを入れる</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr"/>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>3. 店舗の権限の場合は、あわせて担当店舗を選ぶ</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr"/>
@@ -2080,45 +2080,45 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
           <t>保存すると役割サマリが開き、割り当てた権限が強調表示されます。</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B115" s="15" t="inlineStr">
+      <c r="B116" s="15" t="inlineStr">
         <is>
           <t>【画像⑤】</t>
         </is>
       </c>
-      <c r="C115" s="15" t="inlineStr">
+      <c r="C116" s="15" t="inlineStr">
         <is>
           <t>まとめて割り当てる画面　※スクリーンショット未取得（撮影リスト ⑤ 番）</t>
         </is>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>&gt; すでに別の権限をお持ちの方については、1人が持てる権限が1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -2128,36 +2128,36 @@
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
+          <t>&gt; すでに別の権限をお持ちの方については、1人が持てる権限が1つのため、行に「⚠ 既に『◯◯』を保持。含めると置き換わります」と表示されます。保存前にも確認画面が表示されます。すでにこの権限をお持ちの方には「✓ この権限で登録済み」と表示されます。</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
           <t>&gt; 対象は自動で絞り込まれます。店舗の権限を割り当てるときは店舗所属の方、会社の権限を割り当てるときは本部所属の方が表示されます。全員から選びたい場合は「すべて表示」を選択してください。</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B118" s="17" t="inlineStr">
+      <c r="B119" s="17" t="inlineStr">
         <is>
           <t>方法2　メンバーを選んで割り当てる（入社・異動のとき）</t>
         </is>
       </c>
-      <c r="C118" s="16" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「ユーザー割当」を選択する</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr"/>
+      <c r="C119" s="16" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の方の行で「割当を編集」を選択する</t>
+          <t>1. 権限設定画面の上部で「ユーザー割当」を選択する</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr"/>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>3. 権限を1つ選ぶ</t>
+          <t>2. 対象の方の行で「割当を編集」を選択する</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>3. 権限を1つ選ぶ</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr"/>
@@ -2201,58 +2201,58 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
           <t>保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="15" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B124" s="15" t="inlineStr">
+      <c r="B125" s="15" t="inlineStr">
         <is>
           <t>【画像⑥】</t>
         </is>
       </c>
-      <c r="C124" s="15" t="inlineStr">
+      <c r="C125" s="15" t="inlineStr">
         <is>
           <t>メンバーごとの割当編集画面　※スクリーンショット未取得（撮影リスト ⑥ 番）</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="16" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B125" s="17" t="inlineStr">
+      <c r="B126" s="17" t="inlineStr">
         <is>
           <t>方法3　権限から探して割り当てる（保持者を確認したいとき）</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定画面の上部で「役割サマリ」を選択する</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr"/>
+      <c r="C126" s="16" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>2. 対象の権限の「割当へ →」を選択する</t>
+          <t>1. 権限設定画面の上部で「役割サマリ」を選択する</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開く</t>
+          <t>2. 対象の権限の「割当へ →」を選択する</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr"/>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>4. 対象の方の行で「割当を編集」→「保存」を選択する</t>
+          <t>3. その権限をお持ちの方に絞り込まれた状態でユーザー割当が開く</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr"/>
@@ -2296,41 +2296,41 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
+          <t>4. 対象の方の行で「割当を編集」→「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
           <t>絞り込みは保たれたままです。</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B131" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>担当店舗を設定する</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr"/>
+      <c r="C132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -2340,50 +2340,50 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
           <t>どの店舗の数字を見せるかは、権限ではなく人ごとに決めます。 同じ「店長」の権限でも、渋谷店の店長には渋谷店を、新宿店の店長には新宿店を設定します。</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="14" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
         <is>
           <t>図</t>
         </is>
       </c>
-      <c r="B134" s="14" t="inlineStr">
+      <c r="B135" s="14" t="inlineStr">
         <is>
           <t>【図2】</t>
         </is>
       </c>
-      <c r="C134" s="14" t="inlineStr">
+      <c r="C135" s="14" t="inlineStr">
         <is>
           <t>権限と担当店舗の関係　※作成済み。help/figures/ の SVG または PNG を掲載</t>
         </is>
       </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
-        </is>
-      </c>
-      <c r="C135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>1. 割当編集の画面で、店舗の権限を選択する</t>
+          <t>店舗の権限（区分が「店舗」の権限）を割り当てると、担当店舗の選択欄が表示されます。</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr"/>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>2. 「対象店舗」で担当店舗を選ぶ</t>
+          <t>1. 割当編集の画面で、店舗の権限を選択する</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れる</t>
+          <t>2. 「対象店舗」で担当店舗を選ぶ</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr"/>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>4. 「保存」を選択する</t>
+          <t>3. すべての店舗を選ぶ場合は「全店」にチェックを入れる</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr"/>
@@ -2430,110 +2430,110 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
+          <t>4. 「保存」を選択する</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
           <t>担当店舗は複数選択できます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B141" s="15" t="inlineStr">
+      <c r="B142" s="15" t="inlineStr">
         <is>
           <t>【画像⑦】</t>
         </is>
       </c>
-      <c r="C141" s="15" t="inlineStr">
+      <c r="C142" s="15" t="inlineStr">
         <is>
           <t>担当店舗の選択画面　※スクリーンショット未取得（撮影リスト ⑦ 番）</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>&gt; 担当店舗は必ず1つ以上お選びください。店舗の権限で担当店舗が未設定の場合、保存できません。また、権限の設定画面に「⚠ ◯名が店舗未設定」と表示されます。</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="C143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>会社の権限は全社が対象となるため、担当店舗の設定は不要です。</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B144" s="6" t="inlineStr">
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>&gt; 今回のリリースでは、担当店舗は割り当ての記録として保存されます。担当外の店舗のデータを画面に出さない制御は、次回以降のリリースで対応予定です。</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="C145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>ここまでで初期設定は完了です。 以降は、見せる数字をさらに絞りたいとき、権限を直したいとき、異動・退職で付け替えたいときにお読みください。</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="10" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B146" s="11" t="inlineStr">
+      <c r="B147" s="11" t="inlineStr">
         <is>
           <t>表示する数字を選ぶ</t>
         </is>
       </c>
-      <c r="C146" s="10" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
-        </is>
-      </c>
-      <c r="C147" s="4" t="inlineStr"/>
+      <c r="C147" s="10" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -2543,36 +2543,36 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
+          <t>同じ画面でも、表示する数字（指標）を権限ごとに選べます。</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
           <t>流れ — 権限一覧 →「指標一覧」→ 店舗／会社のタブを切り替えて選ぶ → その場で反映（保存ボタンはありません）</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>&gt; 今回のリリースでは、この設定は指標一覧の画面での選択状態を保存するところまでです。選んだ内容が分析画面の表示に反映されるのは次回以降のリリースになります。</t>
         </is>
       </c>
-      <c r="C149" s="5" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>手順</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択する</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr"/>
+      <c r="C150" s="5" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替える</t>
+          <t>1. 権限設定の一覧で、対象の権限の「指標一覧」を選択する</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>3. 各項目を選択して、表示／非表示を切り替える</t>
+          <t>2. 🏬店舗指標／🏢会社指標のタブを切り替える</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr"/>
@@ -2603,58 +2603,58 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
+          <t>3. 各項目を選択して、表示／非表示を切り替える</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
           <t>保存操作は不要で、その場で反映されます。</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="15" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B154" s="15" t="inlineStr">
+      <c r="B155" s="15" t="inlineStr">
         <is>
           <t>【画像⑧】</t>
         </is>
       </c>
-      <c r="C154" s="15" t="inlineStr">
+      <c r="C155" s="15" t="inlineStr">
         <is>
           <t>指標一覧の画面　※スクリーンショット未取得（撮影リスト ⑧ 番）</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="B156" s="6" t="inlineStr">
         <is>
           <t>&gt; 初期値は自動で設定されます。権限の性質に応じた初期値が設定済みです。現場でお使いいただく数字は表示、経営に関わる数字は非表示から始まります。設定後の変更は自由です。</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr"/>
+      <c r="C156" s="5" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -2664,62 +2664,62 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
+          <t>項目が多い場合は「指標条件設定」が便利です。 「指標条件設定 ＞」から、おすすめの組み合わせ（現場スタッフ向け／店長向け／管理者・経理向け）を選んで一括設定できます。この画面だけは「適用して指標一覧へ」を選ぶまで反映されません。「キャンセル」を選ぶと、変更は破棄されて指標一覧に戻ります。</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
           <t>作った組み合わせは「名前をつけて保存」するとマイテンプレートに登録されます。他の権限を設定するときに読み込めるので、同じ組み合わせを作り直す必要はありません。保存した組み合わせは更新・削除もできます。</t>
         </is>
       </c>
-      <c r="C157" s="4" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="C158" s="4" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B158" s="11" t="inlineStr">
+      <c r="B159" s="11" t="inlineStr">
         <is>
           <t>作成した権限を修正する</t>
         </is>
       </c>
-      <c r="C158" s="10" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="C159" s="10" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t>作成済みの権限は、いくつかの入口から修正できます。どこから入っても同じ編集画面が開き、保存すると元いた画面に戻ります。</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="12" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B160" s="13" t="inlineStr">
+      <c r="B161" s="13" t="inlineStr">
         <is>
           <t>入口 ｜ 操作 ｜ こんなときに</t>
         </is>
       </c>
-      <c r="C160" s="12" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr"/>
+      <c r="C161" s="12" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
+          <t>権限一覧 ｜ 対象の権限の行で「権限編集」 ｜ 権限をまとめて見直したいとき</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr"/>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
+          <t>権限一覧のマス目 ｜ 権限×画面のマス目を選択 ｜ 一覧で気づいた箇所をその場で直したいとき</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+          <t>役割サマリ ｜ 対象の権限の行で「権限編集」 ｜ 全体を確認していて気づいたとき</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr"/>
@@ -2763,45 +2763,45 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
+          <t>割当編集 ｜ 権限の行で「権限編集 →」 ｜ メンバーの設定中に権限そのものを直したいとき（割当編集の開き方は「権限をメンバーに割り当てる」で説明します）</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
           <t>権限名を変えるには — 編集画面の上部にある基本情報で、権限名を書き換えて「基本情報を更新」を選択します。権限名を変えても、その権限を割り当てた方の設定はそのまま引き継がれます。</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="15" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B166" s="15" t="inlineStr">
+      <c r="B167" s="15" t="inlineStr">
         <is>
           <t>【画像⑨】</t>
         </is>
       </c>
-      <c r="C166" s="15" t="inlineStr">
+      <c r="C167" s="15" t="inlineStr">
         <is>
           <t>マス目を選択して該当箇所へ移動したところ　※スクリーンショット未取得（撮影リスト ⑨ 番）</t>
         </is>
       </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>注記（引用）</t>
-        </is>
-      </c>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -2811,49 +2811,49 @@
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
+          <t>&gt; 権限一覧のマス目を選択すると、その画面の設定箇所まで自動で移動し、一時的に色が付いて表示されます。27種類の画面から目的の項目を探す必要はありません。</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>注記（引用）</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
           <t>&gt; 権限の修正は、その権限をお持ちの全員に反映されますのでご注意ください。特定の方だけ変更したい場合は、権限を修正するのではなく、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
-      <c r="C168" s="5" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="C169" s="5" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>メンバーの設定中に必要な権限が無いことに気づいた場合は、割当編集の画面から「＋ 権限を新規作成」を選ぶと、その場で権限を作れます。作成後は元の割当編集の画面に戻ります。</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="10" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B170" s="11" t="inlineStr">
+      <c r="B171" s="11" t="inlineStr">
         <is>
           <t>権限を変更・解除する</t>
         </is>
       </c>
-      <c r="C170" s="10" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr"/>
+      <c r="C171" s="10" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -2863,127 +2863,127 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
+          <t>開く場所 — 権限設定画面の上部で「ユーザー割当」→ 対象の方の行で「割当を編集」</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
           <t>異動や退職で、割り当て済みの権限を付け替える／外すときの操作です。</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="8" t="inlineStr">
+      <c r="C173" s="4" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B173" s="9" t="inlineStr">
+      <c r="B174" s="9" t="inlineStr">
         <is>
           <t>別の権限に変更する</t>
         </is>
       </c>
-      <c r="C173" s="8" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="C174" s="8" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>割当編集の画面で、別の権限を選んで保存します。それまでの権限は自動的に外れます。 選択する前に、行に「選ぶと『◯◯』から置き換わります」と表示されます。保存するとユーザー割当に戻ります。</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="8" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B175" s="9" t="inlineStr">
+      <c r="B176" s="9" t="inlineStr">
         <is>
           <t>権限を外す</t>
         </is>
       </c>
-      <c r="C175" s="8" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="C176" s="8" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>割当編集の画面で「割当なし」を選んで保存します。担当店舗の選択欄も表示されなくなります。保存するとユーザー割当に戻り、その方は「未割当」と表示されます。</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="5" t="inlineStr">
+      <c r="C177" s="4" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="B178" s="6" t="inlineStr">
         <is>
           <t>&gt; 権限を外した方は、ログインしても画面が表示されませんのでご注意ください。退職・異動の際は、権限を外すか、別の権限に付け替えてください。</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="10" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B178" s="11" t="inlineStr">
+      <c r="B179" s="11" t="inlineStr">
         <is>
           <t>オーナーだけができること</t>
         </is>
       </c>
-      <c r="C178" s="10" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="C179" s="10" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t>全権をお持ちの方（オーナー）は、画面右上の「👑 オーナー操作」から次の2つを行えます。</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="12" t="inlineStr">
+      <c r="C180" s="4" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B180" s="13" t="inlineStr">
+      <c r="B181" s="13" t="inlineStr">
         <is>
           <t>操作 ｜ 内容</t>
         </is>
       </c>
-      <c r="C180" s="12" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr"/>
+      <c r="C181" s="12" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+          <t>指標管理 ｜ すべての数字を一覧で確認できます（確認のみ。変更はできません）</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr"/>
@@ -3001,41 +3001,41 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
+          <t>全権の付与先を指定 ｜ 全権を委ねる相手を指名できます</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
           <t>オーナーの権限は全権で固定されているため、権限設定の一覧には表示されません。設定を変更することもできません。</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="10" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B184" s="11" t="inlineStr">
+      <c r="B185" s="11" t="inlineStr">
         <is>
           <t>設定内容を確認する</t>
         </is>
       </c>
-      <c r="C184" s="10" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>設定が増えてきたら、一覧で確認できます。</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr"/>
+      <c r="C185" s="10" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+          <t>設定が増えてきたら、一覧で確認できます。</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr"/>
@@ -3058,76 +3058,76 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
+          <t>権限一覧 — 権限ごとに、どの画面をどこまで使えるかを一覧で見比べられます。「👤 表示ロール」で見たい権限だけに絞り込み、「📌 権限列設定」で見たい画面だけを表示できます。選んだ表示は次に開いたときも保持されます。</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
           <t>役割サマリ — 権限ごとに「割当ユーザー ◯名」を確認できます。店舗が未設定の方がいる場合は警告が表示されます。</t>
         </is>
       </c>
-      <c r="C187" s="4" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="15" t="inlineStr">
+      <c r="C188" s="4" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="inlineStr">
         <is>
           <t>画像</t>
         </is>
       </c>
-      <c r="B188" s="15" t="inlineStr">
+      <c r="B189" s="15" t="inlineStr">
         <is>
           <t>【画像⑩】</t>
         </is>
       </c>
-      <c r="C188" s="15" t="inlineStr">
+      <c r="C189" s="15" t="inlineStr">
         <is>
           <t>役割サマリの画面　※スクリーンショット未取得（撮影リスト ⑩ 番）</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="10" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B189" s="11" t="inlineStr">
+      <c r="B190" s="11" t="inlineStr">
         <is>
           <t>ケース別のやり方</t>
         </is>
       </c>
-      <c r="C189" s="10" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="16" t="inlineStr">
+      <c r="C190" s="10" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B190" s="17" t="inlineStr">
+      <c r="B191" s="17" t="inlineStr">
         <is>
           <t>どのケースも共通の登録手順</t>
         </is>
       </c>
-      <c r="C190" s="16" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr"/>
+      <c r="C191" s="16" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>本文</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
+          <t>権限の登録は、どのケースでも次の3つを順に行います。</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
+          <t>1. 権限を作成する — 雛形を選び、権限名と区分を決め、画面ごとに「操作／閲覧／なし」を設定して保存します。</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
+          <t>2. 権限をメンバーに割り当てる — 対象の方に、作った権限を付けます。1人が持てる権限は1つです。</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr"/>
@@ -3161,54 +3161,54 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>手順</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
+          <t>3. 担当店舗を設定する — 区分が「店舗」の場合のみ。どの店舗の数字を見せるかを、メンバーごとに選びます。</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
           <t>以下は、この3つのうちケースによって変わる部分だけをご案内します。</t>
         </is>
       </c>
-      <c r="C195" s="4" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="16" t="inlineStr">
+      <c r="C196" s="4" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="16" t="inlineStr">
         <is>
           <t>H3</t>
         </is>
       </c>
-      <c r="B196" s="17" t="inlineStr">
+      <c r="B197" s="17" t="inlineStr">
         <is>
           <t>ケース別の設定</t>
         </is>
       </c>
-      <c r="C196" s="16" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="8" t="inlineStr">
+      <c r="C197" s="16" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B197" s="9" t="inlineStr">
+      <c r="B198" s="9" t="inlineStr">
         <is>
           <t>経理担当に、売上とお支払だけ見せたい</t>
         </is>
       </c>
-      <c r="C197" s="8" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr"/>
+      <c r="C198" s="8" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -3218,88 +3218,88 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
+          <t>区分は「会社」、雛形は「本部管理」を選びます。従業員（閲覧）・従業員管理・ユーザーを「なし」にすると、売上や仕入の数字とお支払いは見えて、従業員の情報は見えない状態になります。区分が「会社」なので、担当店舗の設定は不要です。</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
           <t>ただしお支払いは会社の画面、費用設定・予算設定は店舗の画面です。経理の方が両方を扱う場合は、「経理（会社）」と「経理（店舗）」の2つの権限を作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="8" t="inlineStr">
+      <c r="C200" s="4" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B200" s="9" t="inlineStr">
+      <c r="B201" s="9" t="inlineStr">
         <is>
           <t>人事担当に、従業員情報だけ見せたい</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
+      <c r="C201" s="8" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
         <is>
           <t>区分は「会社」、雛形は「本部管理」を選びます。売上分析・仕入分析・詳細分析・集計・お支払いを「なし」にすると、従業員の情報と締め管理は見えて、経営の数字は見えない状態になります。担当店舗の設定は不要です。</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="8" t="inlineStr">
+      <c r="C202" s="4" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B202" s="9" t="inlineStr">
+      <c r="B203" s="9" t="inlineStr">
         <is>
           <t>アルバイトリーダーに、一部の画面だけ見せたい</t>
         </is>
       </c>
-      <c r="C202" s="8" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="C203" s="8" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
         <is>
           <t>区分は「店舗」、雛形は「店長」を選びます。仕入分析・詳細分析・従業員（閲覧）・従業員管理・締め管理・費用設定・予算設定を「なし」にすると、売上と日々の入力画面だけが残ります。所属する店舗を担当店舗に設定してください。</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="8" t="inlineStr">
+      <c r="C204" s="4" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B204" s="9" t="inlineStr">
+      <c r="B205" s="9" t="inlineStr">
         <is>
           <t>複数の店舗をまとめて見せたい（エリアマネージャー）</t>
         </is>
       </c>
-      <c r="C204" s="8" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr"/>
+      <c r="C205" s="8" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -3309,118 +3309,114 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
+          <t>区分は「店舗」、雛形は「店長」を選びます。画面の設定は変えずに権限名を「エリアマネージャー」などに変え、担当店舗で複数の店舗を選びます。</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
           <t>エリアマネージャーは雛形の一覧にはありません。担当する店舗数や見せる範囲は組織によって変わるため、権限は「店長」と共通のものを使い、店舗はメンバーごとに設定する形にしています。</t>
         </is>
       </c>
-      <c r="C206" s="4" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="8" t="inlineStr">
+      <c r="C207" s="4" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B207" s="9" t="inlineStr">
+      <c r="B208" s="9" t="inlineStr">
         <is>
           <t>新しく入った方には、まず最小限から始めたい</t>
         </is>
       </c>
-      <c r="C207" s="8" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
+      <c r="C208" s="8" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
         <is>
           <t>区分は「店舗」、雛形は「まっさら（なし）」を選びます。ダッシュボード以外をすべて「なし」にすると、ログインしてダッシュボードだけが見える状態になります。慣れてきたら、必要な画面を1つずつ追加してください。</t>
         </is>
       </c>
-      <c r="C208" s="4" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="8" t="inlineStr">
+      <c r="C209" s="4" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
         <is>
           <t>小見出し</t>
         </is>
       </c>
-      <c r="B209" s="9" t="inlineStr">
+      <c r="B210" s="9" t="inlineStr">
         <is>
           <t>会社と店舗の両方の画面を使わせたい</t>
         </is>
       </c>
-      <c r="C209" s="8" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
+      <c r="C210" s="8" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
         <is>
           <t>1つの権限ではできません。区分ごとに権限を2つ作り、担当を分けて割り当ててください。1人が持てる権限は1つのためです。</t>
         </is>
       </c>
-      <c r="C210" s="4" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="5" t="inlineStr">
+      <c r="C211" s="4" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
         <is>
           <t>注記（引用）</t>
         </is>
       </c>
-      <c r="B211" s="6" t="inlineStr">
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>&gt; 画面の名前は区分によって変わります。会社の権限を作っているときに「費用設定」が見当たらないのは、それが店舗の画面のためです。どの画面がどちらに属するかは「権限を作成する」の STEP 3 にある図でご確認いただけます。</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="10" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B212" s="11" t="inlineStr">
+      <c r="B213" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問</t>
         </is>
       </c>
-      <c r="C212" s="10" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
+      <c r="C213" s="10" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
         <is>
           <t>権限の持ち方、見える範囲、設定を間違えたときの戻し方についてのご質問です。</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="18" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="B214" s="18" t="inlineStr">
-        <is>
-          <t>Q. 1人に複数の権限を割り当てられますか？</t>
-        </is>
-      </c>
-      <c r="C214" s="18" t="inlineStr">
-        <is>
-          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
-        </is>
-      </c>
+      <c r="C214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="18" t="inlineStr">
@@ -3430,12 +3426,12 @@
       </c>
       <c r="B215" s="18" t="inlineStr">
         <is>
-          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
+          <t>Q. 1人に複数の権限を割り当てられますか？</t>
         </is>
       </c>
       <c r="C215" s="18" t="inlineStr">
         <is>
-          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
+          <t>できません。1人が持てる権限は1つです。「店長 兼 経理」のように兼務される方には、その方に合わせた権限を新しく作成してご利用ください。</t>
         </is>
       </c>
     </row>
@@ -3447,12 +3443,12 @@
       </c>
       <c r="B216" s="18" t="inlineStr">
         <is>
-          <t>Q. 権限を変更すると、誰に影響しますか？</t>
+          <t>Q. 会社の画面と店舗の画面を1人で両方見られますか？</t>
         </is>
       </c>
       <c r="C216" s="18" t="inlineStr">
         <is>
-          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
+          <t>1つの権限ではできません。権限は会社／店舗のどちらかの区分に属し、1人が持てる権限は1つのためです。両方を見る必要がある場合は、区分ごとに権限を作り、担当を分けて割り当ててください（例：「経理（会社）」と「経理（店舗）」）。</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3460,12 @@
       </c>
       <c r="B217" s="18" t="inlineStr">
         <is>
-          <t>Q. 設定した権限はいつから反映されますか？</t>
+          <t>Q. 権限を変更すると、誰に影響しますか？</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
         <is>
-          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
+          <t>その権限をお持ちの全員に反映されます。特定の方だけ変更したい場合は、既存の権限をコピーして新しい権限を作成し、その方に割り当ててください。</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3477,12 @@
       </c>
       <c r="B218" s="18" t="inlineStr">
         <is>
-          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
+          <t>Q. 設定した権限はいつから反映されますか？</t>
         </is>
       </c>
       <c r="C218" s="18" t="inlineStr">
         <is>
-          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
+          <t>保存後に反映されます。対象の方がログイン中の場合は、画面を移動された時点から反映されます。</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3494,12 @@
       </c>
       <c r="B219" s="18" t="inlineStr">
         <is>
-          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
+          <t>Q. 権限を絞りすぎて、何も見えなくなりませんか？</t>
         </is>
       </c>
       <c r="C219" s="18" t="inlineStr">
         <is>
-          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
+          <t>ダッシュボードは常に表示されます。すべての画面を「なし」にしても、ログインしてダッシュボードに着地します。</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3511,12 @@
       </c>
       <c r="B220" s="18" t="inlineStr">
         <is>
-          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
+          <t>Q. 同じ権限で、人によって担当店舗を変えられますか？</t>
         </is>
       </c>
       <c r="C220" s="18" t="inlineStr">
         <is>
-          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
+          <t>できます。権限は共通のものを使い、担当店舗をメンバーごとに設定してください。同じ権限でも、Aさんは2店舗、Bさんは3店舗という割り当てが可能です。ただし今回のリリースでは、担当店舗は割り当ての記録として保存されるところまでで、担当外の店舗のデータを画面に出さない制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
@@ -3532,12 +3528,12 @@
       </c>
       <c r="B221" s="18" t="inlineStr">
         <is>
-          <t>Q. 役職を変更すると権限も変わりますか？</t>
+          <t>Q. 画面は見せたいが、変更はさせたくない場合はどうすればよいですか？</t>
         </is>
       </c>
       <c r="C221" s="18" t="inlineStr">
         <is>
-          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
+          <t>今回のリリースでは、その設定はできません。「閲覧」を選んでも画面内の変更操作は制限されないためです。変更させたくない場合は、その画面を「なし」に設定してください。変更のみを禁止する制御は次回以降のリリースで対応予定です。</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3545,12 @@
       </c>
       <c r="B222" s="18" t="inlineStr">
         <is>
-          <t>Q. 自分の権限を変更できますか？</t>
+          <t>Q. 役職を変更すると権限も変わりますか？</t>
         </is>
       </c>
       <c r="C222" s="18" t="inlineStr">
         <is>
-          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
+          <t>変わりません。役職は従業員情報の肩書きで、権限とは別のものです。権限を変更する場合は「ユーザー割当」から操作してください。</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3562,12 @@
       </c>
       <c r="B223" s="18" t="inlineStr">
         <is>
-          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
+          <t>Q. 自分の権限を変更できますか？</t>
         </is>
       </c>
       <c r="C223" s="18" t="inlineStr">
         <is>
-          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
+          <t>権限設定の画面を開けなくなる変更はできません。誤ってご自身を締め出さないよう、警告が表示されます。</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3579,12 @@
       </c>
       <c r="B224" s="18" t="inlineStr">
         <is>
-          <t>Q. 権限が未設定の方はどうなりますか？</t>
+          <t>Q. 作った指標の組み合わせを、他の権限にも使えますか？</t>
         </is>
       </c>
       <c r="C224" s="18" t="inlineStr">
         <is>
-          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+          <t>できます。「指標条件設定」で作った組み合わせを「名前をつけて保存」すると、マイテンプレートに登録され、他の権限を設定するときに読み込めます。</t>
         </is>
       </c>
     </row>
@@ -3600,66 +3596,70 @@
       </c>
       <c r="B225" s="18" t="inlineStr">
         <is>
+          <t>Q. 権限が未設定の方はどうなりますか？</t>
+        </is>
+      </c>
+      <c r="C225" s="18" t="inlineStr">
+        <is>
+          <t>ログインしても画面が表示されません。「ユーザー割当」で未割当の方がいないかご確認ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="18" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="B226" s="18" t="inlineStr">
+        <is>
           <t>Q. 新しい画面が追加された場合、権限はどうなりますか？</t>
         </is>
       </c>
-      <c r="C225" s="18" t="inlineStr">
+      <c r="C226" s="18" t="inlineStr">
         <is>
           <t>すべての権限で「なし」の状態で追加されます。ご利用になる場合は、権限設定から個別に許可してください。</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="10" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B226" s="11" t="inlineStr">
+      <c r="B227" s="11" t="inlineStr">
         <is>
           <t>用語の説明</t>
         </is>
       </c>
-      <c r="C226" s="10" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>本文</t>
-        </is>
-      </c>
-      <c r="B227" s="4" t="inlineStr">
+      <c r="C227" s="10" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
         <is>
           <t>画面に出てくる言葉の意味です。読んでいて分からない言葉が出たときにご覧ください。</t>
         </is>
       </c>
-      <c r="C227" s="4" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="12" t="inlineStr">
+      <c r="C228" s="4" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="12" t="inlineStr">
         <is>
           <t>表 見出し</t>
         </is>
       </c>
-      <c r="B228" s="13" t="inlineStr">
+      <c r="B229" s="13" t="inlineStr">
         <is>
           <t>用語 ｜ 意味</t>
         </is>
       </c>
-      <c r="C228" s="12" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>表 行</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr"/>
+      <c r="C229" s="12" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
+          <t>権限 ｜ 「どの画面をどこまで使えるか」を決めたもの。名前を付けて保存します</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr"/>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
+          <t>区分 ｜ その権限が会社画面向けか店舗画面向けか。会社／店舗のどちらかを選びます</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
+          <t>担当店舗 ｜ 店舗の権限を持つメンバーが、どの店舗を担当するか。メンバーごとに設定します</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr"/>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
+          <t>スコープ選択 ｜ 画面上部にある、会社と店舗を切り替える欄。ここで選んだ側の権限と画面が表示されます</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr"/>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
+          <t>雛形（ベース） ｜ 権限を作るときの土台。近いものを選んで違うところだけ直します</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr"/>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
+          <t>権限母体 ｜ 経理・人事など複数の権限を派生させるための、共通の土台となる権限</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr"/>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
+          <t>権限一覧 ｜ 作った権限を、画面ごとの設定とあわせて一覧で見比べる画面</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr"/>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+          <t>役割サマリ ｜ 権限ごとに、何名に割り当てているかを確認する画面</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr"/>
@@ -3768,41 +3768,41 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>表 行</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
+          <t>指標 ｜ 売上・原価・人件費など、画面に表示される数字のこと</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
           <t>「役職」は従業員情報に登録された肩書きで、権限とは別のものです。役職を変更しても権限は変わりません。</t>
         </is>
       </c>
-      <c r="C238" s="4" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="10" t="inlineStr">
+      <c r="C239" s="4" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="10" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="B239" s="11" t="inlineStr">
+      <c r="B240" s="11" t="inlineStr">
         <is>
           <t>参照リンク</t>
         </is>
       </c>
-      <c r="C239" s="10" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
-        <is>
-          <t>箇条書き</t>
-        </is>
-      </c>
-      <c r="B240" s="4" t="inlineStr">
-        <is>
-          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
-        </is>
-      </c>
-      <c r="C240" s="4" t="inlineStr"/>
+      <c r="C240" s="10" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+          <t>・[ラクミー経営管理 ログイン](https://manager.rakmy.jp/users/sign_in)</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr"/>
@@ -3820,18 +3820,31 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>本文</t>
+          <t>箇条書き</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
+          <t>・[店舗の登録方法](https://help.rakmy.jp/management/店舗)</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
           <t>サポートが必要ですか？ [サポートチームに連絡](https://docs.google.com/forms/d/e/1FAIpQLSe1qwnma82vLEpQQNdzjl_gLSt_qHMHZp6eqmhaziUB11IAOA/viewform)</t>
         </is>
       </c>
-      <c r="C242" s="4" t="inlineStr"/>
+      <c r="C243" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C242"/>
+  <autoFilter ref="A2:C243"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>